--- a/compare/output/dscale_per_capita_co2_downscaled_SSP245.xlsx
+++ b/compare/output/dscale_per_capita_co2_downscaled_SSP245.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.01454074560602464</v>
+        <v>0.01454064189319881</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01871787220954733</v>
+        <v>0.018717688589384</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02057582776175348</v>
+        <v>0.02057557853601478</v>
       </c>
       <c r="H2" t="n">
-        <v>0.02258001409158922</v>
+        <v>0.02257947916141289</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02481252169764505</v>
+        <v>0.02481131479387148</v>
       </c>
       <c r="J2" t="n">
         <v>0.09881113284428165</v>
@@ -684,13 +684,13 @@
         <v>0.2898401301933755</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2662677623096311</v>
+        <v>0.2662686583212148</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2624914850496511</v>
+        <v>0.2624931774621428</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2750983581857457</v>
+        <v>0.2751007753436997</v>
       </c>
       <c r="J4" t="n">
         <v>0.125368615304722</v>
@@ -760,13 +760,13 @@
         <v>0.0459760820640894</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06336049295740018</v>
+        <v>0.06336036354780042</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08310511544550091</v>
+        <v>0.08310488123574689</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1026065445336482</v>
+        <v>0.1026060110681292</v>
       </c>
       <c r="J5" t="n">
         <v>0.1287076814709371</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0473698744464414</v>
+        <v>0.04736985284731557</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0610421621138909</v>
+        <v>0.06104208446012188</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06106515438709138</v>
+        <v>0.06106499606390979</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06222831233655504</v>
+        <v>0.06222798968149105</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06643290485276142</v>
+        <v>0.06643205901968695</v>
       </c>
       <c r="J6" t="n">
         <v>0.1131686277259659</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.1263994522279574</v>
+        <v>0.126399496119948</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1723574866925069</v>
+        <v>0.1723576643560535</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2063792188829621</v>
+        <v>0.206379596128313</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2481236624967344</v>
+        <v>0.2481245206772827</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2993113484398103</v>
+        <v>0.2993137628844239</v>
       </c>
       <c r="J7" t="n">
         <v>0.1418681565809266</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04676888530936796</v>
+        <v>0.04676884316430211</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05901822018679832</v>
+        <v>0.05901814575032892</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06405466950681389</v>
+        <v>0.06405453641650347</v>
       </c>
       <c r="H8" t="n">
-        <v>0.070191013498688</v>
+        <v>0.07019074298389837</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07805597771301442</v>
+        <v>0.07805529140211669</v>
       </c>
       <c r="J8" t="n">
         <v>0.1148677500754383</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9745719228178303</v>
+        <v>0.9745726729749883</v>
       </c>
       <c r="F9" t="n">
-        <v>1.064596624179864</v>
+        <v>1.064598087728003</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9671534360359022</v>
+        <v>0.9671570113666916</v>
       </c>
       <c r="H9" t="n">
-        <v>0.923907944257175</v>
+        <v>0.923913554162585</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9388372864488307</v>
+        <v>0.9388490352186653</v>
       </c>
       <c r="J9" t="n">
         <v>0.1751965754381352</v>
@@ -1137,16 +1137,16 @@
         <v>0.02947245745995844</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03424583309392912</v>
+        <v>0.03424568763314208</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0327824590359035</v>
+        <v>0.03278219747251296</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03291667260962378</v>
+        <v>0.03291613774348295</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03443675053971199</v>
+        <v>0.03443533704068757</v>
       </c>
       <c r="J10" t="n">
         <v>0.1149054903057933</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.1432747365066669</v>
+        <v>0.1432747979067484</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1803656899248412</v>
+        <v>0.1803658560217033</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1952708532157484</v>
+        <v>0.1952711394551753</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2169445781414336</v>
+        <v>0.2169451516821407</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2453177448325659</v>
+        <v>0.2453191422540495</v>
       </c>
       <c r="J11" t="n">
         <v>0.1489868069269987</v>
@@ -1289,16 +1289,16 @@
         <v>0.02574079203782809</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03416505333992016</v>
+        <v>0.03416496432878931</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03938947877436778</v>
+        <v>0.03938931485404944</v>
       </c>
       <c r="H12" t="n">
-        <v>0.04570159324414726</v>
+        <v>0.04570121400865567</v>
       </c>
       <c r="I12" t="n">
-        <v>0.053156955327059</v>
+        <v>0.05315603492159916</v>
       </c>
       <c r="J12" t="n">
         <v>0.1097137106062473</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.04460870563279939</v>
+        <v>0.04460868006995018</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05377562728051011</v>
+        <v>0.05377553929362369</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05397629777541661</v>
+        <v>0.05397608786585328</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05600592584883882</v>
+        <v>0.05600550891137127</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0604557853805394</v>
+        <v>0.06045468265974492</v>
       </c>
       <c r="J13" t="n">
         <v>0.1223768602826815</v>
@@ -1438,58 +1438,58 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.165064427849061</v>
+        <v>1.165065479002938</v>
       </c>
       <c r="F14" t="n">
-        <v>1.233995260516162</v>
+        <v>1.23399723447861</v>
       </c>
       <c r="G14" t="n">
-        <v>1.351716356217693</v>
+        <v>1.351719470033271</v>
       </c>
       <c r="H14" t="n">
-        <v>1.475537096334</v>
+        <v>1.475541521455663</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5949661322463</v>
+        <v>1.594971863528616</v>
       </c>
       <c r="J14" t="n">
-        <v>1.581193065048008</v>
+        <v>1.581199536815397</v>
       </c>
       <c r="K14" t="n">
-        <v>1.541917806754672</v>
+        <v>1.541924755836406</v>
       </c>
       <c r="L14" t="n">
-        <v>1.48062632357716</v>
+        <v>1.48063351188332</v>
       </c>
       <c r="M14" t="n">
-        <v>1.464223052959003</v>
+        <v>1.464230690334801</v>
       </c>
       <c r="N14" t="n">
-        <v>1.449552808885217</v>
+        <v>1.449560927482969</v>
       </c>
       <c r="O14" t="n">
-        <v>1.398325070537405</v>
+        <v>1.398333474398138</v>
       </c>
       <c r="P14" t="n">
-        <v>1.345117340769091</v>
+        <v>1.345126069036361</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.326142599812843</v>
+        <v>1.326151967847277</v>
       </c>
       <c r="R14" t="n">
-        <v>1.299649228893409</v>
+        <v>1.299659417094647</v>
       </c>
       <c r="S14" t="n">
-        <v>1.283381721601213</v>
+        <v>1.283393125538941</v>
       </c>
       <c r="T14" t="n">
-        <v>1.265700886759106</v>
+        <v>1.265713949511506</v>
       </c>
       <c r="U14" t="n">
-        <v>1.261072905721072</v>
+        <v>1.261088480778287</v>
       </c>
       <c r="V14" t="n">
-        <v>1.246380541192972</v>
+        <v>1.246399773337012</v>
       </c>
     </row>
     <row r="15">
@@ -1514,58 +1514,58 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.7308697354601993</v>
+        <v>0.7308694062286745</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8380339388400087</v>
+        <v>0.8380334850134328</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9421253738262674</v>
+        <v>0.9421248884340951</v>
       </c>
       <c r="H15" t="n">
-        <v>1.028072904071222</v>
+        <v>1.028072388536763</v>
       </c>
       <c r="I15" t="n">
-        <v>1.099002904456506</v>
+        <v>1.099002306243823</v>
       </c>
       <c r="J15" t="n">
-        <v>1.074454811333832</v>
+        <v>1.074454118243006</v>
       </c>
       <c r="K15" t="n">
-        <v>1.035899318742301</v>
+        <v>1.035898510176787</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9870848657064507</v>
+        <v>0.9870839526897153</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9711981379923639</v>
+        <v>0.9711970752382992</v>
       </c>
       <c r="N15" t="n">
-        <v>0.958796700207003</v>
+        <v>0.9587954744295154</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9246660477823944</v>
+        <v>0.9246646590664659</v>
       </c>
       <c r="P15" t="n">
-        <v>0.890798299572202</v>
+        <v>0.8907967148584112</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8801277426306334</v>
+        <v>0.8801258674548357</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8631152727640365</v>
+        <v>0.8631130574668894</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8514604657123145</v>
+        <v>0.8514577835526992</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8376911104589705</v>
+        <v>0.8376878164836514</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8316903010946908</v>
+        <v>0.8316860910353652</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8172870162733763</v>
+        <v>0.8172814386588123</v>
       </c>
     </row>
     <row r="16">
@@ -1590,58 +1590,58 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.120037709222399</v>
+        <v>2.120041889526105</v>
       </c>
       <c r="F16" t="n">
-        <v>1.926652493403777</v>
+        <v>1.926658792433177</v>
       </c>
       <c r="G16" t="n">
-        <v>1.75877225435076</v>
+        <v>1.758779084379055</v>
       </c>
       <c r="H16" t="n">
-        <v>1.659531059422974</v>
+        <v>1.659537682299183</v>
       </c>
       <c r="I16" t="n">
-        <v>1.61662404262849</v>
+        <v>1.616630259513503</v>
       </c>
       <c r="J16" t="n">
-        <v>1.495419980528778</v>
+        <v>1.495425388588398</v>
       </c>
       <c r="K16" t="n">
-        <v>1.398824374371667</v>
+        <v>1.398829262362819</v>
       </c>
       <c r="L16" t="n">
-        <v>1.315236119931722</v>
+        <v>1.31524075783801</v>
       </c>
       <c r="M16" t="n">
-        <v>1.294559986097797</v>
+        <v>1.294564729154794</v>
       </c>
       <c r="N16" t="n">
-        <v>1.287609133646743</v>
+        <v>1.287614315066173</v>
       </c>
       <c r="O16" t="n">
-        <v>1.252396297911863</v>
+        <v>1.252401935910789</v>
       </c>
       <c r="P16" t="n">
-        <v>1.213978471298516</v>
+        <v>1.213984387402249</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.208048815579675</v>
+        <v>1.208055418139103</v>
       </c>
       <c r="R16" t="n">
-        <v>1.202048557223361</v>
+        <v>1.202056257824008</v>
       </c>
       <c r="S16" t="n">
-        <v>1.21487637819098</v>
+        <v>1.214885900914082</v>
       </c>
       <c r="T16" t="n">
-        <v>1.234845376696238</v>
+        <v>1.234857672982759</v>
       </c>
       <c r="U16" t="n">
-        <v>1.272691628716229</v>
+        <v>1.272708289514592</v>
       </c>
       <c r="V16" t="n">
-        <v>1.301882057690786</v>
+        <v>1.301905158700873</v>
       </c>
     </row>
     <row r="17">
@@ -1666,58 +1666,58 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.4928710260883538</v>
+        <v>0.4928699168004058</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5407614972260533</v>
+        <v>0.5407591851220732</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5913322601781766</v>
+        <v>0.5913285825536863</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6336946251957833</v>
+        <v>0.6336896206201714</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6707535925249326</v>
+        <v>0.6707472978227114</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6501119255065195</v>
+        <v>0.650105004222791</v>
       </c>
       <c r="K17" t="n">
-        <v>0.624327166623744</v>
+        <v>0.6243198276497057</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5974106411740527</v>
+        <v>0.5974030891921429</v>
       </c>
       <c r="M17" t="n">
-        <v>0.598227795984422</v>
+        <v>0.5982199368056763</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6078560715426311</v>
+        <v>0.6078479427002031</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6181654949869403</v>
+        <v>0.6181575384163679</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6357421316074021</v>
+        <v>0.6357345632364525</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.670717704773203</v>
+        <v>0.6707103523168699</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6953284893696381</v>
+        <v>0.6953213577023498</v>
       </c>
       <c r="S17" t="n">
-        <v>0.71691146465851</v>
+        <v>0.7169042366114917</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7306230428208607</v>
+        <v>0.7306154749317567</v>
       </c>
       <c r="U17" t="n">
-        <v>0.746510630442981</v>
+        <v>0.7465023381922957</v>
       </c>
       <c r="V17" t="n">
-        <v>0.752341341395802</v>
+        <v>0.7523318203250895</v>
       </c>
     </row>
     <row r="18">
@@ -1742,58 +1742,58 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.7510827918919263</v>
+        <v>0.7510825191254744</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8569114632717942</v>
+        <v>0.8569111146745495</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9219733046644912</v>
+        <v>0.9219727158091671</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9712071619760486</v>
+        <v>0.9712060968885518</v>
       </c>
       <c r="I18" t="n">
-        <v>1.026826156966896</v>
+        <v>1.026824628768417</v>
       </c>
       <c r="J18" t="n">
-        <v>1.022664546389919</v>
+        <v>1.02266311734668</v>
       </c>
       <c r="K18" t="n">
-        <v>1.016908470455215</v>
+        <v>1.016907446863795</v>
       </c>
       <c r="L18" t="n">
-        <v>1.001139557988677</v>
+        <v>1.001138930176274</v>
       </c>
       <c r="M18" t="n">
-        <v>1.006177950449016</v>
+        <v>1.006177635929457</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9976889054462156</v>
+        <v>0.9976885091272264</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9517226575940677</v>
+        <v>0.9517219340585839</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8987117486361186</v>
+        <v>0.8987104376055993</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.8680016351339351</v>
+        <v>0.867999624723359</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8340434088081484</v>
+        <v>0.8340404935087428</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8098089089236687</v>
+        <v>0.8098050470793925</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7894587564767771</v>
+        <v>0.7894538183692213</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7846561220620464</v>
+        <v>0.7846498786669618</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7813441557221501</v>
+        <v>0.7813367341187081</v>
       </c>
     </row>
     <row r="19">
@@ -1818,58 +1818,58 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.4039036119620092</v>
+        <v>0.4039036573903508</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4923281123460528</v>
+        <v>0.4923282312089626</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5310794279239976</v>
+        <v>0.5310796379989103</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5763165214050093</v>
+        <v>0.5763167725417169</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6305974812796656</v>
+        <v>0.6305978236987078</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5911144854548027</v>
+        <v>0.5911148522945828</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5471558776357679</v>
+        <v>0.5471562421998477</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5014990394795725</v>
+        <v>0.5014993805734744</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5025648622211547</v>
+        <v>0.5025652489356222</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5306199643973181</v>
+        <v>0.5306204147014473</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5689198683948752</v>
+        <v>0.568920379528546</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6179476293784856</v>
+        <v>0.6179482377688349</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.7157683729521638</v>
+        <v>0.7157691322588094</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8029166999898625</v>
+        <v>0.802917624878563</v>
       </c>
       <c r="S19" t="n">
-        <v>0.86740960095578</v>
+        <v>0.8674107253608493</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8975154876751446</v>
+        <v>0.8975168128049233</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8895647832266923</v>
+        <v>0.8895663127397007</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8881878832705946</v>
+        <v>0.8881897288753834</v>
       </c>
     </row>
     <row r="20">
@@ -1897,55 +1897,55 @@
         <v>0.8939836798282621</v>
       </c>
       <c r="F20" t="n">
-        <v>1.135857417312452</v>
+        <v>1.135857863374019</v>
       </c>
       <c r="G20" t="n">
-        <v>1.351814061621897</v>
+        <v>1.351814916353799</v>
       </c>
       <c r="H20" t="n">
-        <v>1.585786780706942</v>
+        <v>1.585788016216474</v>
       </c>
       <c r="I20" t="n">
-        <v>1.823278859596366</v>
+        <v>1.823280452783896</v>
       </c>
       <c r="J20" t="n">
-        <v>1.74244338794272</v>
+        <v>1.742445319468583</v>
       </c>
       <c r="K20" t="n">
-        <v>1.600691962005924</v>
+        <v>1.600693839480435</v>
       </c>
       <c r="L20" t="n">
-        <v>1.424302614817482</v>
+        <v>1.424304442466522</v>
       </c>
       <c r="M20" t="n">
-        <v>1.366648328355367</v>
+        <v>1.366650111081676</v>
       </c>
       <c r="N20" t="n">
-        <v>1.372069885358481</v>
+        <v>1.372071974815083</v>
       </c>
       <c r="O20" t="n">
-        <v>1.399233707560688</v>
+        <v>1.399235760496318</v>
       </c>
       <c r="P20" t="n">
-        <v>1.445851796577483</v>
+        <v>1.445854505121857</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.589229917869604</v>
+        <v>1.589232617307446</v>
       </c>
       <c r="R20" t="n">
-        <v>1.683739003413588</v>
+        <v>1.683742385547735</v>
       </c>
       <c r="S20" t="n">
-        <v>1.710689879557622</v>
+        <v>1.710693633038548</v>
       </c>
       <c r="T20" t="n">
-        <v>1.65774397177404</v>
+        <v>1.65774777823686</v>
       </c>
       <c r="U20" t="n">
-        <v>1.536806199756038</v>
+        <v>1.536810081131329</v>
       </c>
       <c r="V20" t="n">
-        <v>1.436497237153051</v>
+        <v>1.436501943260275</v>
       </c>
     </row>
     <row r="21">
@@ -1988,40 +1988,40 @@
         <v>0.09266502394403511</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0893030985416892</v>
+        <v>0.08930272032943799</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08476991718961482</v>
+        <v>0.08476954215956553</v>
       </c>
       <c r="M21" t="n">
-        <v>0.08784971891018123</v>
+        <v>0.08784934541852728</v>
       </c>
       <c r="N21" t="n">
-        <v>0.09611877966850779</v>
+        <v>0.09611840639169353</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1071882202716953</v>
+        <v>0.1071878459222678</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1212725887322089</v>
+        <v>0.1212722124493194</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.145969662666281</v>
+        <v>0.145968903435746</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1687855582430634</v>
+        <v>0.1687847905055436</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1892523155468067</v>
+        <v>0.1892515376366545</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2030934985811524</v>
+        <v>0.2030927085769179</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2070833127448771</v>
+        <v>0.2070825092929261</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2096529501486422</v>
+        <v>0.2096517233905957</v>
       </c>
     </row>
     <row r="22">
@@ -2049,55 +2049,55 @@
         <v>0.06674451532477127</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08557271206740624</v>
+        <v>0.08557267714913246</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09645090239589757</v>
+        <v>0.09645083842341087</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1078608664884299</v>
+        <v>0.1078607481504514</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1207830359606021</v>
+        <v>0.1207828702702658</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1159063472852161</v>
+        <v>0.1159061913169338</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1101089403603883</v>
+        <v>0.1101087674862219</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1035460360710981</v>
+        <v>0.1035458705596227</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1062101963409954</v>
+        <v>0.1062099913802625</v>
       </c>
       <c r="N22" t="n">
-        <v>0.114654237722073</v>
+        <v>0.1146540173923849</v>
       </c>
       <c r="O22" t="n">
-        <v>0.12591242150047</v>
+        <v>0.125912164484854</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1402430378432621</v>
+        <v>0.1402427238625158</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1669803366111812</v>
+        <v>0.1669799667900637</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1929975899632966</v>
+        <v>0.1929971242361569</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2150870445741835</v>
+        <v>0.21508648324203</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2292541933148184</v>
+        <v>0.2292535553739639</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2334415574076536</v>
+        <v>0.2334408210089379</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2384848418439618</v>
+        <v>0.2384839851695717</v>
       </c>
     </row>
     <row r="23">
@@ -2122,58 +2122,58 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.07604156435993636</v>
+        <v>0.07604150658672394</v>
       </c>
       <c r="F23" t="n">
         <v>0.09778481866252937</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1130194727524999</v>
+        <v>0.1130194292574083</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1319437846246526</v>
+        <v>0.1319437083693957</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1545178199114111</v>
+        <v>0.1545177525023913</v>
       </c>
       <c r="J23" t="n">
-        <v>0.153450944817466</v>
+        <v>0.1534508546430506</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1487940479021867</v>
+        <v>0.1487939395482616</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1419557174546379</v>
+        <v>0.1419556187891625</v>
       </c>
       <c r="M23" t="n">
-        <v>0.147568791127723</v>
+        <v>0.1475687002753735</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1611107159823893</v>
+        <v>0.1611106104583983</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1783502038597445</v>
+        <v>0.178350065482221</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1998470422601984</v>
+        <v>0.1998468929420875</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.2379352248842262</v>
+        <v>0.2379350474803685</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2735562619406046</v>
+        <v>0.2735560583714262</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3022129237737524</v>
+        <v>0.3022126953462798</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3192645606679038</v>
+        <v>0.3192642922939579</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3224952978903119</v>
+        <v>0.3224950063104031</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3276807110069987</v>
+        <v>0.3276803963119539</v>
       </c>
     </row>
     <row r="24">
@@ -2204,52 +2204,52 @@
         <v>0.5541063279404799</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6264851245725365</v>
+        <v>0.6264854814985611</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7077976734730173</v>
+        <v>0.7077980128741643</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7960956493365167</v>
+        <v>0.7960962999857183</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7607176399441267</v>
+        <v>0.7607182685815801</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7105897783819299</v>
+        <v>0.710590390147154</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6491450968942041</v>
+        <v>0.6491456952097066</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6409928115126341</v>
+        <v>0.6409933995039118</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6606936640815363</v>
+        <v>0.6606942440973244</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6876092732099028</v>
+        <v>0.6876101356094549</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7210460123384209</v>
+        <v>0.7210468710018484</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.8011230939593282</v>
+        <v>0.8011242385136818</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8557797758256884</v>
+        <v>0.8557806375484791</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8740420802751568</v>
+        <v>0.8740432385381909</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8492234006598911</v>
+        <v>0.8492245721337986</v>
       </c>
       <c r="U24" t="n">
-        <v>0.788227971364468</v>
+        <v>0.78822916035018</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7384036099518473</v>
+        <v>0.7384048188299692</v>
       </c>
     </row>
     <row r="25">
@@ -2289,7 +2289,7 @@
         <v>0.3601898162632126</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3545120450231755</v>
+        <v>0.3545127135782875</v>
       </c>
       <c r="K25" t="n">
         <v>0.3396900681435143</v>
@@ -2307,7 +2307,7 @@
         <v>0.3623800156438989</v>
       </c>
       <c r="P25" t="n">
-        <v>0.387831375147917</v>
+        <v>0.3878320039134366</v>
       </c>
       <c r="Q25" t="n">
         <v>0.4389098365661451</v>
@@ -2350,58 +2350,58 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0690689994210566</v>
+        <v>0.06906896047430908</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08138292877841229</v>
+        <v>0.08138286024075907</v>
       </c>
       <c r="G26" t="n">
-        <v>0.08312529090291232</v>
+        <v>0.08312519943000179</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08543338468930958</v>
+        <v>0.08543324775221178</v>
       </c>
       <c r="I26" t="n">
-        <v>0.08884868537830455</v>
+        <v>0.08884849918708915</v>
       </c>
       <c r="J26" t="n">
-        <v>0.07966300768760165</v>
+        <v>0.0796627920306823</v>
       </c>
       <c r="K26" t="n">
-        <v>0.0712034901885642</v>
+        <v>0.07120326994372116</v>
       </c>
       <c r="L26" t="n">
-        <v>0.06363223309819967</v>
+        <v>0.06363199838832553</v>
       </c>
       <c r="M26" t="n">
-        <v>0.06261791568946481</v>
+        <v>0.06261765786471384</v>
       </c>
       <c r="N26" t="n">
-        <v>0.06522284754745694</v>
+        <v>0.06522255019000267</v>
       </c>
       <c r="O26" t="n">
-        <v>0.06919753957917547</v>
+        <v>0.06919718871106929</v>
       </c>
       <c r="P26" t="n">
-        <v>0.07462987945236244</v>
+        <v>0.07462946238801421</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.086090790310351</v>
+        <v>0.08609025590345357</v>
       </c>
       <c r="R26" t="n">
-        <v>0.09648343680166389</v>
+        <v>0.09648277556614533</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1044531888685831</v>
+        <v>0.1044523984305414</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1086988804455015</v>
+        <v>0.108697949452827</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1087264353539749</v>
+        <v>0.1087253651138327</v>
       </c>
       <c r="V26" t="n">
-        <v>0.1098721237048587</v>
+        <v>0.1098708301283701</v>
       </c>
     </row>
     <row r="27">
@@ -2429,55 +2429,55 @@
         <v>0.09551209777399355</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1171443708890278</v>
+        <v>0.1171443119556397</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1235916493274185</v>
+        <v>0.1235915446902662</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1320463951081465</v>
+        <v>0.1320462547097802</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1443021382700331</v>
+        <v>0.1443019691933903</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1367319381925859</v>
+        <v>0.136731745184348</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1285220741135792</v>
+        <v>0.1285218602154026</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1196512179865992</v>
+        <v>0.1196509854608279</v>
       </c>
       <c r="M27" t="n">
-        <v>0.121491495470512</v>
+        <v>0.1214912458603718</v>
       </c>
       <c r="N27" t="n">
-        <v>0.1294518618186887</v>
+        <v>0.1294515664887993</v>
       </c>
       <c r="O27" t="n">
-        <v>0.1393690085143424</v>
+        <v>0.1393686706882981</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1510787431373982</v>
+        <v>0.1510783385227411</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.1740449267099327</v>
+        <v>0.1740444069775117</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1935827134204456</v>
+        <v>0.1935820847480558</v>
       </c>
       <c r="S27" t="n">
-        <v>0.206679004160973</v>
+        <v>0.2066782469098045</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2106172069870041</v>
+        <v>0.2106162768873332</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2047588440075111</v>
+        <v>0.2047577918383943</v>
       </c>
       <c r="V27" t="n">
-        <v>0.1998255009451361</v>
+        <v>0.1998242115999623</v>
       </c>
     </row>
     <row r="28">
@@ -2505,55 +2505,55 @@
         <v>0.2669370399373532</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3292577307602883</v>
+        <v>0.3292578837234915</v>
       </c>
       <c r="G28" t="n">
-        <v>0.422801362639949</v>
+        <v>0.4228016643759873</v>
       </c>
       <c r="H28" t="n">
-        <v>0.5756634853984064</v>
+        <v>0.5756640106490823</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7864489981962586</v>
+        <v>0.7864497478810161</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8926805593016468</v>
+        <v>0.8926816111289337</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9639685881354946</v>
+        <v>0.9639698722873237</v>
       </c>
       <c r="L28" t="n">
-        <v>1.000712004639003</v>
+        <v>1.000713528621535</v>
       </c>
       <c r="M28" t="n">
-        <v>1.113160625439273</v>
+        <v>1.113162477038244</v>
       </c>
       <c r="N28" t="n">
-        <v>1.287014758803789</v>
+        <v>1.287017186625054</v>
       </c>
       <c r="O28" t="n">
-        <v>1.496766686232662</v>
+        <v>1.496769704532295</v>
       </c>
       <c r="P28" t="n">
-        <v>1.753318810443278</v>
+        <v>1.753322674626885</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.179520843816781</v>
+        <v>2.179526153614911</v>
       </c>
       <c r="R28" t="n">
-        <v>2.60219198045015</v>
+        <v>2.602199026486465</v>
       </c>
       <c r="S28" t="n">
-        <v>2.962800245113491</v>
+        <v>2.96280915527469</v>
       </c>
       <c r="T28" t="n">
-        <v>3.199534262650658</v>
+        <v>3.199545248227192</v>
       </c>
       <c r="U28" t="n">
-        <v>3.285750531092046</v>
+        <v>3.2857637168256</v>
       </c>
       <c r="V28" t="n">
-        <v>3.380646625120306</v>
+        <v>3.380663086885896</v>
       </c>
     </row>
     <row r="29">
@@ -2587,7 +2587,7 @@
         <v>0.1615911997953441</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1839249983863681</v>
+        <v>0.1839250685442795</v>
       </c>
       <c r="I29" t="n">
         <v>0.2096476282162025</v>
@@ -2599,37 +2599,37 @@
         <v>0.206314104762811</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2102196136722991</v>
+        <v>0.2102196657183869</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2259742198234532</v>
+        <v>0.2259742692486383</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2464096064711387</v>
+        <v>0.2464097010341888</v>
       </c>
       <c r="O29" t="n">
-        <v>0.2684815325338412</v>
+        <v>0.2684816235783402</v>
       </c>
       <c r="P29" t="n">
-        <v>0.297517256224945</v>
+        <v>0.2975173885579583</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.3395173402145584</v>
+        <v>0.3395175121019464</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3840511423096951</v>
+        <v>0.3840513529591188</v>
       </c>
       <c r="S29" t="n">
-        <v>0.4304444760271013</v>
+        <v>0.4304447253638655</v>
       </c>
       <c r="T29" t="n">
-        <v>0.4758983737542986</v>
+        <v>0.4758987857436842</v>
       </c>
       <c r="U29" t="n">
-        <v>0.5183654819543834</v>
+        <v>0.5183660564399213</v>
       </c>
       <c r="V29" t="n">
-        <v>0.5570098846517243</v>
+        <v>0.5570106638102986</v>
       </c>
     </row>
     <row r="30">
@@ -2660,52 +2660,52 @@
         <v>0.04866580731316016</v>
       </c>
       <c r="G30" t="n">
-        <v>0.05048780958093217</v>
+        <v>0.05048776855577923</v>
       </c>
       <c r="H30" t="n">
-        <v>0.05542869601222385</v>
+        <v>0.05542865936997314</v>
       </c>
       <c r="I30" t="n">
-        <v>0.06102188419201563</v>
+        <v>0.06102181803265891</v>
       </c>
       <c r="J30" t="n">
-        <v>0.05907316878841527</v>
+        <v>0.05907310842858618</v>
       </c>
       <c r="K30" t="n">
-        <v>0.05783693610160588</v>
+        <v>0.05783688042958757</v>
       </c>
       <c r="L30" t="n">
-        <v>0.05858353938995151</v>
+        <v>0.05858346167346901</v>
       </c>
       <c r="M30" t="n">
-        <v>0.06349270359000203</v>
+        <v>0.06349260630129244</v>
       </c>
       <c r="N30" t="n">
-        <v>0.07082156354121637</v>
+        <v>0.07082147141728296</v>
       </c>
       <c r="O30" t="n">
-        <v>0.07964825870373522</v>
+        <v>0.07964812689137013</v>
       </c>
       <c r="P30" t="n">
-        <v>0.09136864427400315</v>
+        <v>0.09136849680508591</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.108040406010516</v>
+        <v>0.1080402028427238</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1261904499475075</v>
+        <v>0.1261902137607893</v>
       </c>
       <c r="S30" t="n">
-        <v>0.1454584750401325</v>
+        <v>0.1454581877642699</v>
       </c>
       <c r="T30" t="n">
-        <v>0.1647224412466155</v>
+        <v>0.1647221043659916</v>
       </c>
       <c r="U30" t="n">
-        <v>0.1840262352674004</v>
+        <v>0.184025813018093</v>
       </c>
       <c r="V30" t="n">
-        <v>0.2034302449795408</v>
+        <v>0.2034297388757483</v>
       </c>
     </row>
     <row r="31">
@@ -2736,7 +2736,7 @@
         <v>0.01297948532755073</v>
       </c>
       <c r="G31" t="n">
-        <v>0.01460805226145712</v>
+        <v>0.01460787639643423</v>
       </c>
       <c r="H31" t="n">
         <v>0.01683094252195652</v>
@@ -2745,43 +2745,43 @@
         <v>0.01943241206813475</v>
       </c>
       <c r="J31" t="n">
-        <v>0.01951836630656539</v>
+        <v>0.01951821998539422</v>
       </c>
       <c r="K31" t="n">
-        <v>0.01967622308300937</v>
+        <v>0.01967608316817553</v>
       </c>
       <c r="L31" t="n">
-        <v>0.02026627029381992</v>
+        <v>0.02026613541195283</v>
       </c>
       <c r="M31" t="n">
-        <v>0.02203795434921335</v>
+        <v>0.02203782350192614</v>
       </c>
       <c r="N31" t="n">
-        <v>0.02445562543282808</v>
+        <v>0.02445549763712128</v>
       </c>
       <c r="O31" t="n">
-        <v>0.02725847080051673</v>
+        <v>0.02725821954489819</v>
       </c>
       <c r="P31" t="n">
-        <v>0.03098618838224417</v>
+        <v>0.03098581578341078</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.03636238143909583</v>
+        <v>0.03636201102308655</v>
       </c>
       <c r="R31" t="n">
-        <v>0.04223455631715942</v>
+        <v>0.04223418646690808</v>
       </c>
       <c r="S31" t="n">
-        <v>0.04848398190546292</v>
+        <v>0.04848348757322915</v>
       </c>
       <c r="T31" t="n">
-        <v>0.05475410977555235</v>
+        <v>0.0547534880713617</v>
       </c>
       <c r="U31" t="n">
-        <v>0.06072490689999887</v>
+        <v>0.06072402889392557</v>
       </c>
       <c r="V31" t="n">
-        <v>0.06628410215038151</v>
+        <v>0.06628283406478624</v>
       </c>
     </row>
     <row r="32">
@@ -2827,37 +2827,37 @@
         <v>0.2011974617881012</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2168494270937434</v>
+        <v>0.2168494597528619</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2449386431977844</v>
+        <v>0.2449386751636091</v>
       </c>
       <c r="N32" t="n">
-        <v>0.2777630297535885</v>
+        <v>0.2777630926449496</v>
       </c>
       <c r="O32" t="n">
-        <v>0.3112523652651889</v>
+        <v>0.3112524273049316</v>
       </c>
       <c r="P32" t="n">
-        <v>0.3513076401488304</v>
+        <v>0.3513077629867298</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.405382795075175</v>
+        <v>0.4053829780680044</v>
       </c>
       <c r="R32" t="n">
-        <v>0.459601702864126</v>
+        <v>0.459601945939442</v>
       </c>
       <c r="S32" t="n">
-        <v>0.5189380105893491</v>
+        <v>0.5189383445807466</v>
       </c>
       <c r="T32" t="n">
-        <v>0.5774423083527409</v>
+        <v>0.5774428250102344</v>
       </c>
       <c r="U32" t="n">
-        <v>0.6285648643761909</v>
+        <v>0.6285655656604863</v>
       </c>
       <c r="V32" t="n">
-        <v>0.6663515523895094</v>
+        <v>0.666352532336727</v>
       </c>
     </row>
     <row r="33">
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.1018368586923099</v>
+        <v>0.1018368125226808</v>
       </c>
       <c r="F33" t="n">
         <v>0.1114089122192023</v>
@@ -2891,49 +2891,49 @@
         <v>0.127943335457509</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1502081419736567</v>
+        <v>0.1502081053643921</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1760701895281186</v>
+        <v>0.1760701550897499</v>
       </c>
       <c r="J33" t="n">
         <v>0.1782752830124596</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1801451167945343</v>
+        <v>0.1801450855234067</v>
       </c>
       <c r="L33" t="n">
-        <v>0.1849057941094061</v>
+        <v>0.1849057639485613</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1992242813802066</v>
+        <v>0.1992242228398232</v>
       </c>
       <c r="N33" t="n">
-        <v>0.2173002432316351</v>
+        <v>0.217300186041032</v>
       </c>
       <c r="O33" t="n">
-        <v>0.2364087495277036</v>
+        <v>0.2364086933437461</v>
       </c>
       <c r="P33" t="n">
-        <v>0.2605146788919608</v>
+        <v>0.2605145957191509</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2941915249619326</v>
+        <v>0.2941914425648136</v>
       </c>
       <c r="R33" t="n">
-        <v>0.3274517018212751</v>
+        <v>0.3274515924813494</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3661360457237777</v>
+        <v>0.3661359637619391</v>
       </c>
       <c r="T33" t="n">
-        <v>0.4064686625743859</v>
+        <v>0.4064685803156487</v>
       </c>
       <c r="U33" t="n">
-        <v>0.4424064310079538</v>
+        <v>0.4424063758383707</v>
       </c>
       <c r="V33" t="n">
-        <v>0.4693203539734328</v>
+        <v>0.4693203261374547</v>
       </c>
     </row>
     <row r="34">
@@ -2961,55 +2961,55 @@
         <v>0.01112350651284582</v>
       </c>
       <c r="F34" t="n">
-        <v>0.02051570773258468</v>
+        <v>0.02051568441480236</v>
       </c>
       <c r="G34" t="n">
-        <v>0.03824308469869423</v>
+        <v>0.03824304329667702</v>
       </c>
       <c r="H34" t="n">
-        <v>0.06253273392553731</v>
+        <v>0.06253267803380332</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0898740461258689</v>
+        <v>0.0898739696459831</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1018483701307568</v>
+        <v>0.1018482759594875</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1083309854367051</v>
+        <v>0.1083308684683209</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1129897425797203</v>
+        <v>0.1129896053291646</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1212824190729599</v>
+        <v>0.1212822565917022</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1309890647292467</v>
+        <v>0.1309888783114023</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1410023727736929</v>
+        <v>0.1410021454850608</v>
       </c>
       <c r="P34" t="n">
-        <v>0.1543847937605084</v>
+        <v>0.1543845213594321</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.1739881145705243</v>
+        <v>0.1739877756646368</v>
       </c>
       <c r="R34" t="n">
-        <v>0.1935784172399119</v>
+        <v>0.1935780022123735</v>
       </c>
       <c r="S34" t="n">
-        <v>0.2122973046653923</v>
+        <v>0.2122967866883163</v>
       </c>
       <c r="T34" t="n">
-        <v>0.2281574568186391</v>
+        <v>0.2281568257054039</v>
       </c>
       <c r="U34" t="n">
-        <v>0.2401899204949079</v>
+        <v>0.2401891380910632</v>
       </c>
       <c r="V34" t="n">
-        <v>0.2485670202043157</v>
+        <v>0.2485660202818498</v>
       </c>
     </row>
     <row r="35">
@@ -3043,49 +3043,49 @@
         <v>0.5450727421962086</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6968053340429777</v>
+        <v>0.6968054985155528</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8314665395554517</v>
+        <v>0.8314669961330917</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8230850427405728</v>
+        <v>0.8230854693428661</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8000737883282283</v>
+        <v>0.8000741912495691</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7874083846360624</v>
+        <v>0.787408895927094</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8150823772966446</v>
+        <v>0.8150828674043114</v>
       </c>
       <c r="N35" t="n">
-        <v>0.8562588519226371</v>
+        <v>0.8562595616141129</v>
       </c>
       <c r="O35" t="n">
-        <v>0.8981299735296836</v>
+        <v>0.8981307781684491</v>
       </c>
       <c r="P35" t="n">
-        <v>0.9552587226765552</v>
+        <v>0.955259621307805</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.042958529491695</v>
+        <v>1.042959632873859</v>
       </c>
       <c r="R35" t="n">
-        <v>1.124863913213238</v>
+        <v>1.124865221608984</v>
       </c>
       <c r="S35" t="n">
-        <v>1.218475895633959</v>
+        <v>1.218477628907625</v>
       </c>
       <c r="T35" t="n">
-        <v>1.311441252433141</v>
+        <v>1.311443416427094</v>
       </c>
       <c r="U35" t="n">
-        <v>1.387046532670394</v>
+        <v>1.387049353812073</v>
       </c>
       <c r="V35" t="n">
-        <v>1.43367022238392</v>
+        <v>1.433673937067792</v>
       </c>
     </row>
     <row r="36">
@@ -3128,7 +3128,7 @@
         <v>0.4706467348654464</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4484810812034343</v>
+        <v>0.4484828223839199</v>
       </c>
       <c r="L36" t="n">
         <v>0.4393675594199662</v>
@@ -3146,7 +3146,7 @@
         <v>0.5361213666197844</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.5936217950505337</v>
+        <v>0.5936236539351658</v>
       </c>
       <c r="R36" t="n">
         <v>0.648755382639571</v>
@@ -3161,7 +3161,7 @@
         <v>0.7714420395331133</v>
       </c>
       <c r="V36" t="n">
-        <v>0.803915753183341</v>
+        <v>0.8039177437044793</v>
       </c>
     </row>
     <row r="37">
@@ -3192,52 +3192,52 @@
         <v>0.9340171427889399</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9589572298647679</v>
+        <v>0.9589577626732494</v>
       </c>
       <c r="H37" t="n">
         <v>1.030226440970794</v>
       </c>
       <c r="I37" t="n">
-        <v>1.129669264356274</v>
+        <v>1.129669746183208</v>
       </c>
       <c r="J37" t="n">
-        <v>1.085665327214359</v>
+        <v>1.085665790585776</v>
       </c>
       <c r="K37" t="n">
-        <v>1.046944270726317</v>
+        <v>1.046945167979198</v>
       </c>
       <c r="L37" t="n">
-        <v>1.027200541370422</v>
+        <v>1.027201415676661</v>
       </c>
       <c r="M37" t="n">
-        <v>1.057017006957041</v>
+        <v>1.057017862997563</v>
       </c>
       <c r="N37" t="n">
-        <v>1.099885915392161</v>
+        <v>1.099886757344986</v>
       </c>
       <c r="O37" t="n">
-        <v>1.143956723879062</v>
+        <v>1.143957972997393</v>
       </c>
       <c r="P37" t="n">
-        <v>1.209094157310721</v>
+        <v>1.209095399387822</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.336219238892236</v>
+        <v>1.336220894050039</v>
       </c>
       <c r="R37" t="n">
-        <v>1.468450346978124</v>
+        <v>1.468452006961972</v>
       </c>
       <c r="S37" t="n">
-        <v>1.589790330047178</v>
+        <v>1.589792836861535</v>
       </c>
       <c r="T37" t="n">
-        <v>1.683390327431941</v>
+        <v>1.683393281222836</v>
       </c>
       <c r="U37" t="n">
-        <v>1.749981292938052</v>
+        <v>1.749985141247939</v>
       </c>
       <c r="V37" t="n">
-        <v>1.794342005337731</v>
+        <v>1.794346778918133</v>
       </c>
     </row>
     <row r="38">
@@ -3268,52 +3268,52 @@
         <v>0.1527279376342567</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1673061508689085</v>
+        <v>0.1673061811160091</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1888522851878858</v>
+        <v>0.1888523130186968</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2165968502376975</v>
+        <v>0.2165968760351216</v>
       </c>
       <c r="J38" t="n">
-        <v>0.2189834491326975</v>
+        <v>0.2189834732291179</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2237889593211267</v>
+        <v>0.2237889820192375</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2339796055004902</v>
+        <v>0.233979648626031</v>
       </c>
       <c r="M38" t="n">
-        <v>0.257536465837442</v>
+        <v>0.2575365277979723</v>
       </c>
       <c r="N38" t="n">
-        <v>0.2866897706001452</v>
+        <v>0.2866898302899492</v>
       </c>
       <c r="O38" t="n">
-        <v>0.3177171167614362</v>
+        <v>0.3177172130555569</v>
       </c>
       <c r="P38" t="n">
-        <v>0.3563500226172091</v>
+        <v>0.3563501537314649</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.409524143188621</v>
+        <v>0.4095243261379954</v>
       </c>
       <c r="R38" t="n">
-        <v>0.4630544664868244</v>
+        <v>0.4630547179139878</v>
       </c>
       <c r="S38" t="n">
-        <v>0.5143973725817391</v>
+        <v>0.5143977089399953</v>
       </c>
       <c r="T38" t="n">
-        <v>0.5594603051450655</v>
+        <v>0.5594607784447407</v>
       </c>
       <c r="U38" t="n">
-        <v>0.5951340394060347</v>
+        <v>0.5951346666132379</v>
       </c>
       <c r="V38" t="n">
-        <v>0.6209809378316669</v>
+        <v>0.6209817885655464</v>
       </c>
     </row>
     <row r="39">
@@ -3362,34 +3362,34 @@
         <v>0.1324853017841996</v>
       </c>
       <c r="M39" t="n">
-        <v>0.1458667477649817</v>
+        <v>0.1458666842746515</v>
       </c>
       <c r="N39" t="n">
-        <v>0.1612118074836783</v>
+        <v>0.1612117447379897</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1762210282244923</v>
+        <v>0.1762209661448876</v>
       </c>
       <c r="P39" t="n">
-        <v>0.1948197592688861</v>
+        <v>0.194819697748029</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.2214012815058212</v>
+        <v>0.2214011594227669</v>
       </c>
       <c r="R39" t="n">
-        <v>0.2490705739636851</v>
+        <v>0.2490705132486318</v>
       </c>
       <c r="S39" t="n">
-        <v>0.2771927659234629</v>
+        <v>0.2771926449199077</v>
       </c>
       <c r="T39" t="n">
-        <v>0.3063153132529466</v>
+        <v>0.3063152528511174</v>
       </c>
       <c r="U39" t="n">
-        <v>0.3344870577131733</v>
+        <v>0.3344869370222904</v>
       </c>
       <c r="V39" t="n">
-        <v>0.3602805508700552</v>
+        <v>0.3602804905417243</v>
       </c>
     </row>
     <row r="40">
@@ -3453,19 +3453,19 @@
         <v>0.1623529846677079</v>
       </c>
       <c r="R40" t="n">
-        <v>0.1875918834390838</v>
+        <v>0.1875915147994084</v>
       </c>
       <c r="S40" t="n">
-        <v>0.2146602197503378</v>
+        <v>0.2146598502854301</v>
       </c>
       <c r="T40" t="n">
-        <v>0.2412412735833291</v>
+        <v>0.2412409022069413</v>
       </c>
       <c r="U40" t="n">
-        <v>0.2656199908350401</v>
+        <v>0.2656196167550431</v>
       </c>
       <c r="V40" t="n">
-        <v>0.2871534935701395</v>
+        <v>0.2871531160093333</v>
       </c>
     </row>
     <row r="41">
@@ -3496,7 +3496,7 @@
         <v>0.07396903500440559</v>
       </c>
       <c r="G41" t="n">
-        <v>0.08523294145103416</v>
+        <v>0.08523252470275429</v>
       </c>
       <c r="H41" t="n">
         <v>0.09813103691912281</v>
@@ -3508,7 +3508,7 @@
         <v>0.1107695151046742</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1094555736910561</v>
+        <v>0.1094552549029609</v>
       </c>
       <c r="L41" t="n">
         <v>0.1100716879168098</v>
@@ -3520,28 +3520,28 @@
         <v>0.1239012450354256</v>
       </c>
       <c r="O41" t="n">
-        <v>0.1310201172068888</v>
+        <v>0.1310198367807982</v>
       </c>
       <c r="P41" t="n">
-        <v>0.140544641942248</v>
+        <v>0.1405443672285203</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.1555573933849493</v>
+        <v>0.1555568528468923</v>
       </c>
       <c r="R41" t="n">
-        <v>0.1704647399004295</v>
+        <v>0.1704644731412152</v>
       </c>
       <c r="S41" t="n">
-        <v>0.1845294694700143</v>
+        <v>0.1845289410615884</v>
       </c>
       <c r="T41" t="n">
-        <v>0.1960555165449939</v>
+        <v>0.1960549921311706</v>
       </c>
       <c r="U41" t="n">
-        <v>0.2043015355654007</v>
+        <v>0.2043010135217145</v>
       </c>
       <c r="V41" t="n">
-        <v>0.20914068752501</v>
+        <v>0.209139905962385</v>
       </c>
     </row>
     <row r="42">
@@ -3569,55 +3569,55 @@
         <v>1.626524621152847</v>
       </c>
       <c r="F42" t="n">
-        <v>1.635936471718906</v>
+        <v>1.635937581499513</v>
       </c>
       <c r="G42" t="n">
-        <v>1.696388244941335</v>
+        <v>1.696389243739781</v>
       </c>
       <c r="H42" t="n">
         <v>1.80418316617377</v>
       </c>
       <c r="I42" t="n">
-        <v>1.929321728439436</v>
+        <v>1.929323408036199</v>
       </c>
       <c r="J42" t="n">
-        <v>1.803304211154544</v>
+        <v>1.803304992328868</v>
       </c>
       <c r="K42" t="n">
-        <v>1.69517216007692</v>
+        <v>1.695172892922471</v>
       </c>
       <c r="L42" t="n">
-        <v>1.622293296002273</v>
+        <v>1.622293989029381</v>
       </c>
       <c r="M42" t="n">
-        <v>1.629432165669795</v>
+        <v>1.629432825267335</v>
       </c>
       <c r="N42" t="n">
-        <v>1.662620468322083</v>
+        <v>1.662622363595587</v>
       </c>
       <c r="O42" t="n">
-        <v>1.698690618781932</v>
+        <v>1.698692446505575</v>
       </c>
       <c r="P42" t="n">
-        <v>1.766250470573472</v>
+        <v>1.766252246322424</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.889555918197285</v>
+        <v>1.889558232931727</v>
       </c>
       <c r="R42" t="n">
-        <v>1.997014687555128</v>
+        <v>1.997016963813187</v>
       </c>
       <c r="S42" t="n">
-        <v>2.084952201189156</v>
+        <v>2.084955016693123</v>
       </c>
       <c r="T42" t="n">
-        <v>2.142239087823436</v>
+        <v>2.142243009187756</v>
       </c>
       <c r="U42" t="n">
-        <v>2.166910318676642</v>
+        <v>2.166914804789599</v>
       </c>
       <c r="V42" t="n">
-        <v>2.16151644296002</v>
+        <v>2.161522080965137</v>
       </c>
     </row>
     <row r="43">
@@ -3657,43 +3657,43 @@
         <v>0.1889261299845144</v>
       </c>
       <c r="J43" t="n">
-        <v>0.2083071934619466</v>
+        <v>0.208307299919933</v>
       </c>
       <c r="K43" t="n">
-        <v>0.2265389642390349</v>
+        <v>0.2265390616325886</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2457916048439001</v>
+        <v>0.2457916949864516</v>
       </c>
       <c r="M43" t="n">
-        <v>0.2760991950318106</v>
+        <v>0.2760992794100275</v>
       </c>
       <c r="N43" t="n">
-        <v>0.3113602330876382</v>
+        <v>0.3113603127811688</v>
       </c>
       <c r="O43" t="n">
-        <v>0.3487352775644779</v>
+        <v>0.3487354294694037</v>
       </c>
       <c r="P43" t="n">
-        <v>0.3949109624758435</v>
+        <v>0.3949111815822109</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.4579168243704524</v>
+        <v>0.4579171073529464</v>
       </c>
       <c r="R43" t="n">
-        <v>0.5238243652473575</v>
+        <v>0.5238247796105676</v>
       </c>
       <c r="S43" t="n">
-        <v>0.591475913603201</v>
+        <v>0.5914765252090333</v>
       </c>
       <c r="T43" t="n">
-        <v>0.6597543332657883</v>
+        <v>0.659755073793596</v>
       </c>
       <c r="U43" t="n">
-        <v>0.7272217839265991</v>
+        <v>0.7272228582171477</v>
       </c>
       <c r="V43" t="n">
-        <v>0.7921797303963299</v>
+        <v>0.7921812782183089</v>
       </c>
     </row>
     <row r="44">
@@ -3724,52 +3724,52 @@
         <v>0.0541310523105236</v>
       </c>
       <c r="G44" t="n">
-        <v>0.06542868801930941</v>
+        <v>0.06542864460786442</v>
       </c>
       <c r="H44" t="n">
-        <v>0.08127887320884285</v>
+        <v>0.08127883442031714</v>
       </c>
       <c r="I44" t="n">
-        <v>0.09989482343180929</v>
+        <v>0.09989478833785929</v>
       </c>
       <c r="J44" t="n">
-        <v>0.1040746702590591</v>
+        <v>0.1040746059867708</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1065995436875036</v>
+        <v>0.1065994544361352</v>
       </c>
       <c r="L44" t="n">
-        <v>0.1099575051099688</v>
+        <v>0.1099574215682452</v>
       </c>
       <c r="M44" t="n">
-        <v>0.1182513673278882</v>
+        <v>0.1182512620881046</v>
       </c>
       <c r="N44" t="n">
-        <v>0.1280680435291218</v>
+        <v>0.1280678930724481</v>
       </c>
       <c r="O44" t="n">
-        <v>0.1377319577214857</v>
+        <v>0.1377317893616806</v>
       </c>
       <c r="P44" t="n">
-        <v>0.1499769605932224</v>
+        <v>0.1499767750720808</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.1680973997410204</v>
+        <v>0.1680971747369984</v>
       </c>
       <c r="R44" t="n">
-        <v>0.1865428435973791</v>
+        <v>0.1865425581322323</v>
       </c>
       <c r="S44" t="n">
-        <v>0.2050042478743946</v>
+        <v>0.2050039034812337</v>
       </c>
       <c r="T44" t="n">
-        <v>0.22228622092841</v>
+        <v>0.2222857973141159</v>
       </c>
       <c r="U44" t="n">
-        <v>0.2377297767268474</v>
+        <v>0.2377292532160837</v>
       </c>
       <c r="V44" t="n">
-        <v>0.2511082228115609</v>
+        <v>0.2511075788643222</v>
       </c>
     </row>
     <row r="45">
@@ -3812,40 +3812,40 @@
         <v>0.3027313587162075</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3059198820852447</v>
+        <v>0.3059200483684623</v>
       </c>
       <c r="L45" t="n">
-        <v>0.316102060596087</v>
+        <v>0.3161022200577953</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3418647563025443</v>
+        <v>0.3418649101854643</v>
       </c>
       <c r="N45" t="n">
-        <v>0.3737569301517112</v>
+        <v>0.3737570793797842</v>
       </c>
       <c r="O45" t="n">
-        <v>0.4083119449197425</v>
+        <v>0.4083120904191547</v>
       </c>
       <c r="P45" t="n">
-        <v>0.4535835263317174</v>
+        <v>0.4535838114281177</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.5175861646343225</v>
+        <v>0.5175864450930521</v>
       </c>
       <c r="R45" t="n">
-        <v>0.5814344427550027</v>
+        <v>0.5814348583050517</v>
       </c>
       <c r="S45" t="n">
-        <v>0.6417825898412329</v>
+        <v>0.6417831392889899</v>
       </c>
       <c r="T45" t="n">
-        <v>0.6927684636612826</v>
+        <v>0.6927692834456302</v>
       </c>
       <c r="U45" t="n">
-        <v>0.7311886502659565</v>
+        <v>0.731189468614755</v>
       </c>
       <c r="V45" t="n">
-        <v>0.7567641572796479</v>
+        <v>0.7567653863939235</v>
       </c>
     </row>
     <row r="46">
@@ -3879,49 +3879,49 @@
         <v>0.03858074629659079</v>
       </c>
       <c r="H46" t="n">
-        <v>0.04687574309410887</v>
+        <v>0.04687570955530565</v>
       </c>
       <c r="I46" t="n">
-        <v>0.05578141979642386</v>
+        <v>0.05578136187013853</v>
       </c>
       <c r="J46" t="n">
-        <v>0.05699452302870742</v>
+        <v>0.05699447262635806</v>
       </c>
       <c r="K46" t="n">
-        <v>0.05790850673973252</v>
+        <v>0.05790841823227146</v>
       </c>
       <c r="L46" t="n">
-        <v>0.05986462220002764</v>
+        <v>0.05986454368145329</v>
       </c>
       <c r="M46" t="n">
-        <v>0.06523781996888701</v>
+        <v>0.06523771390185264</v>
       </c>
       <c r="N46" t="n">
-        <v>0.07193854091833615</v>
+        <v>0.07193841194216191</v>
       </c>
       <c r="O46" t="n">
-        <v>0.07891330472459318</v>
+        <v>0.07891314164706524</v>
       </c>
       <c r="P46" t="n">
-        <v>0.08788430109488649</v>
+        <v>0.08788412249715891</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.1010033619072564</v>
+        <v>0.1010031437432554</v>
       </c>
       <c r="R46" t="n">
-        <v>0.1152013930687187</v>
+        <v>0.1152011148613995</v>
       </c>
       <c r="S46" t="n">
-        <v>0.130099619027356</v>
+        <v>0.1300992743804915</v>
       </c>
       <c r="T46" t="n">
-        <v>0.144655210738472</v>
+        <v>0.1446548043908388</v>
       </c>
       <c r="U46" t="n">
-        <v>0.1579901723404986</v>
+        <v>0.1579896653790197</v>
       </c>
       <c r="V46" t="n">
-        <v>0.1699129189050281</v>
+        <v>0.1699122856473997</v>
       </c>
     </row>
     <row r="47">
@@ -3946,58 +3946,58 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.1580323892344546</v>
+        <v>0.1580323948261324</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1970267718160802</v>
+        <v>0.1970267817402052</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2346624712972261</v>
+        <v>0.2346624889842811</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2770911016831787</v>
+        <v>0.2770911333382399</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3247268642769248</v>
+        <v>0.3247269069788462</v>
       </c>
       <c r="J47" t="n">
-        <v>0.3309591924839765</v>
+        <v>0.3309592439935781</v>
       </c>
       <c r="K47" t="n">
-        <v>0.3377173325167855</v>
+        <v>0.337717394109828</v>
       </c>
       <c r="L47" t="n">
-        <v>0.3493178654542031</v>
+        <v>0.3493179327136496</v>
       </c>
       <c r="M47" t="n">
-        <v>0.3776347937861709</v>
+        <v>0.3776348737183685</v>
       </c>
       <c r="N47" t="n">
-        <v>0.4083579346413059</v>
+        <v>0.4083580329123899</v>
       </c>
       <c r="O47" t="n">
-        <v>0.4341918243765416</v>
+        <v>0.4341919390639391</v>
       </c>
       <c r="P47" t="n">
-        <v>0.4624024521440255</v>
+        <v>0.4624025839527297</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.5014621256828876</v>
+        <v>0.5014622795111537</v>
       </c>
       <c r="R47" t="n">
-        <v>0.5331462656320051</v>
+        <v>0.533146444039585</v>
       </c>
       <c r="S47" t="n">
-        <v>0.5569470322331777</v>
+        <v>0.5569472378893524</v>
       </c>
       <c r="T47" t="n">
-        <v>0.5701034253681578</v>
+        <v>0.570103655686137</v>
       </c>
       <c r="U47" t="n">
-        <v>0.5720422611331074</v>
+        <v>0.5720425173207405</v>
       </c>
       <c r="V47" t="n">
-        <v>0.565077770527834</v>
+        <v>0.5650780607163708</v>
       </c>
     </row>
     <row r="48">
@@ -4031,49 +4031,49 @@
         <v>0.1931867258434137</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2183859024704097</v>
+        <v>0.2183859556879134</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2453630925314609</v>
+        <v>0.2453631417429937</v>
       </c>
       <c r="J48" t="n">
-        <v>0.2389768639280587</v>
+        <v>0.2389769098840255</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2339059687821972</v>
+        <v>0.2339060121089651</v>
       </c>
       <c r="L48" t="n">
-        <v>0.234917122196671</v>
+        <v>0.2349171634304347</v>
       </c>
       <c r="M48" t="n">
-        <v>0.2494972254439527</v>
+        <v>0.2494972650013529</v>
       </c>
       <c r="N48" t="n">
-        <v>0.2692021221564695</v>
+        <v>0.2692021603329909</v>
       </c>
       <c r="O48" t="n">
-        <v>0.2902230221462861</v>
+        <v>0.2902230960460661</v>
       </c>
       <c r="P48" t="n">
-        <v>0.3184460807725389</v>
+        <v>0.3184461525378176</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.3604822464969303</v>
+        <v>0.3604823514106702</v>
       </c>
       <c r="R48" t="n">
-        <v>0.404176290341265</v>
+        <v>0.4041764612010004</v>
       </c>
       <c r="S48" t="n">
-        <v>0.4487570496938935</v>
+        <v>0.4487573176794062</v>
       </c>
       <c r="T48" t="n">
-        <v>0.4907608394925102</v>
+        <v>0.4907611688602558</v>
       </c>
       <c r="U48" t="n">
-        <v>0.5273272771918975</v>
+        <v>0.5273277644029326</v>
       </c>
       <c r="V48" t="n">
-        <v>0.5569570924696332</v>
+        <v>0.5569577345240018</v>
       </c>
     </row>
     <row r="49">
@@ -4107,49 +4107,49 @@
         <v>0.04924732101838695</v>
       </c>
       <c r="H49" t="n">
-        <v>0.05624574099249181</v>
+        <v>0.05624562677170714</v>
       </c>
       <c r="I49" t="n">
-        <v>0.06352089418997474</v>
+        <v>0.06352078836767408</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0624419702203575</v>
+        <v>0.06244187138317693</v>
       </c>
       <c r="K49" t="n">
-        <v>0.06191557394919306</v>
+        <v>0.06191548078016021</v>
       </c>
       <c r="L49" t="n">
-        <v>0.06314824945052898</v>
+        <v>0.06314816079042258</v>
       </c>
       <c r="M49" t="n">
-        <v>0.06816424862053636</v>
+        <v>0.06816407860498844</v>
       </c>
       <c r="N49" t="n">
-        <v>0.07489675900760748</v>
+        <v>0.07489659503541389</v>
       </c>
       <c r="O49" t="n">
-        <v>0.08242678090859928</v>
+        <v>0.08242662161979196</v>
       </c>
       <c r="P49" t="n">
-        <v>0.0922395326420421</v>
+        <v>0.09223929886955416</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.1061744832611113</v>
+        <v>0.1061741764773555</v>
       </c>
       <c r="R49" t="n">
-        <v>0.1214489790031865</v>
+        <v>0.1214486753835854</v>
       </c>
       <c r="S49" t="n">
-        <v>0.1380416245602428</v>
+        <v>0.1380411713969363</v>
       </c>
       <c r="T49" t="n">
-        <v>0.1549042296555951</v>
+        <v>0.1549037012883104</v>
       </c>
       <c r="U49" t="n">
-        <v>0.1707248186534379</v>
+        <v>0.1707241375395897</v>
       </c>
       <c r="V49" t="n">
-        <v>0.1848437660465488</v>
+        <v>0.1848429292487458</v>
       </c>
     </row>
     <row r="50">
@@ -4256,52 +4256,52 @@
         <v>0.03055320062537159</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0322214205905046</v>
+        <v>0.03222135950087328</v>
       </c>
       <c r="H51" t="n">
-        <v>0.03496769584905082</v>
+        <v>0.03496758628774524</v>
       </c>
       <c r="I51" t="n">
-        <v>0.03856085416396486</v>
+        <v>0.03856080447553615</v>
       </c>
       <c r="J51" t="n">
-        <v>0.03744652982988579</v>
+        <v>0.03744639291704222</v>
       </c>
       <c r="K51" t="n">
-        <v>0.03668676757057932</v>
+        <v>0.03668664055510841</v>
       </c>
       <c r="L51" t="n">
-        <v>0.03686558033347571</v>
+        <v>0.03686542184494909</v>
       </c>
       <c r="M51" t="n">
-        <v>0.03925755563885412</v>
+        <v>0.03925736877766247</v>
       </c>
       <c r="N51" t="n">
-        <v>0.0427182808670207</v>
+        <v>0.04271810304726165</v>
       </c>
       <c r="O51" t="n">
-        <v>0.04668923620586148</v>
+        <v>0.04668899743491787</v>
       </c>
       <c r="P51" t="n">
-        <v>0.05196783042213524</v>
+        <v>0.05196753433463546</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.05961478584465296</v>
+        <v>0.05961443528492062</v>
       </c>
       <c r="R51" t="n">
-        <v>0.06768356638471144</v>
+        <v>0.06768313168391289</v>
       </c>
       <c r="S51" t="n">
-        <v>0.07593823792906401</v>
+        <v>0.0759376607248045</v>
       </c>
       <c r="T51" t="n">
-        <v>0.08391508680231471</v>
+        <v>0.08391439985066268</v>
       </c>
       <c r="U51" t="n">
-        <v>0.09123631028371725</v>
+        <v>0.09123542536346625</v>
       </c>
       <c r="V51" t="n">
-        <v>0.09775660520368872</v>
+        <v>0.09775546476210974</v>
       </c>
     </row>
     <row r="52">
@@ -4332,7 +4332,7 @@
         <v>0.05282377992842298</v>
       </c>
       <c r="G52" t="n">
-        <v>0.05220619657645623</v>
+        <v>0.05220606980577083</v>
       </c>
       <c r="H52" t="n">
         <v>0.05529000463174334</v>
@@ -4344,40 +4344,40 @@
         <v>0.06099340096773485</v>
       </c>
       <c r="K52" t="n">
-        <v>0.06246498830031977</v>
+        <v>0.06246488790834936</v>
       </c>
       <c r="L52" t="n">
-        <v>0.06512863126669792</v>
+        <v>0.06512853464227222</v>
       </c>
       <c r="M52" t="n">
-        <v>0.07066170785178973</v>
+        <v>0.07066161424214569</v>
       </c>
       <c r="N52" t="n">
-        <v>0.07724413559458161</v>
+        <v>0.07724404432689166</v>
       </c>
       <c r="O52" t="n">
-        <v>0.08429313514374652</v>
+        <v>0.08429304564339121</v>
       </c>
       <c r="P52" t="n">
-        <v>0.09377428954995864</v>
+        <v>0.09377411313924627</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.1080759134289895</v>
+        <v>0.1080757387145384</v>
       </c>
       <c r="R52" t="n">
-        <v>0.1240402974684589</v>
+        <v>0.1240401236526012</v>
       </c>
       <c r="S52" t="n">
-        <v>0.1416619256093415</v>
+        <v>0.1416617521560247</v>
       </c>
       <c r="T52" t="n">
-        <v>0.1603964529085248</v>
+        <v>0.160396192552427</v>
       </c>
       <c r="U52" t="n">
-        <v>0.179908763271252</v>
+        <v>0.1799085020475584</v>
       </c>
       <c r="V52" t="n">
-        <v>0.2002382566619892</v>
+        <v>0.200237906284545</v>
       </c>
     </row>
     <row r="53">
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2.5800013421779</v>
+        <v>2.580001507878874</v>
       </c>
       <c r="F54" t="n">
-        <v>2.261945373316966</v>
+        <v>2.26194548875797</v>
       </c>
       <c r="G54" t="n">
-        <v>2.053988494823246</v>
+        <v>2.053988602657319</v>
       </c>
       <c r="H54" t="n">
-        <v>1.885305991972817</v>
+        <v>1.885306059627123</v>
       </c>
       <c r="I54" t="n">
-        <v>1.746191232870395</v>
+        <v>1.746191264894334</v>
       </c>
       <c r="J54" t="n">
         <v>1.577266197735202</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>12.9850516760564</v>
+        <v>12.98505080864463</v>
       </c>
       <c r="F55" t="n">
-        <v>13.61705400152117</v>
+        <v>13.61705338315954</v>
       </c>
       <c r="G55" t="n">
-        <v>13.9170327141592</v>
+        <v>13.91703212336298</v>
       </c>
       <c r="H55" t="n">
-        <v>13.64962632366392</v>
+        <v>13.64962594484512</v>
       </c>
       <c r="I55" t="n">
-        <v>13.00119394557359</v>
+        <v>13.00119376248118</v>
       </c>
       <c r="J55" t="n">
         <v>11.71984485810645</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.2384979221347332</v>
+        <v>0.3688675634295713</v>
       </c>
       <c r="F58" t="n">
-        <v>0.156199652992936</v>
+        <v>0.2463930887759739</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1253307673803223</v>
+        <v>0.1948913315626948</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1043376153683568</v>
+        <v>0.1567530119067189</v>
       </c>
       <c r="I58" t="n">
-        <v>0.08131643989570873</v>
+        <v>0.1125721638178023</v>
       </c>
       <c r="J58" t="n">
         <v>0.04621269715379914</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.2048340289264712</v>
+        <v>0.2125483432325361</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2153179824561404</v>
+        <v>0.2198026315789474</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2261996773540961</v>
+        <v>0.2299578277942328</v>
       </c>
       <c r="H59" t="n">
-        <v>0.244288421094401</v>
+        <v>0.2466965596603309</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2668581582843244</v>
+        <v>0.2677956859378027</v>
       </c>
       <c r="J59" t="n">
         <v>0.2704960871898149</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.223787422600479</v>
+        <v>0.3316739310804593</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1572404239207284</v>
+        <v>0.2182445260320776</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1524361965510106</v>
+        <v>0.1905862711102549</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1624843720502801</v>
+        <v>0.1871328990158399</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1717682456190504</v>
+        <v>0.1851862439610074</v>
       </c>
       <c r="J60" t="n">
         <v>0.1597918801506776</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.2035276168690551</v>
+        <v>0.2568113878718924</v>
       </c>
       <c r="F61" t="n">
-        <v>0.1813677466062805</v>
+        <v>0.2173114524116991</v>
       </c>
       <c r="G61" t="n">
-        <v>0.1873960425987126</v>
+        <v>0.2127477505239053</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2026625041493769</v>
+        <v>0.2198163073811028</v>
       </c>
       <c r="I61" t="n">
-        <v>0.2204814852500129</v>
+        <v>0.229655082543551</v>
       </c>
       <c r="J61" t="n">
         <v>0.2184339245113266</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.2612692991321925</v>
+        <v>0.3646248928756857</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2015990493943227</v>
+        <v>0.2840128443644854</v>
       </c>
       <c r="G62" t="n">
-        <v>0.1770520132753088</v>
+        <v>0.2442100019048457</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1611526942608396</v>
+        <v>0.2124418757953654</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1445414872341427</v>
+        <v>0.1749853202492146</v>
       </c>
       <c r="J62" t="n">
         <v>0.1121975473641921</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.2622144945937752</v>
+        <v>0.3454501132375289</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2173998225171835</v>
+        <v>0.2779810154836587</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2122254111264501</v>
+        <v>0.2564970607875498</v>
       </c>
       <c r="H63" t="n">
-        <v>0.2193361486627186</v>
+        <v>0.250431295134811</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2235494409423457</v>
+        <v>0.2415002328902364</v>
       </c>
       <c r="J63" t="n">
         <v>0.2011802002969404</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.1765870606804958</v>
+        <v>0.2088466316113908</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1777664168271908</v>
+        <v>0.196079863425144</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1917243608738989</v>
+        <v>0.2042150444941318</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2057323315207267</v>
+        <v>0.2145144550204473</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2182547343664988</v>
+        <v>0.2232392017831757</v>
       </c>
       <c r="J64" t="n">
         <v>0.2135870840976865</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.3085236999476483</v>
+        <v>0.3185557802378158</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3157923570313803</v>
+        <v>0.3233179322305778</v>
       </c>
       <c r="G65" t="n">
-        <v>0.3357712598506095</v>
+        <v>0.3414318072012388</v>
       </c>
       <c r="H65" t="n">
-        <v>0.361323664711081</v>
+        <v>0.3650764482224005</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3869876577535381</v>
+        <v>0.3888661078929247</v>
       </c>
       <c r="J65" t="n">
         <v>0.3790649540656524</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.6254580832606821</v>
+        <v>0.597603964143395</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6710060809398702</v>
+        <v>0.6515477457155231</v>
       </c>
       <c r="G66" t="n">
-        <v>0.7237330924976898</v>
+        <v>0.7084803200873729</v>
       </c>
       <c r="H66" t="n">
-        <v>0.7825193313057824</v>
+        <v>0.7702605005267656</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8423728508331281</v>
+        <v>0.8343756753170437</v>
       </c>
       <c r="J66" t="n">
         <v>0.8324477423664766</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2.375442139241657</v>
+        <v>2.02371336344073</v>
       </c>
       <c r="F67" t="n">
-        <v>2.498934661016183</v>
+        <v>2.267757456921089</v>
       </c>
       <c r="G67" t="n">
-        <v>2.41927899359885</v>
+        <v>2.261894921105736</v>
       </c>
       <c r="H67" t="n">
-        <v>2.318854625846796</v>
+        <v>2.213657301982902</v>
       </c>
       <c r="I67" t="n">
-        <v>2.23865701122392</v>
+        <v>2.18163882660657</v>
       </c>
       <c r="J67" t="n">
         <v>2.019930685505744</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.3144715146471885</v>
+        <v>0.4041250014782832</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2585288321966963</v>
+        <v>0.3320385672697195</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2276474046365278</v>
+        <v>0.2961252084261706</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2024545416347336</v>
+        <v>0.2615147359659245</v>
       </c>
       <c r="I68" t="n">
-        <v>0.17413769424805</v>
+        <v>0.212257336617811</v>
       </c>
       <c r="J68" t="n">
         <v>0.1263686450518917</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.1471237302521698</v>
+        <v>0.1787585904772335</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1367539344098517</v>
+        <v>0.1578496274601564</v>
       </c>
       <c r="G69" t="n">
-        <v>0.1423857390543887</v>
+        <v>0.1575781611474651</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1531866685795418</v>
+        <v>0.1636893424821534</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1648791683411854</v>
+        <v>0.1706266008802723</v>
       </c>
       <c r="J69" t="n">
         <v>0.1603445483044145</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1.314438900744573</v>
+        <v>1.158992503795303</v>
       </c>
       <c r="F70" t="n">
-        <v>1.491258400701276</v>
+        <v>1.378091096749058</v>
       </c>
       <c r="G70" t="n">
-        <v>1.611117603249183</v>
+        <v>1.524188262818836</v>
       </c>
       <c r="H70" t="n">
-        <v>1.709451409235731</v>
+        <v>1.644560131393737</v>
       </c>
       <c r="I70" t="n">
-        <v>1.782091124373115</v>
+        <v>1.743916336665876</v>
       </c>
       <c r="J70" t="n">
         <v>1.696572071334574</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.2872357134211377</v>
+        <v>0.3964753578845579</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2240762569869211</v>
+        <v>0.3091294111679847</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2030108516002093</v>
+        <v>0.2679381677718091</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1969095271857156</v>
+        <v>0.2432165828330793</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1956598880150603</v>
+        <v>0.2214715990492281</v>
       </c>
       <c r="J71" t="n">
         <v>0.1743519683178779</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.3270101634666925</v>
+        <v>0.3391099062747815</v>
       </c>
       <c r="F72" t="n">
-        <v>0.357301500689395</v>
+        <v>0.361743363329575</v>
       </c>
       <c r="G72" t="n">
-        <v>0.3976577132956234</v>
+        <v>0.398864492343394</v>
       </c>
       <c r="H72" t="n">
-        <v>0.43399916161019</v>
+        <v>0.4339431855654354</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4607580020916222</v>
+        <v>0.4605566787408208</v>
       </c>
       <c r="J72" t="n">
         <v>0.4431911268142765</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1.907814146687774</v>
+        <v>3.086041158650857</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9331602893140457</v>
+        <v>1.592864121558563</v>
       </c>
       <c r="G73" t="n">
-        <v>0.5371814379477813</v>
+        <v>0.9072415287185448</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3755165858800595</v>
+        <v>0.5975981605058609</v>
       </c>
       <c r="I73" t="n">
-        <v>0.277090621061463</v>
+        <v>0.3944079380807074</v>
       </c>
       <c r="J73" t="n">
         <v>0.153948562508387</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.190917127676057</v>
+        <v>0.208497762547506</v>
       </c>
       <c r="F74" t="n">
-        <v>0.1656849912739965</v>
+        <v>0.1849821844095404</v>
       </c>
       <c r="G74" t="n">
-        <v>0.1634724607653372</v>
+        <v>0.1797660914369837</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1725683876729055</v>
+        <v>0.1843323431320734</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1851233452290304</v>
+        <v>0.1916002311862976</v>
       </c>
       <c r="J74" t="n">
         <v>0.1807350771543365</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.7735044165262726</v>
+        <v>0.6837526745287387</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8817160233899649</v>
+        <v>0.7527068182985263</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9593776887786684</v>
+        <v>0.811166005320722</v>
       </c>
       <c r="H75" t="n">
-        <v>1.026760259245786</v>
+        <v>0.8497232706253472</v>
       </c>
       <c r="I75" t="n">
-        <v>1.179507520367114</v>
+        <v>0.9471794115968706</v>
       </c>
       <c r="J75" t="n">
         <v>1.674374444479216</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.7786005873740847</v>
+        <v>0.9470749221888533</v>
       </c>
       <c r="F76" t="n">
-        <v>0.9038890813394956</v>
+        <v>1.045093644491422</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9142608123379901</v>
+        <v>0.9609473183329591</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8977407301814021</v>
+        <v>0.8629036947544029</v>
       </c>
       <c r="I76" t="n">
-        <v>0.9707825192897304</v>
+        <v>0.8582109875045156</v>
       </c>
       <c r="J76" t="n">
         <v>1.269389428073719</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8833423357835655</v>
+        <v>0.8434304032314882</v>
       </c>
       <c r="F77" t="n">
-        <v>1.010439178450807</v>
+        <v>0.9985132848856758</v>
       </c>
       <c r="G77" t="n">
-        <v>1.141339153342923</v>
+        <v>1.1401750011148</v>
       </c>
       <c r="H77" t="n">
-        <v>1.177735629141279</v>
+        <v>1.155009462620502</v>
       </c>
       <c r="I77" t="n">
-        <v>1.221359545049401</v>
+        <v>1.138701558342259</v>
       </c>
       <c r="J77" t="n">
         <v>1.514936229885667</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2.349596887035877</v>
+        <v>3.075141940349479</v>
       </c>
       <c r="F78" t="n">
-        <v>2.386552457292289</v>
+        <v>2.901604616128024</v>
       </c>
       <c r="G78" t="n">
-        <v>2.371106161441204</v>
+        <v>2.689252479522604</v>
       </c>
       <c r="H78" t="n">
-        <v>2.19504607512275</v>
+        <v>2.40297911628412</v>
       </c>
       <c r="I78" t="n">
-        <v>2.000928736640404</v>
+        <v>2.157526275394327</v>
       </c>
       <c r="J78" t="n">
         <v>1.661187790847323</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1.65617162050339</v>
+        <v>1.152739189044171</v>
       </c>
       <c r="F79" t="n">
-        <v>1.569705398224087</v>
+        <v>1.177453422190621</v>
       </c>
       <c r="G79" t="n">
-        <v>1.52853465652559</v>
+        <v>1.287160027717909</v>
       </c>
       <c r="H79" t="n">
-        <v>1.574226913394725</v>
+        <v>1.422316712253346</v>
       </c>
       <c r="I79" t="n">
-        <v>1.634399942809314</v>
+        <v>1.526766976454856</v>
       </c>
       <c r="J79" t="n">
         <v>1.683785533926314</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2.357673349735396</v>
+        <v>2.163759125604895</v>
       </c>
       <c r="F80" t="n">
-        <v>2.933700424967493</v>
+        <v>2.301091091466981</v>
       </c>
       <c r="G80" t="n">
-        <v>3.522800553160296</v>
+        <v>2.46225142556599</v>
       </c>
       <c r="H80" t="n">
-        <v>4.196374029742304</v>
+        <v>2.748347120402116</v>
       </c>
       <c r="I80" t="n">
-        <v>5.551279989273762</v>
+        <v>3.631205554643041</v>
       </c>
       <c r="J80" t="n">
         <v>9.521142421424194</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.658810229956553</v>
+        <v>0.9832902309292241</v>
       </c>
       <c r="F81" t="n">
-        <v>1.39555102790185</v>
+        <v>0.8531114105489767</v>
       </c>
       <c r="G81" t="n">
-        <v>1.176258327141283</v>
+        <v>0.7832757307669671</v>
       </c>
       <c r="H81" t="n">
-        <v>1.141161145355493</v>
+        <v>0.8166330125967652</v>
       </c>
       <c r="I81" t="n">
-        <v>1.277517609676405</v>
+        <v>0.9521235854356642</v>
       </c>
       <c r="J81" t="n">
         <v>1.805668823606482</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2.547103287699406</v>
+        <v>3.19767291740632</v>
       </c>
       <c r="F82" t="n">
-        <v>2.904616790910986</v>
+        <v>3.445210239404914</v>
       </c>
       <c r="G82" t="n">
-        <v>3.178595212649524</v>
+        <v>3.598249359411818</v>
       </c>
       <c r="H82" t="n">
-        <v>3.118604098096971</v>
+        <v>3.506191846643309</v>
       </c>
       <c r="I82" t="n">
-        <v>2.788053611243851</v>
+        <v>3.231037723991944</v>
       </c>
       <c r="J82" t="n">
         <v>1.658697991176802</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.819769409601421</v>
+        <v>1.521642670794135</v>
       </c>
       <c r="F83" t="n">
-        <v>1.923868133077659</v>
+        <v>1.767934095050167</v>
       </c>
       <c r="G83" t="n">
-        <v>2.160904931367565</v>
+        <v>2.152295794389683</v>
       </c>
       <c r="H83" t="n">
-        <v>2.313247236152713</v>
+        <v>2.413327930831352</v>
       </c>
       <c r="I83" t="n">
-        <v>2.241306615435251</v>
+        <v>2.440277966153587</v>
       </c>
       <c r="J83" t="n">
         <v>1.619467685319641</v>
@@ -6910,58 +6910,58 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1.881623334878145</v>
+        <v>1.878280431784082</v>
       </c>
       <c r="F86" t="n">
-        <v>2.020277767599288</v>
+        <v>2.015178650883107</v>
       </c>
       <c r="G86" t="n">
-        <v>2.090509709508233</v>
+        <v>2.084024481778159</v>
       </c>
       <c r="H86" t="n">
-        <v>2.110651701604345</v>
+        <v>2.102895538481198</v>
       </c>
       <c r="I86" t="n">
-        <v>2.10094823864031</v>
+        <v>2.092007983260516</v>
       </c>
       <c r="J86" t="n">
-        <v>2.008118875914124</v>
+        <v>1.998441082424618</v>
       </c>
       <c r="K86" t="n">
-        <v>1.744892855648751</v>
+        <v>1.735563969726468</v>
       </c>
       <c r="L86" t="n">
-        <v>1.453323980835305</v>
+        <v>1.444836668132948</v>
       </c>
       <c r="M86" t="n">
-        <v>1.274094943489237</v>
+        <v>1.265961307374747</v>
       </c>
       <c r="N86" t="n">
-        <v>1.111321757699754</v>
+        <v>1.103403587827811</v>
       </c>
       <c r="O86" t="n">
-        <v>0.9330184332946916</v>
+        <v>0.9254184206543379</v>
       </c>
       <c r="P86" t="n">
-        <v>0.7863414301249811</v>
+        <v>0.778823748702604</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.7117748169137332</v>
+        <v>0.7038528851062057</v>
       </c>
       <c r="R86" t="n">
-        <v>0.6420825328810078</v>
+        <v>0.6339714012010209</v>
       </c>
       <c r="S86" t="n">
-        <v>0.5871117371812951</v>
+        <v>0.5788947787047092</v>
       </c>
       <c r="T86" t="n">
-        <v>0.5460072780424277</v>
+        <v>0.537607925619521</v>
       </c>
       <c r="U86" t="n">
-        <v>0.5166165259615935</v>
+        <v>0.5078035913111976</v>
       </c>
       <c r="V86" t="n">
-        <v>0.5005079329204543</v>
+        <v>0.4908088046447709</v>
       </c>
     </row>
     <row r="87">
@@ -6986,58 +6986,58 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1.586846507168575</v>
+        <v>1.587925108200088</v>
       </c>
       <c r="F87" t="n">
-        <v>1.75005249348039</v>
+        <v>1.752830240091555</v>
       </c>
       <c r="G87" t="n">
-        <v>1.912606558137025</v>
+        <v>1.918324617675066</v>
       </c>
       <c r="H87" t="n">
-        <v>2.013756302612521</v>
+        <v>2.022485761268472</v>
       </c>
       <c r="I87" t="n">
-        <v>2.059926168046217</v>
+        <v>2.071337385784871</v>
       </c>
       <c r="J87" t="n">
-        <v>2.001381109387906</v>
+        <v>2.014583841424389</v>
       </c>
       <c r="K87" t="n">
-        <v>1.753666410152734</v>
+        <v>1.766819705487224</v>
       </c>
       <c r="L87" t="n">
-        <v>1.466031194632947</v>
+        <v>1.478236413079626</v>
       </c>
       <c r="M87" t="n">
-        <v>1.28775921427556</v>
+        <v>1.299444331126729</v>
       </c>
       <c r="N87" t="n">
-        <v>1.125919441915276</v>
+        <v>1.136843630314941</v>
       </c>
       <c r="O87" t="n">
-        <v>0.9491974298092017</v>
+        <v>0.9588922930842348</v>
       </c>
       <c r="P87" t="n">
-        <v>0.8045280002676251</v>
+        <v>0.8131009615384616</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.7304580530124815</v>
+        <v>0.7385654564797195</v>
       </c>
       <c r="R87" t="n">
-        <v>0.6577297475165087</v>
+        <v>0.6653875444058464</v>
       </c>
       <c r="S87" t="n">
-        <v>0.5971210045564054</v>
+        <v>0.604504381253401</v>
       </c>
       <c r="T87" t="n">
-        <v>0.5487361419622601</v>
+        <v>0.5560263456495769</v>
       </c>
       <c r="U87" t="n">
-        <v>0.5110219802145558</v>
+        <v>0.5184190513466634</v>
       </c>
       <c r="V87" t="n">
-        <v>0.4849767405146899</v>
+        <v>0.4927846995576425</v>
       </c>
     </row>
     <row r="88">
@@ -7062,58 +7062,58 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2.719213075263061</v>
+        <v>2.728586338483958</v>
       </c>
       <c r="F88" t="n">
-        <v>2.495968709214066</v>
+        <v>2.504503040488811</v>
       </c>
       <c r="G88" t="n">
-        <v>2.29610052055222</v>
+        <v>2.300662211280006</v>
       </c>
       <c r="H88" t="n">
-        <v>2.177717517886826</v>
+        <v>2.179165821660439</v>
       </c>
       <c r="I88" t="n">
-        <v>2.113646638727785</v>
+        <v>2.113441751648406</v>
       </c>
       <c r="J88" t="n">
-        <v>2.009488071735126</v>
+        <v>2.008826619781874</v>
       </c>
       <c r="K88" t="n">
-        <v>1.748352335826826</v>
+        <v>1.747815784682319</v>
       </c>
       <c r="L88" t="n">
-        <v>1.458722797064176</v>
+        <v>1.458393328605484</v>
       </c>
       <c r="M88" t="n">
-        <v>1.282834158038073</v>
+        <v>1.28270053212957</v>
       </c>
       <c r="N88" t="n">
-        <v>1.12718832947249</v>
+        <v>1.127301156732772</v>
       </c>
       <c r="O88" t="n">
-        <v>0.9581070428545666</v>
+        <v>0.9585023720599032</v>
       </c>
       <c r="P88" t="n">
-        <v>0.8204669629912801</v>
+        <v>0.821095337281863</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.7533246971216748</v>
+        <v>0.7541642265918846</v>
       </c>
       <c r="R88" t="n">
-        <v>0.6858799374539718</v>
+        <v>0.6868807786142844</v>
       </c>
       <c r="S88" t="n">
-        <v>0.629276911828595</v>
+        <v>0.6304152140972524</v>
       </c>
       <c r="T88" t="n">
-        <v>0.585149714520766</v>
+        <v>0.5864673453784556</v>
       </c>
       <c r="U88" t="n">
-        <v>0.5523496279801033</v>
+        <v>0.5539162279739377</v>
       </c>
       <c r="V88" t="n">
-        <v>0.5323567423467108</v>
+        <v>0.5342717572834403</v>
       </c>
     </row>
     <row r="89">
@@ -7138,58 +7138,58 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4.043955360494802</v>
+        <v>4.059159408713141</v>
       </c>
       <c r="F89" t="n">
-        <v>4.031114466358403</v>
+        <v>4.05108087194489</v>
       </c>
       <c r="G89" t="n">
-        <v>4.079713679486867</v>
+        <v>4.103064105065483</v>
       </c>
       <c r="H89" t="n">
-        <v>4.068466819433692</v>
+        <v>4.094803710820038</v>
       </c>
       <c r="I89" t="n">
-        <v>4.00733250648396</v>
+        <v>4.036194019088216</v>
       </c>
       <c r="J89" t="n">
-        <v>3.778932251936882</v>
+        <v>3.808439165950466</v>
       </c>
       <c r="K89" t="n">
-        <v>3.233346629122517</v>
+        <v>3.260101179639276</v>
       </c>
       <c r="L89" t="n">
-        <v>2.651713585610994</v>
+        <v>2.674712523205384</v>
       </c>
       <c r="M89" t="n">
-        <v>2.30033312521335</v>
+        <v>2.321249583293695</v>
       </c>
       <c r="N89" t="n">
-        <v>2.001254942798144</v>
+        <v>2.020402290975857</v>
       </c>
       <c r="O89" t="n">
-        <v>1.688387752726396</v>
+        <v>1.705431139815687</v>
       </c>
       <c r="P89" t="n">
-        <v>1.438404017921403</v>
+        <v>1.453809285274229</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.317062303563517</v>
+        <v>1.33217705447312</v>
       </c>
       <c r="R89" t="n">
-        <v>1.198659868239146</v>
+        <v>1.213623524329703</v>
       </c>
       <c r="S89" t="n">
-        <v>1.101761593536884</v>
+        <v>1.117001983588842</v>
       </c>
       <c r="T89" t="n">
-        <v>1.026490727298856</v>
+        <v>1.042496689089355</v>
       </c>
       <c r="U89" t="n">
-        <v>0.9690316217930401</v>
+        <v>0.98634885730814</v>
       </c>
       <c r="V89" t="n">
-        <v>0.9312706162112158</v>
+        <v>0.9507911946876486</v>
       </c>
     </row>
     <row r="90">
@@ -7214,58 +7214,58 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1.324191844397447</v>
+        <v>1.32154330196865</v>
       </c>
       <c r="F90" t="n">
-        <v>1.36106059430243</v>
+        <v>1.355479584762283</v>
       </c>
       <c r="G90" t="n">
-        <v>1.418062847515006</v>
+        <v>1.41127903208439</v>
       </c>
       <c r="H90" t="n">
-        <v>1.459566137521527</v>
+        <v>1.452482646976369</v>
       </c>
       <c r="I90" t="n">
-        <v>1.480139352696669</v>
+        <v>1.473095131640592</v>
       </c>
       <c r="J90" t="n">
-        <v>1.433269718947288</v>
+        <v>1.426479958208163</v>
       </c>
       <c r="K90" t="n">
-        <v>1.256380145444294</v>
+        <v>1.250376712828166</v>
       </c>
       <c r="L90" t="n">
-        <v>1.054094266092519</v>
+        <v>1.049046423788627</v>
       </c>
       <c r="M90" t="n">
-        <v>0.9321520539686572</v>
+        <v>0.9277777968442018</v>
       </c>
       <c r="N90" t="n">
-        <v>0.8219076047679855</v>
+        <v>0.8181559350912742</v>
       </c>
       <c r="O90" t="n">
-        <v>0.6988031652243029</v>
+        <v>0.695676011449801</v>
       </c>
       <c r="P90" t="n">
-        <v>0.5975478911621456</v>
+        <v>0.5948805849136178</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.5478822572379526</v>
+        <v>0.5454092053299332</v>
       </c>
       <c r="R90" t="n">
-        <v>0.4986355501385948</v>
+        <v>0.4963438752966258</v>
       </c>
       <c r="S90" t="n">
-        <v>0.4580142398344232</v>
+        <v>0.4558675886555223</v>
       </c>
       <c r="T90" t="n">
-        <v>0.4265490114555183</v>
+        <v>0.4244961541407267</v>
       </c>
       <c r="U90" t="n">
-        <v>0.4031372767193888</v>
+        <v>0.4010917275660087</v>
       </c>
       <c r="V90" t="n">
-        <v>0.3891151940691648</v>
+        <v>0.3869362346854181</v>
       </c>
     </row>
     <row r="91">
@@ -7290,58 +7290,58 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1.157703091387361</v>
+        <v>1.153300824537914</v>
       </c>
       <c r="F91" t="n">
-        <v>1.236641252487022</v>
+        <v>1.22957005328011</v>
       </c>
       <c r="G91" t="n">
-        <v>1.288420467787408</v>
+        <v>1.279736946794391</v>
       </c>
       <c r="H91" t="n">
-        <v>1.296237329981978</v>
+        <v>1.285689607585916</v>
       </c>
       <c r="I91" t="n">
-        <v>1.275082611389685</v>
+        <v>1.262213708804712</v>
       </c>
       <c r="J91" t="n">
-        <v>1.19870691122161</v>
+        <v>1.183644722521082</v>
       </c>
       <c r="K91" t="n">
-        <v>1.02387163629951</v>
+        <v>1.008157763987153</v>
       </c>
       <c r="L91" t="n">
-        <v>0.840672739022041</v>
+        <v>0.8253715536114713</v>
       </c>
       <c r="M91" t="n">
-        <v>0.7299280854340933</v>
+        <v>0.7146223999920819</v>
       </c>
       <c r="N91" t="n">
-        <v>0.6360456481190963</v>
+        <v>0.6212697656891759</v>
       </c>
       <c r="O91" t="n">
-        <v>0.5378618671334786</v>
+        <v>0.5244769818056111</v>
       </c>
       <c r="P91" t="n">
-        <v>0.4601003982038466</v>
+        <v>0.448123358468186</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.4234860668517521</v>
+        <v>0.4120551678659808</v>
       </c>
       <c r="R91" t="n">
-        <v>0.3877852517332539</v>
+        <v>0.3769368232182902</v>
       </c>
       <c r="S91" t="n">
-        <v>0.3591523124706532</v>
+        <v>0.3487219826812415</v>
       </c>
       <c r="T91" t="n">
-        <v>0.338063531384343</v>
+        <v>0.3278329360247856</v>
       </c>
       <c r="U91" t="n">
-        <v>0.3239040060839006</v>
+        <v>0.313593323389501</v>
       </c>
       <c r="V91" t="n">
-        <v>0.3181086899354171</v>
+        <v>0.3072443958720582</v>
       </c>
     </row>
     <row r="92">
@@ -7366,58 +7366,58 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9760649793047874</v>
+        <v>0.968866525035713</v>
       </c>
       <c r="F92" t="n">
-        <v>1.062203153523689</v>
+        <v>1.051242994223045</v>
       </c>
       <c r="G92" t="n">
-        <v>1.144369267793801</v>
+        <v>1.132257575421034</v>
       </c>
       <c r="H92" t="n">
-        <v>1.18186152295442</v>
+        <v>1.168605526170395</v>
       </c>
       <c r="I92" t="n">
-        <v>1.184695623224725</v>
+        <v>1.169841291590987</v>
       </c>
       <c r="J92" t="n">
-        <v>1.129795804294614</v>
+        <v>1.113525290179406</v>
       </c>
       <c r="K92" t="n">
-        <v>0.976347959448479</v>
+        <v>0.9602312610876419</v>
       </c>
       <c r="L92" t="n">
-        <v>0.8078231589041693</v>
+        <v>0.7926334372207572</v>
       </c>
       <c r="M92" t="n">
-        <v>0.7060226825036253</v>
+        <v>0.6912307172175235</v>
       </c>
       <c r="N92" t="n">
-        <v>0.6175766398906013</v>
+        <v>0.6035186319656203</v>
       </c>
       <c r="O92" t="n">
-        <v>0.5231057804733947</v>
+        <v>0.5104608289219034</v>
       </c>
       <c r="P92" t="n">
-        <v>0.4473891779117806</v>
+        <v>0.4360708277848242</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.411682051739866</v>
+        <v>0.4008755126174784</v>
       </c>
       <c r="R92" t="n">
-        <v>0.3769918143192207</v>
+        <v>0.3667467119462054</v>
       </c>
       <c r="S92" t="n">
-        <v>0.3490217186062623</v>
+        <v>0.3391666683465812</v>
       </c>
       <c r="T92" t="n">
-        <v>0.3280366293710465</v>
+        <v>0.3183112872363814</v>
       </c>
       <c r="U92" t="n">
-        <v>0.3134947429343108</v>
+        <v>0.3035672307785744</v>
       </c>
       <c r="V92" t="n">
-        <v>0.3071446700974424</v>
+        <v>0.2965323170978433</v>
       </c>
     </row>
     <row r="93">
@@ -7442,58 +7442,58 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1.077286105157661</v>
+        <v>1.075961576917919</v>
       </c>
       <c r="F93" t="n">
-        <v>1.163422471744109</v>
+        <v>1.161596457856246</v>
       </c>
       <c r="G93" t="n">
-        <v>1.270219276111498</v>
+        <v>1.269657787416288</v>
       </c>
       <c r="H93" t="n">
-        <v>1.370087918467829</v>
+        <v>1.37191964697596</v>
       </c>
       <c r="I93" t="n">
-        <v>1.448482214271152</v>
+        <v>1.453140087959654</v>
       </c>
       <c r="J93" t="n">
-        <v>1.44972026968871</v>
+        <v>1.456827840338545</v>
       </c>
       <c r="K93" t="n">
-        <v>1.298234294347224</v>
+        <v>1.306392870631823</v>
       </c>
       <c r="L93" t="n">
-        <v>1.099617221424767</v>
+        <v>1.107749009199325</v>
       </c>
       <c r="M93" t="n">
-        <v>0.9704940997266335</v>
+        <v>0.9784684223172231</v>
       </c>
       <c r="N93" t="n">
-        <v>0.8477294994189888</v>
+        <v>0.855148214814646</v>
       </c>
       <c r="O93" t="n">
-        <v>0.7120771503120725</v>
+        <v>0.7185369946780997</v>
       </c>
       <c r="P93" t="n">
-        <v>0.601724178102938</v>
+        <v>0.6073300869078962</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.5458333135608904</v>
+        <v>0.5510840834998173</v>
       </c>
       <c r="R93" t="n">
-        <v>0.4916711341181493</v>
+        <v>0.4966099926984457</v>
       </c>
       <c r="S93" t="n">
-        <v>0.4464454858478253</v>
+        <v>0.4511765510211692</v>
       </c>
       <c r="T93" t="n">
-        <v>0.4101728206109304</v>
+        <v>0.4147975256680059</v>
       </c>
       <c r="U93" t="n">
-        <v>0.3816773713992577</v>
+        <v>0.386289043483723</v>
       </c>
       <c r="V93" t="n">
-        <v>0.3621542377523239</v>
+        <v>0.3669335567262202</v>
       </c>
     </row>
     <row r="94">
@@ -7518,58 +7518,58 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2.16171799306156</v>
+        <v>2.165643941367061</v>
       </c>
       <c r="F94" t="n">
-        <v>2.3757861395336</v>
+        <v>2.383191124702646</v>
       </c>
       <c r="G94" t="n">
-        <v>2.486620388691084</v>
+        <v>2.496468433552038</v>
       </c>
       <c r="H94" t="n">
-        <v>2.510048090868278</v>
+        <v>2.52158696962075</v>
       </c>
       <c r="I94" t="n">
-        <v>2.480581773170354</v>
+        <v>2.493189924462699</v>
       </c>
       <c r="J94" t="n">
-        <v>2.349949898484982</v>
+        <v>2.362820931226719</v>
       </c>
       <c r="K94" t="n">
-        <v>2.024784529927707</v>
+        <v>2.036561869108953</v>
       </c>
       <c r="L94" t="n">
-        <v>1.67283092283681</v>
+        <v>1.683091316752211</v>
       </c>
       <c r="M94" t="n">
-        <v>1.456249791279172</v>
+        <v>1.465566972887346</v>
       </c>
       <c r="N94" t="n">
-        <v>1.265570700127953</v>
+        <v>1.273924348223162</v>
       </c>
       <c r="O94" t="n">
-        <v>1.063157460372189</v>
+        <v>1.070340534166207</v>
       </c>
       <c r="P94" t="n">
-        <v>0.9006052901583462</v>
+        <v>0.9068467630279088</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.818684436169431</v>
+        <v>0.8245268134937163</v>
       </c>
       <c r="R94" t="n">
-        <v>0.7377764524021082</v>
+        <v>0.7432032909889331</v>
       </c>
       <c r="S94" t="n">
-        <v>0.6695289380691462</v>
+        <v>0.6746065573598644</v>
       </c>
       <c r="T94" t="n">
-        <v>0.615042516253035</v>
+        <v>0.6198665380981516</v>
       </c>
       <c r="U94" t="n">
-        <v>0.5733961537135018</v>
+        <v>0.5781117987176573</v>
       </c>
       <c r="V94" t="n">
-        <v>0.5461976813033014</v>
+        <v>0.5510350793518264</v>
       </c>
     </row>
     <row r="95">
@@ -7594,58 +7594,58 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1.065600174100638</v>
+        <v>1.055527837178056</v>
       </c>
       <c r="F95" t="n">
-        <v>1.222729577647917</v>
+        <v>1.209524146615718</v>
       </c>
       <c r="G95" t="n">
-        <v>1.350982355383168</v>
+        <v>1.337648645395524</v>
       </c>
       <c r="H95" t="n">
-        <v>1.431100666827348</v>
+        <v>1.418104663774404</v>
       </c>
       <c r="I95" t="n">
-        <v>1.474013551215624</v>
+        <v>1.461372504146363</v>
       </c>
       <c r="J95" t="n">
-        <v>1.440530401854796</v>
+        <v>1.428448562691778</v>
       </c>
       <c r="K95" t="n">
-        <v>1.270362674674705</v>
+        <v>1.259723306885981</v>
       </c>
       <c r="L95" t="n">
-        <v>1.069027466165685</v>
+        <v>1.059968621037646</v>
       </c>
       <c r="M95" t="n">
-        <v>0.946314743134927</v>
+        <v>0.938214811744678</v>
       </c>
       <c r="N95" t="n">
-        <v>0.8350579414019655</v>
+        <v>0.8278759465841047</v>
       </c>
       <c r="O95" t="n">
-        <v>0.7108446365756979</v>
+        <v>0.7047116470951832</v>
       </c>
       <c r="P95" t="n">
-        <v>0.6092578508986615</v>
+        <v>0.6039893312189946</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.56035012102003</v>
+        <v>0.5554847043734624</v>
       </c>
       <c r="R95" t="n">
-        <v>0.5118906625280097</v>
+        <v>0.5074255049206186</v>
       </c>
       <c r="S95" t="n">
-        <v>0.4720870202456605</v>
+        <v>0.4679431990237332</v>
       </c>
       <c r="T95" t="n">
-        <v>0.4414972053363796</v>
+        <v>0.4375714577128636</v>
       </c>
       <c r="U95" t="n">
-        <v>0.4191169785863398</v>
+        <v>0.415270795329319</v>
       </c>
       <c r="V95" t="n">
-        <v>0.4067139254010251</v>
+        <v>0.4027688484458841</v>
       </c>
     </row>
     <row r="96">
@@ -7670,58 +7670,58 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1.694196036033694</v>
+        <v>1.696335748747787</v>
       </c>
       <c r="F96" t="n">
-        <v>1.644010054940469</v>
+        <v>1.644202856676077</v>
       </c>
       <c r="G96" t="n">
-        <v>1.541673874476218</v>
+        <v>1.537626711523121</v>
       </c>
       <c r="H96" t="n">
-        <v>1.469680571909909</v>
+        <v>1.461793613202263</v>
       </c>
       <c r="I96" t="n">
-        <v>1.426336839395876</v>
+        <v>1.415675617018798</v>
       </c>
       <c r="J96" t="n">
-        <v>1.355383490470063</v>
+        <v>1.343438865978684</v>
       </c>
       <c r="K96" t="n">
-        <v>1.180280960743841</v>
+        <v>1.168889215075993</v>
       </c>
       <c r="L96" t="n">
-        <v>0.9872905126438403</v>
+        <v>0.977147590138112</v>
       </c>
       <c r="M96" t="n">
-        <v>0.8703159777032541</v>
+        <v>0.8609126881224027</v>
       </c>
       <c r="N96" t="n">
-        <v>0.7658867889056391</v>
+        <v>0.757305166718694</v>
       </c>
       <c r="O96" t="n">
-        <v>0.6515104798123378</v>
+        <v>0.6440665628331428</v>
       </c>
       <c r="P96" t="n">
-        <v>0.5586983194509116</v>
+        <v>0.5522534174628242</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.5143149326833784</v>
+        <v>0.5083270025388618</v>
       </c>
       <c r="R96" t="n">
-        <v>0.4699089370585269</v>
+        <v>0.4643352429716699</v>
       </c>
       <c r="S96" t="n">
-        <v>0.4329618728834011</v>
+        <v>0.427646352475592</v>
       </c>
       <c r="T96" t="n">
-        <v>0.4042954385718001</v>
+        <v>0.3990642520066148</v>
       </c>
       <c r="U96" t="n">
-        <v>0.3835001165292633</v>
+        <v>0.3781767428717432</v>
       </c>
       <c r="V96" t="n">
-        <v>0.3722698963016304</v>
+        <v>0.3666028410493663</v>
       </c>
     </row>
     <row r="97">
@@ -7746,58 +7746,58 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1.876764346320975</v>
+        <v>1.881075807642495</v>
       </c>
       <c r="F97" t="n">
-        <v>1.682313131129833</v>
+        <v>1.68333029299037</v>
       </c>
       <c r="G97" t="n">
-        <v>1.530232681191053</v>
+        <v>1.525926954773338</v>
       </c>
       <c r="H97" t="n">
-        <v>1.446557815710403</v>
+        <v>1.437904455131539</v>
       </c>
       <c r="I97" t="n">
-        <v>1.404978323474308</v>
+        <v>1.393470676122527</v>
       </c>
       <c r="J97" t="n">
-        <v>1.337164678473854</v>
+        <v>1.324404499608022</v>
       </c>
       <c r="K97" t="n">
-        <v>1.164895455746283</v>
+        <v>1.152740786933193</v>
       </c>
       <c r="L97" t="n">
-        <v>0.9735236151545165</v>
+        <v>0.9626234735481712</v>
       </c>
       <c r="M97" t="n">
-        <v>0.8571749067556578</v>
+        <v>0.846977508279591</v>
       </c>
       <c r="N97" t="n">
-        <v>0.7532715685691584</v>
+        <v>0.7438622616930536</v>
       </c>
       <c r="O97" t="n">
-        <v>0.6397582021060831</v>
+        <v>0.6314876130082193</v>
       </c>
       <c r="P97" t="n">
-        <v>0.547614740413736</v>
+        <v>0.5403381349029561</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.5034371699581784</v>
+        <v>0.4965777115176309</v>
       </c>
       <c r="R97" t="n">
-        <v>0.4600263570938021</v>
+        <v>0.4536023247844055</v>
       </c>
       <c r="S97" t="n">
-        <v>0.4246233307220026</v>
+        <v>0.4185310353622766</v>
       </c>
       <c r="T97" t="n">
-        <v>0.3975892935868799</v>
+        <v>0.3916711365506702</v>
       </c>
       <c r="U97" t="n">
-        <v>0.3780372942852238</v>
+        <v>0.3720826431709886</v>
       </c>
       <c r="V97" t="n">
-        <v>0.3675631740542978</v>
+        <v>0.361252933479606</v>
       </c>
     </row>
     <row r="98">
@@ -7822,58 +7822,58 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2.100207932769573</v>
+        <v>2.105595951213525</v>
       </c>
       <c r="F98" t="n">
-        <v>1.938447482703523</v>
+        <v>1.941732735289873</v>
       </c>
       <c r="G98" t="n">
-        <v>1.814917463346139</v>
+        <v>1.813760393163796</v>
       </c>
       <c r="H98" t="n">
-        <v>1.70923049011999</v>
+        <v>1.704426104514055</v>
       </c>
       <c r="I98" t="n">
-        <v>1.630216502136493</v>
+        <v>1.622913042260981</v>
       </c>
       <c r="J98" t="n">
-        <v>1.516480287171156</v>
+        <v>1.507944739312041</v>
       </c>
       <c r="K98" t="n">
-        <v>1.283390748337356</v>
+        <v>1.275169938889384</v>
       </c>
       <c r="L98" t="n">
-        <v>1.04252560564111</v>
+        <v>1.035318039590657</v>
       </c>
       <c r="M98" t="n">
-        <v>0.8892573348142931</v>
+        <v>0.8828076829301331</v>
       </c>
       <c r="N98" t="n">
-        <v>0.7725553070439211</v>
+        <v>0.7667758649002623</v>
       </c>
       <c r="O98" t="n">
-        <v>0.6709125779197181</v>
+        <v>0.6657917805179739</v>
       </c>
       <c r="P98" t="n">
-        <v>0.6099801075181155</v>
+        <v>0.6052604905960209</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.6003216083805316</v>
+        <v>0.5956343823330154</v>
       </c>
       <c r="R98" t="n">
-        <v>0.6018002184682925</v>
+        <v>0.5970820168263032</v>
       </c>
       <c r="S98" t="n">
-        <v>0.6031257320359944</v>
+        <v>0.5984012391239956</v>
       </c>
       <c r="T98" t="n">
-        <v>0.6066905500212574</v>
+        <v>0.6019618842795476</v>
       </c>
       <c r="U98" t="n">
-        <v>0.616363680477527</v>
+        <v>0.6116344975535968</v>
       </c>
       <c r="V98" t="n">
-        <v>0.6315336298919502</v>
+        <v>0.6268497431569368</v>
       </c>
     </row>
     <row r="99">
@@ -7898,58 +7898,58 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2.419138116847831</v>
+        <v>2.427743499619255</v>
       </c>
       <c r="F99" t="n">
-        <v>2.338244328859596</v>
+        <v>2.35184149022823</v>
       </c>
       <c r="G99" t="n">
-        <v>2.252628196343666</v>
+        <v>2.269069298274525</v>
       </c>
       <c r="H99" t="n">
-        <v>2.136137074296701</v>
+        <v>2.153586684579991</v>
       </c>
       <c r="I99" t="n">
-        <v>2.02527394265009</v>
+        <v>2.042721642614689</v>
       </c>
       <c r="J99" t="n">
-        <v>1.859024221022971</v>
+        <v>1.875396156577574</v>
       </c>
       <c r="K99" t="n">
-        <v>1.546522787953352</v>
+        <v>1.560216735965062</v>
       </c>
       <c r="L99" t="n">
-        <v>1.232732170545405</v>
+        <v>1.243622887058089</v>
       </c>
       <c r="M99" t="n">
-        <v>1.031460938547854</v>
+        <v>1.040522241665601</v>
       </c>
       <c r="N99" t="n">
-        <v>0.8791273615106839</v>
+        <v>0.8868066609288577</v>
       </c>
       <c r="O99" t="n">
-        <v>0.7491772243505254</v>
+        <v>0.7556930654956209</v>
       </c>
       <c r="P99" t="n">
-        <v>0.6673955694991774</v>
+        <v>0.6731931744270574</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.642015828465029</v>
+        <v>0.647603636219575</v>
       </c>
       <c r="R99" t="n">
-        <v>0.6273642901770852</v>
+        <v>0.632846573297518</v>
       </c>
       <c r="S99" t="n">
-        <v>0.6105563756154884</v>
+        <v>0.6159252429649247</v>
       </c>
       <c r="T99" t="n">
-        <v>0.592840078551327</v>
+        <v>0.5980926841646835</v>
       </c>
       <c r="U99" t="n">
-        <v>0.576553355698785</v>
+        <v>0.5817054027198616</v>
       </c>
       <c r="V99" t="n">
-        <v>0.5588635218875174</v>
+        <v>0.5638896389722148</v>
       </c>
     </row>
     <row r="100">
@@ -7974,58 +7974,58 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1.750376726881332</v>
+        <v>1.749083783670983</v>
       </c>
       <c r="F100" t="n">
-        <v>1.713100233164468</v>
+        <v>1.707491747617462</v>
       </c>
       <c r="G100" t="n">
-        <v>1.676651348953757</v>
+        <v>1.666742288239276</v>
       </c>
       <c r="H100" t="n">
-        <v>1.622692190164516</v>
+        <v>1.609800819459367</v>
       </c>
       <c r="I100" t="n">
-        <v>1.573329546348243</v>
+        <v>1.558571240861097</v>
       </c>
       <c r="J100" t="n">
-        <v>1.47894945287291</v>
+        <v>1.46366618541573</v>
       </c>
       <c r="K100" t="n">
-        <v>1.260601735556947</v>
+        <v>1.246797443625541</v>
       </c>
       <c r="L100" t="n">
-        <v>1.030105691033413</v>
+        <v>1.018406068902321</v>
       </c>
       <c r="M100" t="n">
-        <v>0.8834896916658369</v>
+        <v>0.8732086019649751</v>
       </c>
       <c r="N100" t="n">
-        <v>0.7715156505965133</v>
+        <v>0.7623962219363309</v>
       </c>
       <c r="O100" t="n">
-        <v>0.6731998913194116</v>
+        <v>0.6651730288893863</v>
       </c>
       <c r="P100" t="n">
-        <v>0.614581058408781</v>
+        <v>0.6072432604406709</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.6070462996739341</v>
+        <v>0.5998358818096972</v>
       </c>
       <c r="R100" t="n">
-        <v>0.6108796722757807</v>
+        <v>0.603695479244488</v>
       </c>
       <c r="S100" t="n">
-        <v>0.6150251304699771</v>
+        <v>0.6078964129305385</v>
       </c>
       <c r="T100" t="n">
-        <v>0.622040922776979</v>
+        <v>0.6149754296630507</v>
       </c>
       <c r="U100" t="n">
-        <v>0.6366088643444894</v>
+        <v>0.6295926405012241</v>
       </c>
       <c r="V100" t="n">
-        <v>0.6590209324984664</v>
+        <v>0.6520899840886886</v>
       </c>
     </row>
     <row r="101">
@@ -8050,58 +8050,58 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2.272787532400953</v>
+        <v>2.277053589601401</v>
       </c>
       <c r="F101" t="n">
-        <v>2.160885270533947</v>
+        <v>2.165186468317833</v>
       </c>
       <c r="G101" t="n">
-        <v>2.041406167625066</v>
+        <v>2.044392470021515</v>
       </c>
       <c r="H101" t="n">
-        <v>1.909427453540783</v>
+        <v>1.91100084589515</v>
       </c>
       <c r="I101" t="n">
-        <v>1.799119561742494</v>
+        <v>1.799471777491324</v>
       </c>
       <c r="J101" t="n">
-        <v>1.653378193048585</v>
+        <v>1.652786702167208</v>
       </c>
       <c r="K101" t="n">
-        <v>1.384544349029461</v>
+        <v>1.383369988318789</v>
       </c>
       <c r="L101" t="n">
-        <v>1.114946885908905</v>
+        <v>1.113510420245956</v>
       </c>
       <c r="M101" t="n">
-        <v>0.9442959677108036</v>
+        <v>0.9427060419094678</v>
       </c>
       <c r="N101" t="n">
-        <v>0.8154054184393197</v>
+        <v>0.8137723496444902</v>
       </c>
       <c r="O101" t="n">
-        <v>0.7042208086853127</v>
+        <v>0.7026439754657017</v>
       </c>
       <c r="P101" t="n">
-        <v>0.6364280959729367</v>
+        <v>0.6349040389879737</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.622060346030006</v>
+        <v>0.6205045997651949</v>
       </c>
       <c r="R101" t="n">
-        <v>0.6188717156914449</v>
+        <v>0.6172694990099292</v>
       </c>
       <c r="S101" t="n">
-        <v>0.6150378059283316</v>
+        <v>0.6133867034995983</v>
       </c>
       <c r="T101" t="n">
-        <v>0.6125237085386108</v>
+        <v>0.610818020110441</v>
       </c>
       <c r="U101" t="n">
-        <v>0.6148300445915996</v>
+        <v>0.6130765445603501</v>
       </c>
       <c r="V101" t="n">
-        <v>0.6207441376406836</v>
+        <v>0.6189639727629498</v>
       </c>
     </row>
     <row r="102">
@@ -8126,58 +8126,58 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1.566675064942372</v>
+        <v>1.56321425402754</v>
       </c>
       <c r="F102" t="n">
-        <v>1.58205948374637</v>
+        <v>1.578985355158573</v>
       </c>
       <c r="G102" t="n">
-        <v>1.528926580213962</v>
+        <v>1.527237872141696</v>
       </c>
       <c r="H102" t="n">
-        <v>1.444247736771575</v>
+        <v>1.443739548423646</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3676135244948</v>
+        <v>1.367867121606871</v>
       </c>
       <c r="J102" t="n">
-        <v>1.259642331851755</v>
+        <v>1.26029774745911</v>
       </c>
       <c r="K102" t="n">
-        <v>1.055150824331667</v>
+        <v>1.055891874924769</v>
       </c>
       <c r="L102" t="n">
-        <v>0.8486704073048322</v>
+        <v>0.8493355500400764</v>
       </c>
       <c r="M102" t="n">
-        <v>0.7170738363950521</v>
+        <v>0.717635044261999</v>
       </c>
       <c r="N102" t="n">
-        <v>0.6172886247285754</v>
+        <v>0.61773787900401</v>
       </c>
       <c r="O102" t="n">
-        <v>0.531322338384806</v>
+        <v>0.5316625459907848</v>
       </c>
       <c r="P102" t="n">
-        <v>0.47845114376737</v>
+        <v>0.4787160042351953</v>
       </c>
       <c r="Q102" t="n">
-        <v>0.4658088626236435</v>
+        <v>0.4660319119060569</v>
       </c>
       <c r="R102" t="n">
-        <v>0.4613474277020915</v>
+        <v>0.4615367278869886</v>
       </c>
       <c r="S102" t="n">
-        <v>0.4559753003471235</v>
+        <v>0.4561351255997061</v>
       </c>
       <c r="T102" t="n">
-        <v>0.4509282009659235</v>
+        <v>0.4510670757533248</v>
       </c>
       <c r="U102" t="n">
-        <v>0.4487187619620495</v>
+        <v>0.4488332250677086</v>
       </c>
       <c r="V102" t="n">
-        <v>0.4482611475086194</v>
+        <v>0.4483389349793647</v>
       </c>
     </row>
     <row r="103">
@@ -8202,58 +8202,58 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2.570187751237282</v>
+        <v>2.576032334691774</v>
       </c>
       <c r="F103" t="n">
-        <v>2.372388994288868</v>
+        <v>2.37434804212418</v>
       </c>
       <c r="G103" t="n">
-        <v>2.238475640735277</v>
+        <v>2.23422917725122</v>
       </c>
       <c r="H103" t="n">
-        <v>2.124440594763426</v>
+        <v>2.115499145191359</v>
       </c>
       <c r="I103" t="n">
-        <v>2.035888398091447</v>
+        <v>2.02406186741993</v>
       </c>
       <c r="J103" t="n">
-        <v>1.897154439021125</v>
+        <v>1.884282191692528</v>
       </c>
       <c r="K103" t="n">
-        <v>1.604250329831315</v>
+        <v>1.592531981751487</v>
       </c>
       <c r="L103" t="n">
-        <v>1.300161961682329</v>
+        <v>1.290369500425998</v>
       </c>
       <c r="M103" t="n">
-        <v>1.105680729155786</v>
+        <v>1.097277739618091</v>
       </c>
       <c r="N103" t="n">
-        <v>0.9576391167704899</v>
+        <v>0.9503662260069059</v>
       </c>
       <c r="O103" t="n">
-        <v>0.8290207015115383</v>
+        <v>0.8227726625173045</v>
       </c>
       <c r="P103" t="n">
-        <v>0.751022681444752</v>
+        <v>0.7454411312938066</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.7358726743103842</v>
+        <v>0.7305176375661884</v>
       </c>
       <c r="R103" t="n">
-        <v>0.7337473589682139</v>
+        <v>0.7285577418386263</v>
       </c>
       <c r="S103" t="n">
-        <v>0.7309497754018079</v>
+        <v>0.7259450796978754</v>
       </c>
       <c r="T103" t="n">
-        <v>0.7303548599279336</v>
+        <v>0.7255173516020317</v>
       </c>
       <c r="U103" t="n">
-        <v>0.7367328506509886</v>
+        <v>0.7320310094588774</v>
       </c>
       <c r="V103" t="n">
-        <v>0.7479226745106281</v>
+        <v>0.7434135992560081</v>
       </c>
     </row>
     <row r="104">
@@ -8278,58 +8278,58 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1.83664692729623</v>
+        <v>1.832919330608252</v>
       </c>
       <c r="F104" t="n">
-        <v>1.850032020437088</v>
+        <v>1.846572325943553</v>
       </c>
       <c r="G104" t="n">
-        <v>1.786257279169298</v>
+        <v>1.783921893636427</v>
       </c>
       <c r="H104" t="n">
-        <v>1.687896858874313</v>
+        <v>1.687173619606023</v>
       </c>
       <c r="I104" t="n">
-        <v>1.600003607243345</v>
+        <v>1.600666812129488</v>
       </c>
       <c r="J104" t="n">
-        <v>1.476074878992968</v>
+        <v>1.477731798727466</v>
       </c>
       <c r="K104" t="n">
-        <v>1.238434696088463</v>
+        <v>1.240495618011484</v>
       </c>
       <c r="L104" t="n">
-        <v>0.9971669924887563</v>
+        <v>0.9992187381928388</v>
       </c>
       <c r="M104" t="n">
-        <v>0.8428640508861567</v>
+        <v>0.8448244956914533</v>
       </c>
       <c r="N104" t="n">
-        <v>0.7252691162101179</v>
+        <v>0.7270764702840361</v>
       </c>
       <c r="O104" t="n">
-        <v>0.6235362067521384</v>
+        <v>0.6251428287408152</v>
       </c>
       <c r="P104" t="n">
-        <v>0.5603809693147044</v>
+        <v>0.5618345670462946</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.5441278263123389</v>
+        <v>0.54551601640519</v>
       </c>
       <c r="R104" t="n">
-        <v>0.537247731550821</v>
+        <v>0.5385705322089673</v>
       </c>
       <c r="S104" t="n">
-        <v>0.529173651484348</v>
+        <v>0.5304161564282118</v>
       </c>
       <c r="T104" t="n">
-        <v>0.5213714964213005</v>
+        <v>0.5225306609897092</v>
       </c>
       <c r="U104" t="n">
-        <v>0.5164612316390776</v>
+        <v>0.5175517427154201</v>
       </c>
       <c r="V104" t="n">
-        <v>0.5127478333481262</v>
+        <v>0.5137755273882634</v>
       </c>
     </row>
     <row r="105">
@@ -8354,58 +8354,58 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2.147069231074182</v>
+        <v>2.150996262377375</v>
       </c>
       <c r="F105" t="n">
-        <v>2.040842067979248</v>
+        <v>2.04464234129079</v>
       </c>
       <c r="G105" t="n">
-        <v>1.938344999484273</v>
+        <v>1.941905123296564</v>
       </c>
       <c r="H105" t="n">
-        <v>1.817099275796573</v>
+        <v>1.820180695357176</v>
       </c>
       <c r="I105" t="n">
-        <v>1.711749168553986</v>
+        <v>1.714113670790788</v>
       </c>
       <c r="J105" t="n">
-        <v>1.570051467727688</v>
+        <v>1.571426268740017</v>
       </c>
       <c r="K105" t="n">
-        <v>1.311936757611384</v>
+        <v>1.312330644180484</v>
       </c>
       <c r="L105" t="n">
-        <v>1.054599597134867</v>
+        <v>1.054356280057798</v>
       </c>
       <c r="M105" t="n">
-        <v>0.8918673737036033</v>
+        <v>0.8912831837448338</v>
       </c>
       <c r="N105" t="n">
-        <v>0.7691192835166306</v>
+        <v>0.7683575683386943</v>
       </c>
       <c r="O105" t="n">
-        <v>0.6635735565121214</v>
+        <v>0.6627186076268522</v>
       </c>
       <c r="P105" t="n">
-        <v>0.5994316209226269</v>
+        <v>0.5984788879765103</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.5860649434361577</v>
+        <v>0.5849510340707936</v>
       </c>
       <c r="R105" t="n">
-        <v>0.5836154085616448</v>
+        <v>0.5823263637999332</v>
       </c>
       <c r="S105" t="n">
-        <v>0.580699292641261</v>
+        <v>0.5792570732326179</v>
       </c>
       <c r="T105" t="n">
-        <v>0.5790205190020705</v>
+        <v>0.5774512891374579</v>
       </c>
       <c r="U105" t="n">
-        <v>0.582009370128545</v>
+        <v>0.5803352054961938</v>
       </c>
       <c r="V105" t="n">
-        <v>0.5889621811412504</v>
+        <v>0.5871954506229842</v>
       </c>
     </row>
     <row r="106">
@@ -8430,58 +8430,58 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1.773894856726093</v>
+        <v>1.769263696499491</v>
       </c>
       <c r="F106" t="n">
-        <v>1.806148902770003</v>
+        <v>1.803400066189381</v>
       </c>
       <c r="G106" t="n">
-        <v>1.754194840388528</v>
+        <v>1.754972627545418</v>
       </c>
       <c r="H106" t="n">
-        <v>1.666400969236334</v>
+        <v>1.669671625351289</v>
       </c>
       <c r="I106" t="n">
-        <v>1.585669053043206</v>
+        <v>1.590345726616914</v>
       </c>
       <c r="J106" t="n">
-        <v>1.464418304459931</v>
+        <v>1.469583899257173</v>
       </c>
       <c r="K106" t="n">
-        <v>1.227358811939008</v>
+        <v>1.232067680958401</v>
       </c>
       <c r="L106" t="n">
-        <v>0.9859438231161455</v>
+        <v>0.9898560604803645</v>
       </c>
       <c r="M106" t="n">
-        <v>0.8312529784063691</v>
+        <v>0.8345834073658556</v>
       </c>
       <c r="N106" t="n">
-        <v>0.7135916543960007</v>
+        <v>0.7164416675253363</v>
       </c>
       <c r="O106" t="n">
-        <v>0.6122003838326036</v>
+        <v>0.6146147907815392</v>
       </c>
       <c r="P106" t="n">
-        <v>0.5490731855404081</v>
+        <v>0.551192951493494</v>
       </c>
       <c r="Q106" t="n">
-        <v>0.5320735649428245</v>
+        <v>0.5340688548326602</v>
       </c>
       <c r="R106" t="n">
-        <v>0.5242687965138921</v>
+        <v>0.5261672242345529</v>
       </c>
       <c r="S106" t="n">
-        <v>0.5152536573587324</v>
+        <v>0.5170574959567206</v>
       </c>
       <c r="T106" t="n">
-        <v>0.5063130099227009</v>
+        <v>0.5080462184024006</v>
       </c>
       <c r="U106" t="n">
-        <v>0.4997760323397721</v>
+        <v>0.5014657531001868</v>
       </c>
       <c r="V106" t="n">
-        <v>0.4939393256066523</v>
+        <v>0.4955677877003343</v>
       </c>
     </row>
     <row r="107">
@@ -8506,58 +8506,58 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3.851931477918734</v>
+        <v>3.886409497909765</v>
       </c>
       <c r="F107" t="n">
-        <v>3.521044040725615</v>
+        <v>3.566711969809895</v>
       </c>
       <c r="G107" t="n">
-        <v>3.192887919142489</v>
+        <v>3.238870820005014</v>
       </c>
       <c r="H107" t="n">
-        <v>2.892877697735286</v>
+        <v>2.936125795431512</v>
       </c>
       <c r="I107" t="n">
-        <v>2.665295913826702</v>
+        <v>2.705817283482196</v>
       </c>
       <c r="J107" t="n">
-        <v>2.410675935532046</v>
+        <v>2.447807785582597</v>
       </c>
       <c r="K107" t="n">
-        <v>1.992336108993088</v>
+        <v>2.023449669462458</v>
       </c>
       <c r="L107" t="n">
-        <v>1.582891266639944</v>
+        <v>1.608004506733016</v>
       </c>
       <c r="M107" t="n">
-        <v>1.319759718197725</v>
+        <v>1.341051111378554</v>
       </c>
       <c r="N107" t="n">
-        <v>1.118534952470899</v>
+        <v>1.136898341930112</v>
       </c>
       <c r="O107" t="n">
-        <v>0.9460355929900829</v>
+        <v>0.9618540959108817</v>
       </c>
       <c r="P107" t="n">
-        <v>0.8343419818294366</v>
+        <v>0.8485931746582118</v>
       </c>
       <c r="Q107" t="n">
-        <v>0.7921737627832206</v>
+        <v>0.8060448335628597</v>
       </c>
       <c r="R107" t="n">
-        <v>0.761347312872924</v>
+        <v>0.7750564993139184</v>
       </c>
       <c r="S107" t="n">
-        <v>0.7254444163340752</v>
+        <v>0.7389263789426944</v>
       </c>
       <c r="T107" t="n">
-        <v>0.6855219210023626</v>
+        <v>0.6987291738338535</v>
       </c>
       <c r="U107" t="n">
-        <v>0.643739685922381</v>
+        <v>0.6566758370435453</v>
       </c>
       <c r="V107" t="n">
-        <v>0.5956734364627885</v>
+        <v>0.6082460150072684</v>
       </c>
     </row>
     <row r="108">
@@ -8582,58 +8582,58 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2.513505644990831</v>
+        <v>2.525909864357265</v>
       </c>
       <c r="F108" t="n">
-        <v>2.314808631813332</v>
+        <v>2.330284158905627</v>
       </c>
       <c r="G108" t="n">
-        <v>2.139985718249258</v>
+        <v>2.15474527087569</v>
       </c>
       <c r="H108" t="n">
-        <v>1.973511441631603</v>
+        <v>1.9867318450592</v>
       </c>
       <c r="I108" t="n">
-        <v>1.840305468775002</v>
+        <v>1.852101842788582</v>
       </c>
       <c r="J108" t="n">
-        <v>1.677321944012824</v>
+        <v>1.687682438945796</v>
       </c>
       <c r="K108" t="n">
-        <v>1.394237038851472</v>
+        <v>1.40262040964968</v>
       </c>
       <c r="L108" t="n">
-        <v>1.11449514188872</v>
+        <v>1.121084762844062</v>
       </c>
       <c r="M108" t="n">
-        <v>0.9364779968425146</v>
+        <v>0.9419444267601964</v>
       </c>
       <c r="N108" t="n">
-        <v>0.8018234199755488</v>
+        <v>0.8064543666613512</v>
       </c>
       <c r="O108" t="n">
-        <v>0.6863702651635238</v>
+        <v>0.6902972574829543</v>
       </c>
       <c r="P108" t="n">
-        <v>0.6144203307140983</v>
+        <v>0.6179250047163044</v>
       </c>
       <c r="Q108" t="n">
-        <v>0.5942196773625035</v>
+        <v>0.5976218205741414</v>
       </c>
       <c r="R108" t="n">
-        <v>0.5840299672623918</v>
+        <v>0.587401388508172</v>
       </c>
       <c r="S108" t="n">
-        <v>0.5719392338740511</v>
+        <v>0.575273536521736</v>
       </c>
       <c r="T108" t="n">
-        <v>0.5592187950387991</v>
+        <v>0.5624983220201941</v>
       </c>
       <c r="U108" t="n">
-        <v>0.5484218555860343</v>
+        <v>0.5516308578525557</v>
       </c>
       <c r="V108" t="n">
-        <v>0.5374467419975967</v>
+        <v>0.5405557032941153</v>
       </c>
     </row>
     <row r="109">
@@ -8658,58 +8658,58 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1.874415918556224</v>
+        <v>1.856319111522444</v>
       </c>
       <c r="F109" t="n">
-        <v>2.04377620877746</v>
+        <v>2.022241633585365</v>
       </c>
       <c r="G109" t="n">
-        <v>1.986238817368536</v>
+        <v>1.968229053022038</v>
       </c>
       <c r="H109" t="n">
-        <v>1.846606589210241</v>
+        <v>1.833928603654817</v>
       </c>
       <c r="I109" t="n">
-        <v>1.722813868054081</v>
+        <v>1.714922320730327</v>
       </c>
       <c r="J109" t="n">
-        <v>1.575785600025637</v>
+        <v>1.57149532169521</v>
       </c>
       <c r="K109" t="n">
-        <v>1.317736698163204</v>
+        <v>1.315932161031144</v>
       </c>
       <c r="L109" t="n">
-        <v>1.060404768662569</v>
+        <v>1.0599313684661</v>
       </c>
       <c r="M109" t="n">
-        <v>0.8968237723949742</v>
+        <v>0.8969680378221316</v>
       </c>
       <c r="N109" t="n">
-        <v>0.7725542324019037</v>
+        <v>0.7729867082619117</v>
       </c>
       <c r="O109" t="n">
-        <v>0.6651025173984325</v>
+        <v>0.6656499369356994</v>
       </c>
       <c r="P109" t="n">
-        <v>0.5987277426947094</v>
+        <v>0.5993247796424436</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.5824386313369421</v>
+        <v>0.5830792372388103</v>
       </c>
       <c r="R109" t="n">
-        <v>0.5761884290247421</v>
+        <v>0.5768408348806532</v>
       </c>
       <c r="S109" t="n">
-        <v>0.5686785463132742</v>
+        <v>0.5693135969289254</v>
       </c>
       <c r="T109" t="n">
-        <v>0.5615013327229355</v>
+        <v>0.5621067805235169</v>
       </c>
       <c r="U109" t="n">
-        <v>0.5575628560916589</v>
+        <v>0.5581430735579338</v>
       </c>
       <c r="V109" t="n">
-        <v>0.5551921885445429</v>
+        <v>0.5557463743504565</v>
       </c>
     </row>
     <row r="110">
@@ -8734,58 +8734,58 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1.316678761487608</v>
+        <v>1.314416685574415</v>
       </c>
       <c r="F110" t="n">
-        <v>1.324458693402608</v>
+        <v>1.322879984762713</v>
       </c>
       <c r="G110" t="n">
-        <v>1.278738828286867</v>
+        <v>1.278399798562589</v>
       </c>
       <c r="H110" t="n">
-        <v>1.206999275459937</v>
+        <v>1.207381388422651</v>
       </c>
       <c r="I110" t="n">
-        <v>1.141290622949894</v>
+        <v>1.141827001079281</v>
       </c>
       <c r="J110" t="n">
-        <v>1.04939983426028</v>
+        <v>1.04972627316298</v>
       </c>
       <c r="K110" t="n">
-        <v>0.8780196389469133</v>
+        <v>0.8779697108219211</v>
       </c>
       <c r="L110" t="n">
-        <v>0.7062239244484372</v>
+        <v>0.7058638620429485</v>
       </c>
       <c r="M110" t="n">
-        <v>0.5975056898090916</v>
+        <v>0.5969411184052753</v>
       </c>
       <c r="N110" t="n">
-        <v>0.5154907928263978</v>
+        <v>0.5148244689035076</v>
       </c>
       <c r="O110" t="n">
-        <v>0.4448630750544241</v>
+        <v>0.4441718141339568</v>
       </c>
       <c r="P110" t="n">
-        <v>0.4018458400891228</v>
+        <v>0.4011324715935278</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.392769538124578</v>
+        <v>0.3919841994590869</v>
       </c>
       <c r="R110" t="n">
-        <v>0.3909569287283308</v>
+        <v>0.3900828785066757</v>
       </c>
       <c r="S110" t="n">
-        <v>0.3888060610077961</v>
+        <v>0.3878505229181688</v>
       </c>
       <c r="T110" t="n">
-        <v>0.3874748301284365</v>
+        <v>0.3864486481138306</v>
       </c>
       <c r="U110" t="n">
-        <v>0.3893130373423951</v>
+        <v>0.3882225025267196</v>
       </c>
       <c r="V110" t="n">
-        <v>0.3936859439035447</v>
+        <v>0.3925421027382144</v>
       </c>
     </row>
     <row r="111">
@@ -8810,58 +8810,58 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1.759416684514527</v>
+        <v>1.755256808400988</v>
       </c>
       <c r="F111" t="n">
-        <v>1.779947372327761</v>
+        <v>1.776271821742574</v>
       </c>
       <c r="G111" t="n">
-        <v>1.71940411863926</v>
+        <v>1.716832598643137</v>
       </c>
       <c r="H111" t="n">
-        <v>1.623153025288113</v>
+        <v>1.621418632729828</v>
       </c>
       <c r="I111" t="n">
-        <v>1.536090922908405</v>
+        <v>1.534905617397677</v>
       </c>
       <c r="J111" t="n">
-        <v>1.414412620968429</v>
+        <v>1.413564100301425</v>
       </c>
       <c r="K111" t="n">
-        <v>1.184979942565276</v>
+        <v>1.184356022667357</v>
       </c>
       <c r="L111" t="n">
-        <v>0.9536494531785884</v>
+        <v>0.9531649986533453</v>
       </c>
       <c r="M111" t="n">
-        <v>0.8064850322008642</v>
+        <v>0.8061006852863912</v>
       </c>
       <c r="N111" t="n">
-        <v>0.6949258737257062</v>
+        <v>0.6946216819920008</v>
       </c>
       <c r="O111" t="n">
-        <v>0.5987185313044523</v>
+        <v>0.5984571508310014</v>
       </c>
       <c r="P111" t="n">
-        <v>0.5397875290386388</v>
+        <v>0.5395047797229994</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.5264968853116589</v>
+        <v>0.5261238714152378</v>
       </c>
       <c r="R111" t="n">
-        <v>0.5229437655843713</v>
+        <v>0.5224402976816028</v>
       </c>
       <c r="S111" t="n">
-        <v>0.5189870047609075</v>
+        <v>0.5183421702124785</v>
       </c>
       <c r="T111" t="n">
-        <v>0.5159558757859343</v>
+        <v>0.5151941492434043</v>
       </c>
       <c r="U111" t="n">
-        <v>0.5165902627058471</v>
+        <v>0.5157477231140976</v>
       </c>
       <c r="V111" t="n">
-        <v>0.5200869994911943</v>
+        <v>0.5191740387655495</v>
       </c>
     </row>
     <row r="112">
@@ -8886,58 +8886,58 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1.815455449759325</v>
+        <v>1.816750210508667</v>
       </c>
       <c r="F112" t="n">
-        <v>1.780982772630746</v>
+        <v>1.783957189851469</v>
       </c>
       <c r="G112" t="n">
-        <v>1.713837480446412</v>
+        <v>1.718603518567971</v>
       </c>
       <c r="H112" t="n">
-        <v>1.621794841590932</v>
+        <v>1.627738838674746</v>
       </c>
       <c r="I112" t="n">
-        <v>1.53959281564648</v>
+        <v>1.546187982936819</v>
       </c>
       <c r="J112" t="n">
-        <v>1.419688088419228</v>
+        <v>1.426327610026732</v>
       </c>
       <c r="K112" t="n">
-        <v>1.188590275100912</v>
+        <v>1.194417195952953</v>
       </c>
       <c r="L112" t="n">
-        <v>0.9541436049317208</v>
+        <v>0.9589376865741794</v>
       </c>
       <c r="M112" t="n">
-        <v>0.8039864577601999</v>
+        <v>0.8080789849521841</v>
       </c>
       <c r="N112" t="n">
-        <v>0.6899814142342698</v>
+        <v>0.6935371026742916</v>
       </c>
       <c r="O112" t="n">
-        <v>0.5918956188468966</v>
+        <v>0.5949921977831841</v>
       </c>
       <c r="P112" t="n">
-        <v>0.5307937706469945</v>
+        <v>0.5336269617596167</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.5140330564559206</v>
+        <v>0.5168406307778813</v>
       </c>
       <c r="R112" t="n">
-        <v>0.5056941561715026</v>
+        <v>0.5085205939413104</v>
       </c>
       <c r="S112" t="n">
-        <v>0.4955490165563881</v>
+        <v>0.4983799102865215</v>
       </c>
       <c r="T112" t="n">
-        <v>0.4847418335989478</v>
+        <v>0.4875600242160734</v>
       </c>
       <c r="U112" t="n">
-        <v>0.4754577219008971</v>
+        <v>0.4782551220627193</v>
       </c>
       <c r="V112" t="n">
-        <v>0.4657787944133827</v>
+        <v>0.4685248200330722</v>
       </c>
     </row>
     <row r="113">
@@ -8962,19 +8962,19 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1.660651666436225</v>
+        <v>1.661685157177115</v>
       </c>
       <c r="F113" t="n">
-        <v>1.747042172330555</v>
+        <v>1.748118599175922</v>
       </c>
       <c r="G113" t="n">
-        <v>1.600598340631877</v>
+        <v>1.600758922516438</v>
       </c>
       <c r="H113" t="n">
-        <v>1.511571485455025</v>
+        <v>1.510429647409834</v>
       </c>
       <c r="I113" t="n">
-        <v>1.488425822304078</v>
+        <v>1.484295797859838</v>
       </c>
       <c r="J113" t="n">
         <v>1.952529400284762</v>
@@ -9038,19 +9038,19 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.656362415733566</v>
+        <v>0.6541596524878041</v>
       </c>
       <c r="F114" t="n">
-        <v>1.013725196412725</v>
+        <v>1.011125857727027</v>
       </c>
       <c r="G114" t="n">
-        <v>1.440823539924344</v>
+        <v>1.43885868036365</v>
       </c>
       <c r="H114" t="n">
-        <v>1.854255321388941</v>
+        <v>1.852897908362689</v>
       </c>
       <c r="I114" t="n">
-        <v>2.18176708335215</v>
+        <v>2.181026223454542</v>
       </c>
       <c r="J114" t="n">
         <v>2.001298496452635</v>
@@ -9114,19 +9114,19 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1.35802593563278</v>
+        <v>1.35797355941607</v>
       </c>
       <c r="F115" t="n">
-        <v>1.658985653425532</v>
+        <v>1.658946784486053</v>
       </c>
       <c r="G115" t="n">
-        <v>1.909389164029489</v>
+        <v>1.909495866931278</v>
       </c>
       <c r="H115" t="n">
-        <v>2.131346130354013</v>
+        <v>2.131687956910435</v>
       </c>
       <c r="I115" t="n">
-        <v>2.308657713533755</v>
+        <v>2.309600184636079</v>
       </c>
       <c r="J115" t="n">
         <v>1.942837716972758</v>
@@ -9190,58 +9190,58 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.4712947118637371</v>
+        <v>0.4700891027255532</v>
       </c>
       <c r="F116" t="n">
-        <v>0.5061099285727826</v>
+        <v>0.5039724930917816</v>
       </c>
       <c r="G116" t="n">
-        <v>0.5384877530062792</v>
+        <v>0.5356584746681635</v>
       </c>
       <c r="H116" t="n">
-        <v>0.5566951587668046</v>
+        <v>0.553342398450689</v>
       </c>
       <c r="I116" t="n">
-        <v>0.5653601189726316</v>
+        <v>0.5615962343547134</v>
       </c>
       <c r="J116" t="n">
-        <v>0.5172750363653633</v>
+        <v>0.5135406197213724</v>
       </c>
       <c r="K116" t="n">
-        <v>0.4585951318428395</v>
+        <v>0.4550536054804388</v>
       </c>
       <c r="L116" t="n">
-        <v>0.3959387723547905</v>
+        <v>0.3926918517754986</v>
       </c>
       <c r="M116" t="n">
-        <v>0.3562954539830079</v>
+        <v>0.353213102042189</v>
       </c>
       <c r="N116" t="n">
-        <v>0.3219131188309953</v>
+        <v>0.3190556150240597</v>
       </c>
       <c r="O116" t="n">
-        <v>0.2874620921371803</v>
+        <v>0.2848763907813895</v>
       </c>
       <c r="P116" t="n">
-        <v>0.2576157990350987</v>
+        <v>0.2552562373200329</v>
       </c>
       <c r="Q116" t="n">
-        <v>0.2457079267898455</v>
+        <v>0.2433839176034384</v>
       </c>
       <c r="R116" t="n">
-        <v>0.2343086115326252</v>
+        <v>0.2319890276642932</v>
       </c>
       <c r="S116" t="n">
-        <v>0.2246682748010408</v>
+        <v>0.2223050770195066</v>
       </c>
       <c r="T116" t="n">
-        <v>0.2149038223412707</v>
+        <v>0.2124514852112857</v>
       </c>
       <c r="U116" t="n">
-        <v>0.2064744114039883</v>
+        <v>0.203846207919179</v>
       </c>
       <c r="V116" t="n">
-        <v>0.2012934975760399</v>
+        <v>0.1983226368545451</v>
       </c>
     </row>
     <row r="117">
@@ -9266,58 +9266,58 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1.728139365483535</v>
+        <v>1.728370334689065</v>
       </c>
       <c r="F117" t="n">
-        <v>2.262516756068225</v>
+        <v>2.263529650978898</v>
       </c>
       <c r="G117" t="n">
-        <v>2.615640870227403</v>
+        <v>2.617368469239691</v>
       </c>
       <c r="H117" t="n">
-        <v>2.807682386833655</v>
+        <v>2.809953490548768</v>
       </c>
       <c r="I117" t="n">
-        <v>2.890312055581373</v>
+        <v>2.892946249173313</v>
       </c>
       <c r="J117" t="n">
-        <v>2.648614264368807</v>
+        <v>2.651221710540824</v>
       </c>
       <c r="K117" t="n">
-        <v>2.336682535020195</v>
+        <v>2.339104686147959</v>
       </c>
       <c r="L117" t="n">
-        <v>2.002157651864099</v>
+        <v>2.004318332861798</v>
       </c>
       <c r="M117" t="n">
-        <v>1.781156165201507</v>
+        <v>1.783136485301099</v>
       </c>
       <c r="N117" t="n">
-        <v>1.566407678733585</v>
+        <v>1.56810363232115</v>
       </c>
       <c r="O117" t="n">
-        <v>1.354233871646201</v>
+        <v>1.355623681279298</v>
       </c>
       <c r="P117" t="n">
-        <v>1.178791772246446</v>
+        <v>1.179946165709465</v>
       </c>
       <c r="Q117" t="n">
-        <v>1.098752699297358</v>
+        <v>1.099804207056899</v>
       </c>
       <c r="R117" t="n">
-        <v>1.027167816645415</v>
+        <v>1.028147324047118</v>
       </c>
       <c r="S117" t="n">
-        <v>0.9663190379481533</v>
+        <v>0.9672530377058268</v>
       </c>
       <c r="T117" t="n">
-        <v>0.9072494383417014</v>
+        <v>0.9081593289787171</v>
       </c>
       <c r="U117" t="n">
-        <v>0.8558528445652345</v>
+        <v>0.856773353540197</v>
       </c>
       <c r="V117" t="n">
-        <v>0.8193823160844796</v>
+        <v>0.8203760659448761</v>
       </c>
     </row>
     <row r="118">
@@ -9342,58 +9342,58 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1.280658840705457</v>
+        <v>1.280885244874404</v>
       </c>
       <c r="F118" t="n">
-        <v>1.330508683551112</v>
+        <v>1.330866815650235</v>
       </c>
       <c r="G118" t="n">
-        <v>1.356320088718499</v>
+        <v>1.356708348396801</v>
       </c>
       <c r="H118" t="n">
-        <v>1.349513938551014</v>
+        <v>1.349874557971215</v>
       </c>
       <c r="I118" t="n">
-        <v>1.326913311312337</v>
+        <v>1.327213252463124</v>
       </c>
       <c r="J118" t="n">
-        <v>1.179841893438866</v>
+        <v>1.180040606603133</v>
       </c>
       <c r="K118" t="n">
-        <v>1.018520434934701</v>
+        <v>1.018618577036692</v>
       </c>
       <c r="L118" t="n">
-        <v>0.8572218571650065</v>
+        <v>0.8572331780404548</v>
       </c>
       <c r="M118" t="n">
-        <v>0.7528695551063621</v>
+        <v>0.7528114166885205</v>
       </c>
       <c r="N118" t="n">
-        <v>0.6567065101619775</v>
+        <v>0.6565596699233974</v>
       </c>
       <c r="O118" t="n">
-        <v>0.5652010576584646</v>
+        <v>0.5649810127528133</v>
       </c>
       <c r="P118" t="n">
-        <v>0.4905538355367458</v>
+        <v>0.4902855757223815</v>
       </c>
       <c r="Q118" t="n">
-        <v>0.4561929623201388</v>
+        <v>0.4558780303454454</v>
       </c>
       <c r="R118" t="n">
-        <v>0.4256914368780879</v>
+        <v>0.425334924338429</v>
       </c>
       <c r="S118" t="n">
-        <v>0.4000043709531431</v>
+        <v>0.3996033218108576</v>
       </c>
       <c r="T118" t="n">
-        <v>0.3755570771880544</v>
+        <v>0.3751066246322181</v>
       </c>
       <c r="U118" t="n">
-        <v>0.3546403030269278</v>
+        <v>0.3541276521704577</v>
       </c>
       <c r="V118" t="n">
-        <v>0.3398990927916501</v>
+        <v>0.3392928793523454</v>
       </c>
     </row>
     <row r="119">
@@ -9418,58 +9418,58 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1.179725367349123</v>
+        <v>1.179609256739194</v>
       </c>
       <c r="F119" t="n">
-        <v>1.444281649716632</v>
+        <v>1.44439449843681</v>
       </c>
       <c r="G119" t="n">
-        <v>1.708425771904472</v>
+        <v>1.708936458389228</v>
       </c>
       <c r="H119" t="n">
-        <v>1.898980626159466</v>
+        <v>1.899888163041528</v>
       </c>
       <c r="I119" t="n">
-        <v>2.008728733472081</v>
+        <v>2.009934924895737</v>
       </c>
       <c r="J119" t="n">
-        <v>1.870907799697692</v>
+        <v>1.872175827250727</v>
       </c>
       <c r="K119" t="n">
-        <v>1.661766487374392</v>
+        <v>1.662961720611061</v>
       </c>
       <c r="L119" t="n">
-        <v>1.425488186665997</v>
+        <v>1.426543713706791</v>
       </c>
       <c r="M119" t="n">
-        <v>1.268177699057604</v>
+        <v>1.269126834254208</v>
       </c>
       <c r="N119" t="n">
-        <v>1.116955977743331</v>
+        <v>1.117734021701533</v>
       </c>
       <c r="O119" t="n">
-        <v>0.9695340724226497</v>
+        <v>0.9701379725647008</v>
       </c>
       <c r="P119" t="n">
-        <v>0.8473836474672802</v>
+        <v>0.8478571055210998</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.7921334711302093</v>
+        <v>0.7925405450930919</v>
       </c>
       <c r="R119" t="n">
-        <v>0.7419938927743102</v>
+        <v>0.7423507445979707</v>
       </c>
       <c r="S119" t="n">
-        <v>0.6991681438187725</v>
+        <v>0.6994852993149256</v>
       </c>
       <c r="T119" t="n">
-        <v>0.657676321115656</v>
+        <v>0.6579634329126454</v>
       </c>
       <c r="U119" t="n">
-        <v>0.6216162725057791</v>
+        <v>0.6218853620180153</v>
       </c>
       <c r="V119" t="n">
-        <v>0.5957866565675692</v>
+        <v>0.5960568074228365</v>
       </c>
     </row>
     <row r="120">
@@ -9494,58 +9494,58 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.002698070333858911</v>
+        <v>0.001980664349133421</v>
       </c>
       <c r="F120" t="n">
-        <v>0.004795526426036103</v>
+        <v>0.003521834607280914</v>
       </c>
       <c r="G120" t="n">
-        <v>0.00636381096698773</v>
+        <v>0.00467455791325073</v>
       </c>
       <c r="H120" t="n">
-        <v>0.007550484716020205</v>
+        <v>0.005547081470238033</v>
       </c>
       <c r="I120" t="n">
-        <v>0.008476782402134652</v>
+        <v>0.006228534408548076</v>
       </c>
       <c r="J120" t="n">
-        <v>0.008402621582721146</v>
+        <v>0.006173953487007261</v>
       </c>
       <c r="K120" t="n">
-        <v>0.007956174677049316</v>
+        <v>0.005848627031158159</v>
       </c>
       <c r="L120" t="n">
-        <v>0.007285569632757897</v>
+        <v>0.005354857361185564</v>
       </c>
       <c r="M120" t="n">
-        <v>0.006907579056626202</v>
+        <v>0.005078121602384383</v>
       </c>
       <c r="N120" t="n">
-        <v>0.006391934277580979</v>
+        <v>0.004699013815854317</v>
       </c>
       <c r="O120" t="n">
-        <v>0.005774412934684974</v>
+        <v>0.004244776781027262</v>
       </c>
       <c r="P120" t="n">
-        <v>0.00526179845762149</v>
+        <v>0.003868491937566879</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.005177112535342881</v>
+        <v>0.003805463160772931</v>
       </c>
       <c r="R120" t="n">
-        <v>0.005162900259220618</v>
+        <v>0.003795346321510394</v>
       </c>
       <c r="S120" t="n">
-        <v>0.005256731045319585</v>
+        <v>0.003865243415676165</v>
       </c>
       <c r="T120" t="n">
-        <v>0.005453363665908353</v>
+        <v>0.0040103997400065</v>
       </c>
       <c r="U120" t="n">
-        <v>0.005844095902251538</v>
+        <v>0.004299992447320058</v>
       </c>
       <c r="V120" t="n">
-        <v>0.006609461160288994</v>
+        <v>0.004864090564568282</v>
       </c>
     </row>
     <row r="121">
@@ -9570,58 +9570,58 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.00278560276314779</v>
+        <v>0.002044874974577106</v>
       </c>
       <c r="F121" t="n">
-        <v>0.004464760503361929</v>
+        <v>0.003278747483113289</v>
       </c>
       <c r="G121" t="n">
-        <v>0.005470222034949343</v>
+        <v>0.004018182843161662</v>
       </c>
       <c r="H121" t="n">
-        <v>0.006199940926516409</v>
+        <v>0.004555071224245534</v>
       </c>
       <c r="I121" t="n">
-        <v>0.006836988729487673</v>
+        <v>0.005023783487823706</v>
       </c>
       <c r="J121" t="n">
-        <v>0.006775837158659724</v>
+        <v>0.004979529890184885</v>
       </c>
       <c r="K121" t="n">
-        <v>0.006482897318363912</v>
+        <v>0.004764678062167754</v>
       </c>
       <c r="L121" t="n">
-        <v>0.006024610395392788</v>
+        <v>0.004428348754519802</v>
       </c>
       <c r="M121" t="n">
-        <v>0.005800092794006342</v>
+        <v>0.00426370490301136</v>
       </c>
       <c r="N121" t="n">
-        <v>0.005495779062432397</v>
+        <v>0.00404017529083611</v>
       </c>
       <c r="O121" t="n">
-        <v>0.005088516777503048</v>
+        <v>0.003740813721022403</v>
       </c>
       <c r="P121" t="n">
-        <v>0.004736606443909564</v>
+        <v>0.003482156836094427</v>
       </c>
       <c r="Q121" t="n">
-        <v>0.004737270085676398</v>
+        <v>0.003482814385994985</v>
       </c>
       <c r="R121" t="n">
-        <v>0.004790020335034646</v>
+        <v>0.003521920837266706</v>
       </c>
       <c r="S121" t="n">
-        <v>0.004938236225715523</v>
+        <v>0.003631422657267581</v>
       </c>
       <c r="T121" t="n">
-        <v>0.005177520933956044</v>
+        <v>0.003808055335988355</v>
       </c>
       <c r="U121" t="n">
-        <v>0.005595234505125808</v>
+        <v>0.004116547363971624</v>
       </c>
       <c r="V121" t="n">
-        <v>0.006368150808577864</v>
+        <v>0.004687274749796765</v>
       </c>
     </row>
     <row r="122">
@@ -9646,58 +9646,58 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1.483943398496686</v>
+        <v>1.484073159274508</v>
       </c>
       <c r="F122" t="n">
-        <v>1.538845721859883</v>
+        <v>1.539016078938244</v>
       </c>
       <c r="G122" t="n">
-        <v>1.601300300991332</v>
+        <v>1.601482453518426</v>
       </c>
       <c r="H122" t="n">
-        <v>1.635773910031606</v>
+        <v>1.635963419719581</v>
       </c>
       <c r="I122" t="n">
-        <v>1.654869376206274</v>
+        <v>1.655070680206149</v>
       </c>
       <c r="J122" t="n">
-        <v>1.515722998591258</v>
+        <v>1.515921619779401</v>
       </c>
       <c r="K122" t="n">
-        <v>1.348800781785002</v>
+        <v>1.348993552283194</v>
       </c>
       <c r="L122" t="n">
-        <v>1.169752085682192</v>
+        <v>1.169935012447864</v>
       </c>
       <c r="M122" t="n">
-        <v>1.057177076027553</v>
+        <v>1.057357705165958</v>
       </c>
       <c r="N122" t="n">
-        <v>0.9628508630715213</v>
+        <v>0.9630309247197816</v>
       </c>
       <c r="O122" t="n">
-        <v>0.8671809551117257</v>
+        <v>0.8673555395756563</v>
       </c>
       <c r="P122" t="n">
-        <v>0.7824299081273721</v>
+        <v>0.7825973028189002</v>
       </c>
       <c r="Q122" t="n">
-        <v>0.7495131263802756</v>
+        <v>0.7496829103005509</v>
       </c>
       <c r="R122" t="n">
-        <v>0.7166664035912945</v>
+        <v>0.7168390231274823</v>
       </c>
       <c r="S122" t="n">
-        <v>0.6880953893356793</v>
+        <v>0.6882735358572764</v>
       </c>
       <c r="T122" t="n">
-        <v>0.6578920161565831</v>
+        <v>0.6580781456308046</v>
       </c>
       <c r="U122" t="n">
-        <v>0.6302818505344325</v>
+        <v>0.6304813919008675</v>
       </c>
       <c r="V122" t="n">
-        <v>0.6105086082728225</v>
+        <v>0.6107329406531687</v>
       </c>
     </row>
     <row r="123">
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2.236948303453394</v>
+        <v>2.236226430410279</v>
       </c>
       <c r="F123" t="n">
-        <v>2.040816824634911</v>
+        <v>2.040393768051092</v>
       </c>
       <c r="G123" t="n">
-        <v>1.724945884130777</v>
+        <v>1.724562988829668</v>
       </c>
       <c r="H123" t="n">
-        <v>1.456754748761535</v>
+        <v>1.45648370211005</v>
       </c>
       <c r="I123" t="n">
-        <v>1.240478618125113</v>
+        <v>1.240337902366332</v>
       </c>
       <c r="J123" t="n">
         <v>1.028126963826996</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1.24738381905063</v>
+        <v>1.245424995113615</v>
       </c>
       <c r="F124" t="n">
-        <v>1.101187860862591</v>
+        <v>1.100164433913859</v>
       </c>
       <c r="G124" t="n">
-        <v>0.9469347919239078</v>
+        <v>0.9462769074319776</v>
       </c>
       <c r="H124" t="n">
-        <v>0.8179916115878684</v>
+        <v>0.8176011739779329</v>
       </c>
       <c r="I124" t="n">
-        <v>0.7211842010124648</v>
+        <v>0.7210082157257904</v>
       </c>
       <c r="J124" t="n">
         <v>0.6218666052041774</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2.001300190110555</v>
+        <v>2.002609368002032</v>
       </c>
       <c r="F125" t="n">
-        <v>1.973059662571481</v>
+        <v>1.973764515999617</v>
       </c>
       <c r="G125" t="n">
-        <v>1.922175668491562</v>
+        <v>1.922646178373412</v>
       </c>
       <c r="H125" t="n">
-        <v>1.809004483660662</v>
+        <v>1.809292884997003</v>
       </c>
       <c r="I125" t="n">
-        <v>1.671319119698936</v>
+        <v>1.671453113101914</v>
       </c>
       <c r="J125" t="n">
         <v>1.464164485186431</v>
@@ -10254,58 +10254,58 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6.01422205088128</v>
+        <v>6.015175066444224</v>
       </c>
       <c r="F130" t="n">
-        <v>5.822816441740236</v>
+        <v>5.824258005391714</v>
       </c>
       <c r="G130" t="n">
-        <v>5.866991198360708</v>
+        <v>5.868751607889705</v>
       </c>
       <c r="H130" t="n">
-        <v>5.909324304395768</v>
+        <v>5.911309028762895</v>
       </c>
       <c r="I130" t="n">
-        <v>6.220638203452005</v>
+        <v>6.222886319142006</v>
       </c>
       <c r="J130" t="n">
-        <v>5.648737709187992</v>
+        <v>5.650882594256691</v>
       </c>
       <c r="K130" t="n">
-        <v>5.056569791846712</v>
+        <v>5.058552618583175</v>
       </c>
       <c r="L130" t="n">
-        <v>4.501539921313142</v>
+        <v>4.503351729071276</v>
       </c>
       <c r="M130" t="n">
-        <v>4.161473669414328</v>
+        <v>4.163186548836806</v>
       </c>
       <c r="N130" t="n">
-        <v>3.822062586148923</v>
+        <v>3.823666709717932</v>
       </c>
       <c r="O130" t="n">
-        <v>3.540368605048544</v>
+        <v>3.541880633972598</v>
       </c>
       <c r="P130" t="n">
-        <v>3.479491269689036</v>
+        <v>3.480998246341718</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.433909818399236</v>
+        <v>3.435410060746077</v>
       </c>
       <c r="R130" t="n">
-        <v>3.240416271553163</v>
+        <v>3.241829998797964</v>
       </c>
       <c r="S130" t="n">
-        <v>3.08080521534065</v>
+        <v>3.082137311025455</v>
       </c>
       <c r="T130" t="n">
-        <v>2.881532320782143</v>
+        <v>2.882762808880577</v>
       </c>
       <c r="U130" t="n">
-        <v>2.667241496012968</v>
+        <v>2.668367186989746</v>
       </c>
       <c r="V130" t="n">
-        <v>2.461525825478199</v>
+        <v>2.462554618451758</v>
       </c>
     </row>
     <row r="131">
@@ -10330,58 +10330,58 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5.809272244453418</v>
+        <v>5.810120293207044</v>
       </c>
       <c r="F131" t="n">
-        <v>6.184078447161783</v>
+        <v>6.185526942707672</v>
       </c>
       <c r="G131" t="n">
-        <v>6.160198659599484</v>
+        <v>6.161936530229282</v>
       </c>
       <c r="H131" t="n">
-        <v>5.987293146472347</v>
+        <v>5.989159798154717</v>
       </c>
       <c r="I131" t="n">
-        <v>6.092035718740759</v>
+        <v>6.094055283296682</v>
       </c>
       <c r="J131" t="n">
-        <v>5.412819506828699</v>
+        <v>5.414689276043815</v>
       </c>
       <c r="K131" t="n">
-        <v>4.77976891936956</v>
+        <v>4.78146419266595</v>
       </c>
       <c r="L131" t="n">
-        <v>4.219702026552417</v>
+        <v>4.221231894201874</v>
       </c>
       <c r="M131" t="n">
-        <v>3.869431847625088</v>
+        <v>3.870860746943735</v>
       </c>
       <c r="N131" t="n">
-        <v>3.516437259166032</v>
+        <v>3.517754755351071</v>
       </c>
       <c r="O131" t="n">
-        <v>3.213355694590858</v>
+        <v>3.214573333515875</v>
       </c>
       <c r="P131" t="n">
-        <v>3.099127533097433</v>
+        <v>3.100308365486954</v>
       </c>
       <c r="Q131" t="n">
-        <v>2.983204759287738</v>
+        <v>2.984338159587991</v>
       </c>
       <c r="R131" t="n">
-        <v>2.726942239241269</v>
+        <v>2.727960627816933</v>
       </c>
       <c r="S131" t="n">
-        <v>2.49886701560362</v>
+        <v>2.499774172985546</v>
       </c>
       <c r="T131" t="n">
-        <v>2.247385990302983</v>
+        <v>2.248173731895021</v>
       </c>
       <c r="U131" t="n">
-        <v>2.00012202223276</v>
+        <v>2.000798550561225</v>
       </c>
       <c r="V131" t="n">
-        <v>1.776912539298931</v>
+        <v>1.777493138199431</v>
       </c>
     </row>
     <row r="132">
@@ -10406,58 +10406,58 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2.280642690797834</v>
+        <v>2.280709243395</v>
       </c>
       <c r="F132" t="n">
-        <v>2.173578641379231</v>
+        <v>2.173616023580664</v>
       </c>
       <c r="G132" t="n">
-        <v>2.070951035412634</v>
+        <v>2.070896524930447</v>
       </c>
       <c r="H132" t="n">
-        <v>1.956677249955031</v>
+        <v>1.956529552366016</v>
       </c>
       <c r="I132" t="n">
-        <v>1.976960692654861</v>
+        <v>1.976743759989808</v>
       </c>
       <c r="J132" t="n">
-        <v>1.78064951899059</v>
+        <v>1.780437383241603</v>
       </c>
       <c r="K132" t="n">
-        <v>1.620813396845895</v>
+        <v>1.620640078989882</v>
       </c>
       <c r="L132" t="n">
-        <v>1.484505437529503</v>
+        <v>1.484380599675345</v>
       </c>
       <c r="M132" t="n">
-        <v>1.411662574414968</v>
+        <v>1.41157693933294</v>
       </c>
       <c r="N132" t="n">
-        <v>1.325609442750707</v>
+        <v>1.325554247282618</v>
       </c>
       <c r="O132" t="n">
-        <v>1.244634003416674</v>
+        <v>1.244597917050116</v>
       </c>
       <c r="P132" t="n">
-        <v>1.226784810132262</v>
+        <v>1.226754861301018</v>
       </c>
       <c r="Q132" t="n">
-        <v>1.20059598843042</v>
+        <v>1.20056139580495</v>
       </c>
       <c r="R132" t="n">
-        <v>1.11528846213244</v>
+        <v>1.115244436440253</v>
       </c>
       <c r="S132" t="n">
-        <v>1.041020960086612</v>
+        <v>1.040966692465156</v>
       </c>
       <c r="T132" t="n">
-        <v>0.9564814299244198</v>
+        <v>0.9564204838530876</v>
       </c>
       <c r="U132" t="n">
-        <v>0.871898524525123</v>
+        <v>0.8718353021604686</v>
       </c>
       <c r="V132" t="n">
-        <v>0.7954222319290926</v>
+        <v>0.7953606803316114</v>
       </c>
     </row>
     <row r="133">
@@ -10482,58 +10482,58 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1.08488176312625</v>
+        <v>1.084530214125552</v>
       </c>
       <c r="F133" t="n">
-        <v>1.438923926293096</v>
+        <v>1.438614304319354</v>
       </c>
       <c r="G133" t="n">
-        <v>1.834034079061891</v>
+        <v>1.833901310358843</v>
       </c>
       <c r="H133" t="n">
-        <v>2.076211926105049</v>
+        <v>2.076228587965154</v>
       </c>
       <c r="I133" t="n">
-        <v>2.260767349067542</v>
+        <v>2.260852901847215</v>
       </c>
       <c r="J133" t="n">
-        <v>2.039027381742638</v>
+        <v>2.039104597396873</v>
       </c>
       <c r="K133" t="n">
-        <v>1.791519058978176</v>
+        <v>1.791564232937863</v>
       </c>
       <c r="L133" t="n">
-        <v>1.569691232659297</v>
+        <v>1.569709916940548</v>
       </c>
       <c r="M133" t="n">
-        <v>1.437440563105544</v>
+        <v>1.437445047322502</v>
       </c>
       <c r="N133" t="n">
-        <v>1.315633108952176</v>
+        <v>1.315632881285476</v>
       </c>
       <c r="O133" t="n">
-        <v>1.218735924751926</v>
+        <v>1.218736826031318</v>
       </c>
       <c r="P133" t="n">
-        <v>1.200426290218948</v>
+        <v>1.200432087208619</v>
       </c>
       <c r="Q133" t="n">
-        <v>1.19195431050773</v>
+        <v>1.191970281373775</v>
       </c>
       <c r="R133" t="n">
-        <v>1.133401934367228</v>
+        <v>1.133428361181904</v>
       </c>
       <c r="S133" t="n">
-        <v>1.086827670905942</v>
+        <v>1.086864387301676</v>
       </c>
       <c r="T133" t="n">
-        <v>1.02485961649367</v>
+        <v>1.024904302206069</v>
       </c>
       <c r="U133" t="n">
-        <v>0.9558778242540953</v>
+        <v>0.9559283239925098</v>
       </c>
       <c r="V133" t="n">
-        <v>0.8879704803052496</v>
+        <v>0.8880248228865776</v>
       </c>
     </row>
     <row r="134">
@@ -10558,58 +10558,58 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2.321761568099137</v>
+        <v>2.321978288531222</v>
       </c>
       <c r="F134" t="n">
-        <v>1.947543348392599</v>
+        <v>1.947725882755558</v>
       </c>
       <c r="G134" t="n">
-        <v>1.690812501539295</v>
+        <v>1.69087072383814</v>
       </c>
       <c r="H134" t="n">
-        <v>1.512573912288037</v>
+        <v>1.512515633116325</v>
       </c>
       <c r="I134" t="n">
-        <v>1.468667177150413</v>
+        <v>1.468516626288239</v>
       </c>
       <c r="J134" t="n">
-        <v>1.269353701107272</v>
+        <v>1.269159992628035</v>
       </c>
       <c r="K134" t="n">
-        <v>1.100797740003007</v>
+        <v>1.100585338639978</v>
       </c>
       <c r="L134" t="n">
-        <v>0.9589352882789279</v>
+        <v>0.9587180670450403</v>
       </c>
       <c r="M134" t="n">
-        <v>0.8697721433060643</v>
+        <v>0.869547783959436</v>
       </c>
       <c r="N134" t="n">
-        <v>0.785236200081276</v>
+        <v>0.7850110666592297</v>
       </c>
       <c r="O134" t="n">
-        <v>0.7170115895729418</v>
+        <v>0.7167890473782768</v>
       </c>
       <c r="P134" t="n">
-        <v>0.6982681146373071</v>
+        <v>0.6980417719746327</v>
       </c>
       <c r="Q134" t="n">
-        <v>0.6856957801766437</v>
+        <v>0.6854706522027424</v>
       </c>
       <c r="R134" t="n">
-        <v>0.6441533393614463</v>
+        <v>0.6439421017005571</v>
       </c>
       <c r="S134" t="n">
-        <v>0.6092959520648215</v>
+        <v>0.6090976650081952</v>
       </c>
       <c r="T134" t="n">
-        <v>0.5668024455133683</v>
+        <v>0.5666201152532687</v>
       </c>
       <c r="U134" t="n">
-        <v>0.5221290623385914</v>
+        <v>0.5219636541829731</v>
       </c>
       <c r="V134" t="n">
-        <v>0.4801256051797554</v>
+        <v>0.4799764949371217</v>
       </c>
     </row>
     <row r="135">
@@ -10634,58 +10634,58 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1.033411239414063</v>
+        <v>1.032998695591893</v>
       </c>
       <c r="F135" t="n">
-        <v>1.158643774321865</v>
+        <v>1.1580786594379</v>
       </c>
       <c r="G135" t="n">
-        <v>1.309743223540913</v>
+        <v>1.309151391097344</v>
       </c>
       <c r="H135" t="n">
-        <v>1.401325809347025</v>
+        <v>1.400751911588899</v>
       </c>
       <c r="I135" t="n">
-        <v>1.518025078078524</v>
+        <v>1.517440697501487</v>
       </c>
       <c r="J135" t="n">
-        <v>1.398786243983871</v>
+        <v>1.398259136909444</v>
       </c>
       <c r="K135" t="n">
-        <v>1.263805230790459</v>
+        <v>1.263329755435437</v>
       </c>
       <c r="L135" t="n">
-        <v>1.133984488473498</v>
+        <v>1.133555918230609</v>
       </c>
       <c r="M135" t="n">
-        <v>1.056384427015855</v>
+        <v>1.055985451746313</v>
       </c>
       <c r="N135" t="n">
-        <v>0.9758783259565595</v>
+        <v>0.9755102961532546</v>
       </c>
       <c r="O135" t="n">
-        <v>0.9072659036802101</v>
+        <v>0.9069242866445733</v>
       </c>
       <c r="P135" t="n">
-        <v>0.8907535746836774</v>
+        <v>0.8904156209170868</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.8722744650772251</v>
+        <v>0.8719355788948936</v>
       </c>
       <c r="R135" t="n">
-        <v>0.8095302417449016</v>
+        <v>0.8092005104553799</v>
       </c>
       <c r="S135" t="n">
-        <v>0.7519195235975067</v>
+        <v>0.75159357376076</v>
       </c>
       <c r="T135" t="n">
-        <v>0.6844422597130375</v>
+        <v>0.6841245049573822</v>
       </c>
       <c r="U135" t="n">
-        <v>0.6162824930331555</v>
+        <v>0.6159767164732072</v>
       </c>
       <c r="V135" t="n">
-        <v>0.5530866878194252</v>
+        <v>0.5527937455443656</v>
       </c>
     </row>
     <row r="136">
@@ -10710,58 +10710,58 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>8.445107268708334</v>
+        <v>8.446472895670125</v>
       </c>
       <c r="F136" t="n">
-        <v>7.057265544112646</v>
+        <v>7.058999510918132</v>
       </c>
       <c r="G136" t="n">
-        <v>5.709764035188968</v>
+        <v>5.711352105466535</v>
       </c>
       <c r="H136" t="n">
-        <v>4.592975306944738</v>
+        <v>4.594254542586053</v>
       </c>
       <c r="I136" t="n">
-        <v>4.167831561185809</v>
+        <v>4.16895179142772</v>
       </c>
       <c r="J136" t="n">
-        <v>3.495829138209028</v>
+        <v>3.49674285418932</v>
       </c>
       <c r="K136" t="n">
-        <v>3.025121300194451</v>
+        <v>3.025905303693902</v>
       </c>
       <c r="L136" t="n">
-        <v>2.689857805541291</v>
+        <v>2.690570831004547</v>
       </c>
       <c r="M136" t="n">
-        <v>2.536234587184774</v>
+        <v>2.536937759776589</v>
       </c>
       <c r="N136" t="n">
-        <v>2.374094581886792</v>
+        <v>2.374780306742307</v>
       </c>
       <c r="O136" t="n">
-        <v>2.230899011884306</v>
+        <v>2.231565804415121</v>
       </c>
       <c r="P136" t="n">
-        <v>2.212257326347546</v>
+        <v>2.212935728218799</v>
       </c>
       <c r="Q136" t="n">
-        <v>2.191029745331992</v>
+        <v>2.191712178376741</v>
       </c>
       <c r="R136" t="n">
-        <v>2.06252734689898</v>
+        <v>2.06316940452722</v>
       </c>
       <c r="S136" t="n">
-        <v>1.947238778674027</v>
+        <v>1.947837429945301</v>
       </c>
       <c r="T136" t="n">
-        <v>1.803567604031029</v>
+        <v>1.804111876247415</v>
       </c>
       <c r="U136" t="n">
-        <v>1.651514954117961</v>
+        <v>1.652004269618597</v>
       </c>
       <c r="V136" t="n">
-        <v>1.507537169486818</v>
+        <v>1.507976461354492</v>
       </c>
     </row>
     <row r="137">
@@ -10786,58 +10786,58 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1.741181705185269</v>
+        <v>1.741214984564978</v>
       </c>
       <c r="F137" t="n">
-        <v>1.737572424674704</v>
+        <v>1.737609425762933</v>
       </c>
       <c r="G137" t="n">
-        <v>1.651100956682197</v>
+        <v>1.65106421789858</v>
       </c>
       <c r="H137" t="n">
-        <v>1.558714514836608</v>
+        <v>1.55860367416008</v>
       </c>
       <c r="I137" t="n">
-        <v>1.575522193144683</v>
+        <v>1.575357826014424</v>
       </c>
       <c r="J137" t="n">
-        <v>1.410951388326722</v>
+        <v>1.410783412936129</v>
       </c>
       <c r="K137" t="n">
-        <v>1.262199398258205</v>
+        <v>1.262042835113048</v>
       </c>
       <c r="L137" t="n">
-        <v>1.127539411685447</v>
+        <v>1.127397229970377</v>
       </c>
       <c r="M137" t="n">
-        <v>1.042082347549144</v>
+        <v>1.041945718516342</v>
       </c>
       <c r="N137" t="n">
-        <v>0.9509411270741249</v>
+        <v>0.9508068663381483</v>
       </c>
       <c r="O137" t="n">
-        <v>0.8753499997526504</v>
+        <v>0.8752189044389368</v>
       </c>
       <c r="P137" t="n">
-        <v>0.8578094472092712</v>
+        <v>0.8576789290121598</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.8466226838655955</v>
+        <v>0.8464966226088291</v>
       </c>
       <c r="R137" t="n">
-        <v>0.7981412811646561</v>
+        <v>0.7980255586466131</v>
       </c>
       <c r="S137" t="n">
-        <v>0.7567110290747795</v>
+        <v>0.7566040023054692</v>
       </c>
       <c r="T137" t="n">
-        <v>0.7051401228829723</v>
+        <v>0.7050426738712581</v>
       </c>
       <c r="U137" t="n">
-        <v>0.6507060990585346</v>
+        <v>0.6506189968490895</v>
       </c>
       <c r="V137" t="n">
-        <v>0.5990919955953292</v>
+        <v>0.5990146519671348</v>
       </c>
     </row>
     <row r="138">
@@ -10862,58 +10862,58 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>7.284748665941353</v>
+        <v>7.285821417469693</v>
       </c>
       <c r="F138" t="n">
-        <v>6.761362809977456</v>
+        <v>6.762879920632527</v>
       </c>
       <c r="G138" t="n">
-        <v>6.279499490958138</v>
+        <v>6.281132870226309</v>
       </c>
       <c r="H138" t="n">
-        <v>5.728790939113709</v>
+        <v>5.730364720028962</v>
       </c>
       <c r="I138" t="n">
-        <v>5.480201113855593</v>
+        <v>5.481716092291962</v>
       </c>
       <c r="J138" t="n">
-        <v>4.597913299846888</v>
+        <v>4.599157652227939</v>
       </c>
       <c r="K138" t="n">
-        <v>3.883200751252087</v>
+        <v>3.884217445742905</v>
       </c>
       <c r="L138" t="n">
-        <v>3.311496306595847</v>
+        <v>3.312335798263387</v>
       </c>
       <c r="M138" t="n">
-        <v>3.021374921123092</v>
+        <v>3.022142060339826</v>
       </c>
       <c r="N138" t="n">
-        <v>2.791040845522976</v>
+        <v>2.791769018414741</v>
       </c>
       <c r="O138" t="n">
-        <v>2.626627663380886</v>
+        <v>2.627341449003022</v>
       </c>
       <c r="P138" t="n">
-        <v>2.619925533082866</v>
+        <v>2.62066396951402</v>
       </c>
       <c r="Q138" t="n">
-        <v>2.615771059907246</v>
+        <v>2.61652885442209</v>
       </c>
       <c r="R138" t="n">
-        <v>2.482132932504657</v>
+        <v>2.482858935207783</v>
       </c>
       <c r="S138" t="n">
-        <v>2.360178873400597</v>
+        <v>2.360866117913933</v>
       </c>
       <c r="T138" t="n">
-        <v>2.198740582749329</v>
+        <v>2.199372997455932</v>
       </c>
       <c r="U138" t="n">
-        <v>2.023998774143948</v>
+        <v>2.02457330610383</v>
       </c>
       <c r="V138" t="n">
-        <v>1.854703938747156</v>
+        <v>1.855223687519322</v>
       </c>
     </row>
     <row r="139">
@@ -10938,58 +10938,58 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>14.02787436656065</v>
+        <v>14.03000143943782</v>
       </c>
       <c r="F139" t="n">
-        <v>13.58201118495768</v>
+        <v>13.58521446941699</v>
       </c>
       <c r="G139" t="n">
-        <v>13.68542143119864</v>
+        <v>13.6893245642801</v>
       </c>
       <c r="H139" t="n">
-        <v>13.78436410597654</v>
+        <v>13.78876654774862</v>
       </c>
       <c r="I139" t="n">
-        <v>14.51066685052956</v>
+        <v>14.51565805538085</v>
       </c>
       <c r="J139" t="n">
-        <v>13.17669799538415</v>
+        <v>13.18146205158015</v>
       </c>
       <c r="K139" t="n">
-        <v>11.79542173497249</v>
+        <v>11.799825818839</v>
       </c>
       <c r="L139" t="n">
-        <v>10.50076040530722</v>
+        <v>10.50478377233189</v>
       </c>
       <c r="M139" t="n">
-        <v>9.707528888911618</v>
+        <v>9.711332073532157</v>
       </c>
       <c r="N139" t="n">
-        <v>8.915811674962427</v>
+        <v>8.919373117929011</v>
       </c>
       <c r="O139" t="n">
-        <v>8.258720301159206</v>
+        <v>8.26207749144918</v>
       </c>
       <c r="P139" t="n">
-        <v>8.11672296127788</v>
+        <v>8.120069729489144</v>
       </c>
       <c r="Q139" t="n">
-        <v>8.010394981901294</v>
+        <v>8.013728154091433</v>
       </c>
       <c r="R139" t="n">
-        <v>7.55901280091249</v>
+        <v>7.562155176447231</v>
       </c>
       <c r="S139" t="n">
-        <v>7.18666065572376</v>
+        <v>7.189622823643008</v>
       </c>
       <c r="T139" t="n">
-        <v>6.721786391094382</v>
+        <v>6.724524028071709</v>
       </c>
       <c r="U139" t="n">
-        <v>6.221884083542557</v>
+        <v>6.224389637200578</v>
       </c>
       <c r="V139" t="n">
-        <v>5.741990472120595</v>
+        <v>5.744281622351776</v>
       </c>
     </row>
     <row r="140">
@@ -11014,58 +11014,58 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5.58043926709876</v>
+        <v>5.581206430374029</v>
       </c>
       <c r="F140" t="n">
-        <v>4.686956868349853</v>
+        <v>4.687857652056716</v>
       </c>
       <c r="G140" t="n">
-        <v>4.117131855798021</v>
+        <v>4.117954873693763</v>
       </c>
       <c r="H140" t="n">
-        <v>3.763166552400427</v>
+        <v>3.763902673830005</v>
       </c>
       <c r="I140" t="n">
-        <v>3.759360588792791</v>
+        <v>3.760091061944989</v>
       </c>
       <c r="J140" t="n">
-        <v>3.346575383608958</v>
+        <v>3.347236781202493</v>
       </c>
       <c r="K140" t="n">
-        <v>2.976022826055391</v>
+        <v>2.976621434033861</v>
       </c>
       <c r="L140" t="n">
-        <v>2.629045553324727</v>
+        <v>2.629577123639488</v>
       </c>
       <c r="M140" t="n">
-        <v>2.391389479297443</v>
+        <v>2.391864348808511</v>
       </c>
       <c r="N140" t="n">
-        <v>2.147130739968576</v>
+        <v>2.147541118306808</v>
       </c>
       <c r="O140" t="n">
-        <v>1.94207294230887</v>
+        <v>1.942427541265087</v>
       </c>
       <c r="P140" t="n">
-        <v>1.871533235732575</v>
+        <v>1.871862110654255</v>
       </c>
       <c r="Q140" t="n">
-        <v>1.81901704827236</v>
+        <v>1.819327448234272</v>
       </c>
       <c r="R140" t="n">
-        <v>1.694548630271587</v>
+        <v>1.694828707306528</v>
       </c>
       <c r="S140" t="n">
-        <v>1.59300685086389</v>
+        <v>1.593261417114694</v>
       </c>
       <c r="T140" t="n">
-        <v>1.476542361311319</v>
+        <v>1.476771667376173</v>
       </c>
       <c r="U140" t="n">
-        <v>1.357461413638191</v>
+        <v>1.357668382913836</v>
       </c>
       <c r="V140" t="n">
-        <v>1.247158020890933</v>
+        <v>1.247346918583451</v>
       </c>
     </row>
     <row r="141">
@@ -11090,58 +11090,58 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.3322074383167753</v>
+        <v>0.3315612256216373</v>
       </c>
       <c r="F141" t="n">
-        <v>0.3421481699930058</v>
+        <v>0.3411123606798628</v>
       </c>
       <c r="G141" t="n">
-        <v>0.3549522635524135</v>
+        <v>0.353655322456752</v>
       </c>
       <c r="H141" t="n">
-        <v>0.3593967741692943</v>
+        <v>0.3579502738436608</v>
       </c>
       <c r="I141" t="n">
-        <v>0.3794878241214746</v>
+        <v>0.3778831701491369</v>
       </c>
       <c r="J141" t="n">
-        <v>0.3486839075088142</v>
+        <v>0.3471825043898657</v>
       </c>
       <c r="K141" t="n">
-        <v>0.317450659223486</v>
+        <v>0.3160836469776366</v>
       </c>
       <c r="L141" t="n">
-        <v>0.2885958769145163</v>
+        <v>0.2873663446675935</v>
       </c>
       <c r="M141" t="n">
-        <v>0.2730153084534819</v>
+        <v>0.2718750686769494</v>
       </c>
       <c r="N141" t="n">
-        <v>0.2573636781972632</v>
+        <v>0.2563225649813532</v>
       </c>
       <c r="O141" t="n">
-        <v>0.2454892006538306</v>
+        <v>0.2445393836499113</v>
       </c>
       <c r="P141" t="n">
-        <v>0.2487255315960079</v>
+        <v>0.2478139936351792</v>
       </c>
       <c r="Q141" t="n">
-        <v>0.2527838078943158</v>
+        <v>0.2519121901750828</v>
       </c>
       <c r="R141" t="n">
-        <v>0.2487890776791445</v>
+        <v>0.2480124185528665</v>
       </c>
       <c r="S141" t="n">
-        <v>0.2471487757236079</v>
+        <v>0.2464596973284807</v>
       </c>
       <c r="T141" t="n">
-        <v>0.2394013108590342</v>
+        <v>0.2387971279120361</v>
       </c>
       <c r="U141" t="n">
-        <v>0.2256628333880475</v>
+        <v>0.2251286239706181</v>
       </c>
       <c r="V141" t="n">
-        <v>0.2088629173823957</v>
+        <v>0.2083829889063624</v>
       </c>
     </row>
     <row r="142">
@@ -11166,58 +11166,58 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.1526112856867346</v>
+        <v>0.1517435337117359</v>
       </c>
       <c r="F142" t="n">
-        <v>0.2246474512536387</v>
+        <v>0.2236389047689935</v>
       </c>
       <c r="G142" t="n">
-        <v>0.3466440085249113</v>
+        <v>0.3457933728120022</v>
       </c>
       <c r="H142" t="n">
-        <v>0.4637884298902547</v>
+        <v>0.463101308752403</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5669818265828557</v>
+        <v>0.5663600123907099</v>
       </c>
       <c r="J142" t="n">
-        <v>0.5439554115089297</v>
+        <v>0.5434152572751482</v>
       </c>
       <c r="K142" t="n">
-        <v>0.4879027416126778</v>
+        <v>0.4874041871509022</v>
       </c>
       <c r="L142" t="n">
-        <v>0.4246860056748911</v>
+        <v>0.4242113903094372</v>
       </c>
       <c r="M142" t="n">
-        <v>0.3833040619469041</v>
+        <v>0.382836639081064</v>
       </c>
       <c r="N142" t="n">
-        <v>0.3465143933873174</v>
+        <v>0.3460656422621249</v>
       </c>
       <c r="O142" t="n">
-        <v>0.3186158519440662</v>
+        <v>0.318189365735594</v>
       </c>
       <c r="P142" t="n">
-        <v>0.3130839785378979</v>
+        <v>0.3126615941407822</v>
       </c>
       <c r="Q142" t="n">
-        <v>0.310633814898039</v>
+        <v>0.3102207960582378</v>
       </c>
       <c r="R142" t="n">
-        <v>0.2952658069996295</v>
+        <v>0.2948850988764961</v>
       </c>
       <c r="S142" t="n">
-        <v>0.2827736656135929</v>
+        <v>0.2824232590105895</v>
       </c>
       <c r="T142" t="n">
-        <v>0.2664116270219969</v>
+        <v>0.2660958238720115</v>
       </c>
       <c r="U142" t="n">
-        <v>0.2484172107982695</v>
+        <v>0.2481357211486802</v>
       </c>
       <c r="V142" t="n">
-        <v>0.2308620956928859</v>
+        <v>0.23061159421115</v>
       </c>
     </row>
     <row r="143">
@@ -11470,19 +11470,19 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.9288120088698305</v>
+        <v>0.8544092283981358</v>
       </c>
       <c r="F146" t="n">
-        <v>1.150773550376023</v>
+        <v>0.9928334067341956</v>
       </c>
       <c r="G146" t="n">
-        <v>1.352869377864324</v>
+        <v>1.105866442851696</v>
       </c>
       <c r="H146" t="n">
-        <v>1.735792734296997</v>
+        <v>1.365771653352049</v>
       </c>
       <c r="I146" t="n">
-        <v>2.507629711531902</v>
+        <v>1.942626886189546</v>
       </c>
       <c r="J146" t="n">
         <v>5.517734450691647</v>
@@ -11546,19 +11546,19 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1.329496691397634</v>
+        <v>1.335539675884573</v>
       </c>
       <c r="F147" t="n">
-        <v>1.477482707250715</v>
+        <v>1.484474992831115</v>
       </c>
       <c r="G147" t="n">
-        <v>1.499176024156478</v>
+        <v>1.499105253225133</v>
       </c>
       <c r="H147" t="n">
-        <v>1.561529534470348</v>
+        <v>1.550952653768748</v>
       </c>
       <c r="I147" t="n">
-        <v>1.634209095159192</v>
+        <v>1.610391469034542</v>
       </c>
       <c r="J147" t="n">
         <v>1.634471635930159</v>
@@ -11622,19 +11622,19 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1.524242658584679</v>
+        <v>1.525958038053584</v>
       </c>
       <c r="F148" t="n">
-        <v>1.745757094699294</v>
+        <v>1.749319781672369</v>
       </c>
       <c r="G148" t="n">
-        <v>1.857032970976722</v>
+        <v>1.862532918853424</v>
       </c>
       <c r="H148" t="n">
-        <v>1.985334772491641</v>
+        <v>1.993362058629335</v>
       </c>
       <c r="I148" t="n">
-        <v>2.048578298885053</v>
+        <v>2.060397678451468</v>
       </c>
       <c r="J148" t="n">
         <v>1.787720083395652</v>
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1.129565983489921</v>
+        <v>0.94402427764884</v>
       </c>
       <c r="F149" t="n">
-        <v>1.395541980936155</v>
+        <v>1.196304605288105</v>
       </c>
       <c r="G149" t="n">
-        <v>1.608837718932791</v>
+        <v>1.419111436999017</v>
       </c>
       <c r="H149" t="n">
-        <v>1.774514894552299</v>
+        <v>1.615693890230288</v>
       </c>
       <c r="I149" t="n">
-        <v>1.89850434462069</v>
+        <v>1.79706504859471</v>
       </c>
       <c r="J149" t="n">
         <v>1.826360847174661</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.7612377441859554</v>
+        <v>0.9512389696974106</v>
       </c>
       <c r="F150" t="n">
-        <v>0.6348235488011186</v>
+        <v>0.8118870742488375</v>
       </c>
       <c r="G150" t="n">
-        <v>0.5768703173965154</v>
+        <v>0.7340217617406889</v>
       </c>
       <c r="H150" t="n">
-        <v>0.5364504648570886</v>
+        <v>0.6676521745314601</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4891006028067207</v>
+        <v>0.5766907759461235</v>
       </c>
       <c r="J150" t="n">
         <v>0.3777950528923361</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.7540738365256601</v>
+        <v>0.7657737869644228</v>
       </c>
       <c r="F151" t="n">
-        <v>0.7669233860780594</v>
+        <v>0.7869236430013782</v>
       </c>
       <c r="G151" t="n">
-        <v>0.7700409972093065</v>
+        <v>0.798628020514299</v>
       </c>
       <c r="H151" t="n">
-        <v>0.7794319509508284</v>
+        <v>0.8089920328478117</v>
       </c>
       <c r="I151" t="n">
-        <v>0.7946983770082332</v>
+        <v>0.815798878332714</v>
       </c>
       <c r="J151" t="n">
         <v>0.7359536353071054</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.5174365728143893</v>
+        <v>0.5189914683939332</v>
       </c>
       <c r="F152" t="n">
-        <v>0.517871864122775</v>
+        <v>0.53353821705991</v>
       </c>
       <c r="G152" t="n">
-        <v>0.5302187545334782</v>
+        <v>0.546544070589407</v>
       </c>
       <c r="H152" t="n">
-        <v>0.5581311324580678</v>
+        <v>0.5696866960843063</v>
       </c>
       <c r="I152" t="n">
-        <v>0.595063218000136</v>
+        <v>0.6004168619495853</v>
       </c>
       <c r="J152" t="n">
         <v>0.5767394653616571</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1.102553219935462</v>
+        <v>0.8415488315640951</v>
       </c>
       <c r="F153" t="n">
-        <v>1.446804117362342</v>
+        <v>1.171871711202908</v>
       </c>
       <c r="G153" t="n">
-        <v>1.649312362448069</v>
+        <v>1.403219920537657</v>
       </c>
       <c r="H153" t="n">
-        <v>1.7852989265421</v>
+        <v>1.587638276325043</v>
       </c>
       <c r="I153" t="n">
-        <v>1.899880542681416</v>
+        <v>1.774627709477264</v>
       </c>
       <c r="J153" t="n">
         <v>1.838129781367545</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.4205898166196676</v>
+        <v>0.4722239778096364</v>
       </c>
       <c r="F154" t="n">
-        <v>0.3893323417062194</v>
+        <v>0.452027265464669</v>
       </c>
       <c r="G154" t="n">
-        <v>0.3721203717849149</v>
+        <v>0.4325638834689779</v>
       </c>
       <c r="H154" t="n">
-        <v>0.3663797214699812</v>
+        <v>0.4160555564091852</v>
       </c>
       <c r="I154" t="n">
-        <v>0.365908579017959</v>
+        <v>0.3969170811663826</v>
       </c>
       <c r="J154" t="n">
         <v>0.3306967612495579</v>
@@ -12154,58 +12154,58 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.06883172493880418</v>
+        <v>0.06883150118811615</v>
       </c>
       <c r="F155" t="n">
-        <v>0.08282844204763591</v>
+        <v>0.08282794946276231</v>
       </c>
       <c r="G155" t="n">
-        <v>0.09418562991294747</v>
+        <v>0.09418482455632468</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1064225016521776</v>
+        <v>0.1064213021790171</v>
       </c>
       <c r="I155" t="n">
-        <v>0.1189175600513607</v>
+        <v>0.1189159812704537</v>
       </c>
       <c r="J155" t="n">
-        <v>0.1148228856699228</v>
+        <v>0.1148211403526013</v>
       </c>
       <c r="K155" t="n">
-        <v>0.1081733032269543</v>
+        <v>0.1081715182637721</v>
       </c>
       <c r="L155" t="n">
-        <v>0.1016432514532617</v>
+        <v>0.1016414819411309</v>
       </c>
       <c r="M155" t="n">
-        <v>0.1017478657766857</v>
+        <v>0.1017460181253357</v>
       </c>
       <c r="N155" t="n">
-        <v>0.1023716767674696</v>
+        <v>0.1023697541736599</v>
       </c>
       <c r="O155" t="n">
-        <v>0.1012106851246114</v>
+        <v>0.1012087223580721</v>
       </c>
       <c r="P155" t="n">
-        <v>0.1000214674505826</v>
+        <v>0.1000194594765075</v>
       </c>
       <c r="Q155" t="n">
-        <v>0.1043978744804683</v>
+        <v>0.1043956767378725</v>
       </c>
       <c r="R155" t="n">
-        <v>0.1080273937457361</v>
+        <v>0.1080250030612423</v>
       </c>
       <c r="S155" t="n">
-        <v>0.1109359374396638</v>
+        <v>0.1109333285613779</v>
       </c>
       <c r="T155" t="n">
-        <v>0.1136522747689261</v>
+        <v>0.113649347634389</v>
       </c>
       <c r="U155" t="n">
-        <v>0.1172243038784716</v>
+        <v>0.1172208705687161</v>
       </c>
       <c r="V155" t="n">
-        <v>0.1289192915126541</v>
+        <v>0.1289147905134146</v>
       </c>
     </row>
     <row r="156">
@@ -12230,58 +12230,58 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.1600882512574184</v>
+        <v>0.1600882893898931</v>
       </c>
       <c r="F156" t="n">
-        <v>0.197078927674197</v>
+        <v>0.1970790419766871</v>
       </c>
       <c r="G156" t="n">
-        <v>0.2289770753664183</v>
+        <v>0.22897731060856</v>
       </c>
       <c r="H156" t="n">
-        <v>0.2624146240210924</v>
+        <v>0.2624150159705607</v>
       </c>
       <c r="I156" t="n">
-        <v>0.295655237525042</v>
+        <v>0.2956558158813427</v>
       </c>
       <c r="J156" t="n">
-        <v>0.2864530334293951</v>
+        <v>0.2864537084958421</v>
       </c>
       <c r="K156" t="n">
-        <v>0.2695047177952196</v>
+        <v>0.2695054545079866</v>
       </c>
       <c r="L156" t="n">
-        <v>0.2519678551982208</v>
+        <v>0.2519686264854942</v>
       </c>
       <c r="M156" t="n">
-        <v>0.2507515561808439</v>
+        <v>0.2507523924671006</v>
       </c>
       <c r="N156" t="n">
-        <v>0.2510638874626312</v>
+        <v>0.2510647995843185</v>
       </c>
       <c r="O156" t="n">
-        <v>0.2474135347139352</v>
+        <v>0.2474145179502731</v>
       </c>
       <c r="P156" t="n">
-        <v>0.2441736865405152</v>
+        <v>0.2441747460781372</v>
       </c>
       <c r="Q156" t="n">
-        <v>0.2551221540329179</v>
+        <v>0.2551233754665717</v>
       </c>
       <c r="R156" t="n">
-        <v>0.266327220473593</v>
+        <v>0.2663286563619918</v>
       </c>
       <c r="S156" t="n">
-        <v>0.2769927308040586</v>
+        <v>0.2769944373446673</v>
       </c>
       <c r="T156" t="n">
-        <v>0.2872679101084982</v>
+        <v>0.2872699754941705</v>
       </c>
       <c r="U156" t="n">
-        <v>0.2989207680925376</v>
+        <v>0.2989233323639611</v>
       </c>
       <c r="V156" t="n">
-        <v>0.3306062167442038</v>
+        <v>0.3306097393509806</v>
       </c>
     </row>
     <row r="157">
@@ -12306,58 +12306,58 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.4828437125410284</v>
+        <v>0.4828449677107587</v>
       </c>
       <c r="F157" t="n">
-        <v>0.7267736418441593</v>
+        <v>0.7267770946364324</v>
       </c>
       <c r="G157" t="n">
-        <v>0.9981187578052386</v>
+        <v>0.998125145724406</v>
       </c>
       <c r="H157" t="n">
-        <v>1.24505787466005</v>
+        <v>1.245067811076919</v>
       </c>
       <c r="I157" t="n">
-        <v>1.40973980483726</v>
+        <v>1.409753834555945</v>
       </c>
       <c r="J157" t="n">
-        <v>1.31618367198749</v>
+        <v>1.316198725907087</v>
       </c>
       <c r="K157" t="n">
-        <v>1.188988250762773</v>
+        <v>1.189004264787688</v>
       </c>
       <c r="L157" t="n">
-        <v>1.081309285582247</v>
+        <v>1.081323815620275</v>
       </c>
       <c r="M157" t="n">
-        <v>1.056130200323165</v>
+        <v>1.056146553234567</v>
       </c>
       <c r="N157" t="n">
-        <v>1.038474087543444</v>
+        <v>1.038490742009452</v>
       </c>
       <c r="O157" t="n">
-        <v>1.000099449022728</v>
+        <v>1.000116518631107</v>
       </c>
       <c r="P157" t="n">
-        <v>0.9559037043497508</v>
+        <v>0.9559205612922094</v>
       </c>
       <c r="Q157" t="n">
-        <v>0.9604260631355256</v>
+        <v>0.960443553412025</v>
       </c>
       <c r="R157" t="n">
-        <v>0.946206282802715</v>
+        <v>0.9462245191974528</v>
       </c>
       <c r="S157" t="n">
-        <v>0.9222104737568656</v>
+        <v>0.9222288307339854</v>
       </c>
       <c r="T157" t="n">
-        <v>0.9000703154990358</v>
+        <v>0.9000903632125941</v>
       </c>
       <c r="U157" t="n">
-        <v>0.8925813963296342</v>
+        <v>0.8926039896853801</v>
       </c>
       <c r="V157" t="n">
-        <v>0.9528478648198173</v>
+        <v>0.9528762189397859</v>
       </c>
     </row>
     <row r="158">
@@ -12382,58 +12382,58 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.2673587537739122</v>
+        <v>0.2673590758389565</v>
       </c>
       <c r="F158" t="n">
-        <v>0.2966072477473904</v>
+        <v>0.2966078716772393</v>
       </c>
       <c r="G158" t="n">
-        <v>0.3092882329939659</v>
+        <v>0.3092890159154897</v>
       </c>
       <c r="H158" t="n">
-        <v>0.3290359400708663</v>
+        <v>0.3290369214804094</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3549167825061574</v>
+        <v>0.3549180007637214</v>
       </c>
       <c r="J158" t="n">
-        <v>0.3359823588441703</v>
+        <v>0.3359836464591419</v>
       </c>
       <c r="K158" t="n">
-        <v>0.3137439471589768</v>
+        <v>0.3137452695069047</v>
       </c>
       <c r="L158" t="n">
-        <v>0.2942675825459266</v>
+        <v>0.2942689468559888</v>
       </c>
       <c r="M158" t="n">
-        <v>0.2944735627370059</v>
+        <v>0.294475058468562</v>
       </c>
       <c r="N158" t="n">
-        <v>0.2954978389073757</v>
+        <v>0.2954994727662949</v>
       </c>
       <c r="O158" t="n">
-        <v>0.2902661007800345</v>
+        <v>0.2902678365420234</v>
       </c>
       <c r="P158" t="n">
-        <v>0.2838878195136656</v>
+        <v>0.2838896204663696</v>
       </c>
       <c r="Q158" t="n">
-        <v>0.2917857511052222</v>
+        <v>0.2917876650982074</v>
       </c>
       <c r="R158" t="n">
-        <v>0.2932900666278395</v>
+        <v>0.2932920109340713</v>
       </c>
       <c r="S158" t="n">
-        <v>0.2906625470788111</v>
+        <v>0.2906644789780163</v>
       </c>
       <c r="T158" t="n">
-        <v>0.2877568066506168</v>
+        <v>0.2877586810682901</v>
       </c>
       <c r="U158" t="n">
-        <v>0.288913821778895</v>
+        <v>0.2889158244830112</v>
       </c>
       <c r="V158" t="n">
-        <v>0.3112834317347557</v>
+        <v>0.3112859026598083</v>
       </c>
     </row>
     <row r="159">
@@ -12458,58 +12458,58 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1.382337226841889</v>
+        <v>1.382340178705844</v>
       </c>
       <c r="F159" t="n">
-        <v>1.608117506789428</v>
+        <v>1.608125786580115</v>
       </c>
       <c r="G159" t="n">
-        <v>1.794228901830413</v>
+        <v>1.79424191856212</v>
       </c>
       <c r="H159" t="n">
-        <v>1.981516546512638</v>
+        <v>1.981533918179449</v>
       </c>
       <c r="I159" t="n">
-        <v>2.164523059295331</v>
+        <v>2.164546930201471</v>
       </c>
       <c r="J159" t="n">
-        <v>2.02492551195386</v>
+        <v>2.024950899049369</v>
       </c>
       <c r="K159" t="n">
-        <v>1.858314082326343</v>
+        <v>1.858340970250752</v>
       </c>
       <c r="L159" t="n">
-        <v>1.694659676248611</v>
+        <v>1.694685912179594</v>
       </c>
       <c r="M159" t="n">
-        <v>1.627762439834951</v>
+        <v>1.627788201854007</v>
       </c>
       <c r="N159" t="n">
-        <v>1.558124128090303</v>
+        <v>1.55815173192851</v>
       </c>
       <c r="O159" t="n">
-        <v>1.471275428092874</v>
+        <v>1.471302920780877</v>
       </c>
       <c r="P159" t="n">
-        <v>1.397651287637787</v>
+        <v>1.397678839758983</v>
       </c>
       <c r="Q159" t="n">
-        <v>1.423799876910453</v>
+        <v>1.423829794508839</v>
       </c>
       <c r="R159" t="n">
-        <v>1.428743076008831</v>
+        <v>1.428773439634943</v>
       </c>
       <c r="S159" t="n">
-        <v>1.408525605388417</v>
+        <v>1.408558828936381</v>
       </c>
       <c r="T159" t="n">
-        <v>1.372881394522819</v>
+        <v>1.372915547217239</v>
       </c>
       <c r="U159" t="n">
-        <v>1.344856262906033</v>
+        <v>1.344893850443885</v>
       </c>
       <c r="V159" t="n">
-        <v>1.408441823014688</v>
+        <v>1.408490328088318</v>
       </c>
     </row>
     <row r="160">
@@ -12534,58 +12534,58 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.06579988661440363</v>
+        <v>0.06579964277441143</v>
       </c>
       <c r="F160" t="n">
-        <v>0.08238476806504544</v>
+        <v>0.08238423668465622</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0962129417287417</v>
+        <v>0.09621208727729563</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1103056981649485</v>
+        <v>0.1103044867018912</v>
       </c>
       <c r="I160" t="n">
-        <v>0.1250687730171675</v>
+        <v>0.1250671506617496</v>
       </c>
       <c r="J160" t="n">
-        <v>0.1235563887318188</v>
+        <v>0.1235546752401979</v>
       </c>
       <c r="K160" t="n">
-        <v>0.1200486234478505</v>
+        <v>0.1200469240519236</v>
       </c>
       <c r="L160" t="n">
-        <v>0.1168034353752147</v>
+        <v>0.1168018000140801</v>
       </c>
       <c r="M160" t="n">
-        <v>0.1207242807866008</v>
+        <v>0.1207226573673087</v>
       </c>
       <c r="N160" t="n">
-        <v>0.1247034859050026</v>
+        <v>0.1247018632637994</v>
       </c>
       <c r="O160" t="n">
-        <v>0.1259263354653778</v>
+        <v>0.1259247399106675</v>
       </c>
       <c r="P160" t="n">
-        <v>0.1265658773462993</v>
+        <v>0.1265642805844589</v>
       </c>
       <c r="Q160" t="n">
-        <v>0.1336531229508077</v>
+        <v>0.1336514251790145</v>
       </c>
       <c r="R160" t="n">
-        <v>0.1378518363894929</v>
+        <v>0.1378499918639989</v>
       </c>
       <c r="S160" t="n">
-        <v>0.1398950236308851</v>
+        <v>0.1398929484909877</v>
       </c>
       <c r="T160" t="n">
-        <v>0.1415137307459547</v>
+        <v>0.1415113746033053</v>
       </c>
       <c r="U160" t="n">
-        <v>0.1448206159316306</v>
+        <v>0.1448178530972783</v>
       </c>
       <c r="V160" t="n">
-        <v>0.1588504353523968</v>
+        <v>0.1588467907990101</v>
       </c>
     </row>
     <row r="161">
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5.196605606682582</v>
+        <v>5.396872965372663</v>
       </c>
       <c r="F162" t="n">
-        <v>3.520801169891588</v>
+        <v>3.737795045972279</v>
       </c>
       <c r="G162" t="n">
-        <v>2.467298806701756</v>
+        <v>2.662730523524449</v>
       </c>
       <c r="H162" t="n">
-        <v>1.896197388289034</v>
+        <v>2.089059571594419</v>
       </c>
       <c r="I162" t="n">
-        <v>1.507263516558799</v>
+        <v>1.736528511420794</v>
       </c>
       <c r="J162" t="n">
         <v>0.4770464549362138</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.5944625570659116</v>
+        <v>0.5938892489105473</v>
       </c>
       <c r="F163" t="n">
-        <v>0.7101476236262696</v>
+        <v>0.7137903547661049</v>
       </c>
       <c r="G163" t="n">
-        <v>0.8407114582671832</v>
+        <v>0.8578491141169747</v>
       </c>
       <c r="H163" t="n">
-        <v>0.9277249111521267</v>
+        <v>0.9624297445597603</v>
       </c>
       <c r="I163" t="n">
-        <v>0.9489675425038639</v>
+        <v>1.009110767645544</v>
       </c>
       <c r="J163" t="n">
         <v>0.6412181645904518</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.2608057048658557</v>
+        <v>0.2243585551164844</v>
       </c>
       <c r="F164" t="n">
-        <v>0.3550145480617855</v>
+        <v>0.3014437213307712</v>
       </c>
       <c r="G164" t="n">
-        <v>0.439960461541407</v>
+        <v>0.3797630039347004</v>
       </c>
       <c r="H164" t="n">
-        <v>0.5276239227177943</v>
+        <v>0.4589705389802389</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6472971480275914</v>
+        <v>0.559572909199873</v>
       </c>
       <c r="J164" t="n">
         <v>0.9501137161584531</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.4710213931331755</v>
+        <v>0.4567944111223077</v>
       </c>
       <c r="F165" t="n">
-        <v>0.5517307012496528</v>
+        <v>0.5253362300291999</v>
       </c>
       <c r="G165" t="n">
-        <v>0.5976939029114761</v>
+        <v>0.5471487803275964</v>
       </c>
       <c r="H165" t="n">
-        <v>0.6728374174744588</v>
+        <v>0.5847815916935503</v>
       </c>
       <c r="I165" t="n">
-        <v>0.8476125652933845</v>
+        <v>0.6944526446040908</v>
       </c>
       <c r="J165" t="n">
         <v>1.541481312614384</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.2573698981334218</v>
+        <v>0.1945018229954368</v>
       </c>
       <c r="F166" t="n">
-        <v>0.3823105163084973</v>
+        <v>0.2669678423042129</v>
       </c>
       <c r="G166" t="n">
-        <v>0.5114099905441143</v>
+        <v>0.3427061953285443</v>
       </c>
       <c r="H166" t="n">
-        <v>0.6957019588502494</v>
+        <v>0.452932090973319</v>
       </c>
       <c r="I166" t="n">
-        <v>1.084546397081687</v>
+        <v>0.7068074229053068</v>
       </c>
       <c r="J166" t="n">
         <v>2.711850561007916</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2.533647349282933</v>
+        <v>2.622979712169603</v>
       </c>
       <c r="F167" t="n">
-        <v>2.456544871150832</v>
+        <v>2.593932635222648</v>
       </c>
       <c r="G167" t="n">
-        <v>2.386632510678731</v>
+        <v>2.563034545341134</v>
       </c>
       <c r="H167" t="n">
-        <v>2.31256061813341</v>
+        <v>2.548218437061955</v>
       </c>
       <c r="I167" t="n">
-        <v>2.088183079234514</v>
+        <v>2.440093886130085</v>
       </c>
       <c r="J167" t="n">
         <v>0.4554185441344299</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5.107350746819922</v>
+        <v>5.288903334465997</v>
       </c>
       <c r="F168" t="n">
-        <v>5.432287217920811</v>
+        <v>5.746796902984046</v>
       </c>
       <c r="G168" t="n">
-        <v>5.637542211698948</v>
+        <v>6.080816804461178</v>
       </c>
       <c r="H168" t="n">
-        <v>5.613135892875183</v>
+        <v>6.233977351697703</v>
       </c>
       <c r="I168" t="n">
-        <v>5.040864403419361</v>
+        <v>5.982241361213803</v>
       </c>
       <c r="J168" t="n">
         <v>0.6891816870642783</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.4075119467533057</v>
+        <v>0.3874582579156493</v>
       </c>
       <c r="F169" t="n">
-        <v>0.4801719518964934</v>
+        <v>0.4404344556451797</v>
       </c>
       <c r="G169" t="n">
-        <v>0.5505925153895969</v>
+        <v>0.4886749712068347</v>
       </c>
       <c r="H169" t="n">
-        <v>0.642338890324804</v>
+        <v>0.5528933131028849</v>
       </c>
       <c r="I169" t="n">
-        <v>0.8028162229484013</v>
+        <v>0.6700222564487021</v>
       </c>
       <c r="J169" t="n">
         <v>1.306474521615236</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.2995203090739607</v>
+        <v>0.2795533807276688</v>
       </c>
       <c r="F170" t="n">
-        <v>0.3944174954641165</v>
+        <v>0.368171265253615</v>
       </c>
       <c r="G170" t="n">
-        <v>0.4725342268036373</v>
+        <v>0.4434956179151463</v>
       </c>
       <c r="H170" t="n">
-        <v>0.5380165623555163</v>
+        <v>0.5014378674835506</v>
       </c>
       <c r="I170" t="n">
-        <v>0.6216209978557916</v>
+        <v>0.5658843034873468</v>
       </c>
       <c r="J170" t="n">
         <v>0.8487548469516966</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.4354793992048654</v>
+        <v>0.434000776426503</v>
       </c>
       <c r="F171" t="n">
-        <v>0.4887511113946201</v>
+        <v>0.4846744096122149</v>
       </c>
       <c r="G171" t="n">
-        <v>0.5342171460336734</v>
+        <v>0.5270259421840379</v>
       </c>
       <c r="H171" t="n">
-        <v>0.575823643392148</v>
+        <v>0.5642242828722865</v>
       </c>
       <c r="I171" t="n">
-        <v>0.6253864724954153</v>
+        <v>0.6055307854804888</v>
       </c>
       <c r="J171" t="n">
         <v>0.6891826325489692</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3.054426705370102</v>
+        <v>3.171715893322208</v>
       </c>
       <c r="F172" t="n">
-        <v>2.990422212605619</v>
+        <v>3.178214196729481</v>
       </c>
       <c r="G172" t="n">
-        <v>2.753588245800107</v>
+        <v>2.988207540382207</v>
       </c>
       <c r="H172" t="n">
-        <v>2.443733349453433</v>
+        <v>2.736024382527345</v>
       </c>
       <c r="I172" t="n">
-        <v>1.999457629897079</v>
+        <v>2.405464714966742</v>
       </c>
       <c r="J172" t="n">
         <v>0.1372690786871351</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>0.2518441337797526</v>
+        <v>0.2168794236812328</v>
       </c>
       <c r="F173" t="n">
-        <v>0.3392299499719054</v>
+        <v>0.2841387891724802</v>
       </c>
       <c r="G173" t="n">
-        <v>0.4158070562522047</v>
+        <v>0.343401968446753</v>
       </c>
       <c r="H173" t="n">
-        <v>0.5063405971193432</v>
+        <v>0.4059237847028689</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6769173546503632</v>
+        <v>0.5223700843998427</v>
       </c>
       <c r="J173" t="n">
         <v>1.330872715428976</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1.225519699512147</v>
+        <v>1.260115837049097</v>
       </c>
       <c r="F174" t="n">
-        <v>1.254292646351043</v>
+        <v>1.30801857459338</v>
       </c>
       <c r="G174" t="n">
-        <v>1.266767011911137</v>
+        <v>1.335335854665521</v>
       </c>
       <c r="H174" t="n">
-        <v>1.265861439137313</v>
+        <v>1.35657296702699</v>
       </c>
       <c r="I174" t="n">
-        <v>1.206193644531129</v>
+        <v>1.341694261968123</v>
       </c>
       <c r="J174" t="n">
         <v>0.5498239015316286</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>0.2964460602165224</v>
+        <v>0.2399517946451885</v>
       </c>
       <c r="F175" t="n">
-        <v>0.4197855951557696</v>
+        <v>0.3499551083501374</v>
       </c>
       <c r="G175" t="n">
-        <v>0.5311276301168809</v>
+        <v>0.4638737530692537</v>
       </c>
       <c r="H175" t="n">
-        <v>0.643275424142069</v>
+        <v>0.5779151116153775</v>
       </c>
       <c r="I175" t="n">
-        <v>0.77112112323649</v>
+        <v>0.7035736525191391</v>
       </c>
       <c r="J175" t="n">
         <v>0.9351431631013997</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>0.4126067232100087</v>
+        <v>0.4145134173030141</v>
       </c>
       <c r="F176" t="n">
-        <v>0.4237952863444254</v>
+        <v>0.4208884705534946</v>
       </c>
       <c r="G176" t="n">
-        <v>0.4437769337520999</v>
+        <v>0.4336973194069097</v>
       </c>
       <c r="H176" t="n">
-        <v>0.4741076692820537</v>
+        <v>0.4548505601161051</v>
       </c>
       <c r="I176" t="n">
-        <v>0.527814779575008</v>
+        <v>0.493896968873182</v>
       </c>
       <c r="J176" t="n">
         <v>0.6622146451754066</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>0.713786097907706</v>
+        <v>0.7143966083522887</v>
       </c>
       <c r="F177" t="n">
-        <v>0.9584214056799805</v>
+        <v>0.9782647741488997</v>
       </c>
       <c r="G177" t="n">
-        <v>1.173331446572577</v>
+        <v>1.222544488633956</v>
       </c>
       <c r="H177" t="n">
-        <v>1.288447073200873</v>
+        <v>1.372924680603151</v>
       </c>
       <c r="I177" t="n">
-        <v>1.260617557139935</v>
+        <v>1.394793462442629</v>
       </c>
       <c r="J177" t="n">
         <v>0.6257732316359995</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>0.2106767744421952</v>
+        <v>0.2033354162535126</v>
       </c>
       <c r="F178" t="n">
-        <v>0.2504246418201561</v>
+        <v>0.2374488132154662</v>
       </c>
       <c r="G178" t="n">
-        <v>0.2830878561450549</v>
+        <v>0.263696564569407</v>
       </c>
       <c r="H178" t="n">
-        <v>0.3184476572912059</v>
+        <v>0.2894510888890816</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3785380699155801</v>
+        <v>0.3315850391342706</v>
       </c>
       <c r="J178" t="n">
         <v>0.5754636161423579</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>0.5719096083062638</v>
+        <v>0.5783198300696692</v>
       </c>
       <c r="F179" t="n">
-        <v>0.621371551031342</v>
+        <v>0.6302598446289848</v>
       </c>
       <c r="G179" t="n">
-        <v>0.6737675472827772</v>
+        <v>0.6862230442731443</v>
       </c>
       <c r="H179" t="n">
-        <v>0.7130136251475164</v>
+        <v>0.7308604227014269</v>
       </c>
       <c r="I179" t="n">
-        <v>0.7331974234964974</v>
+        <v>0.7616300505324342</v>
       </c>
       <c r="J179" t="n">
         <v>0.5687905092912359</v>
